--- a/regulatory-compliance/cloud-foundation/9.1/swift-csf/vcf-91-companion-swift-csf.xlsx
+++ b/regulatory-compliance/cloud-foundation/9.1/swift-csf/vcf-91-companion-swift-csf.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="190" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Version 910-20260612-01</t>
+          <t>Version 910-20260623-01</t>
         </is>
       </c>
     </row>
@@ -536,17 +536,16 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Disclaimer</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Additional Resources</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
-This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+          <t>This is one of a library of companion guides that map VMware Cloud Foundation and its advanced services to security and compliance frameworks. For each framework, the guide is published as a spreadsheet, a CSV data file, a Markdown document, and a PDF, together with a Security Configuration Guide crosswalk that identifies the VCF technical hardening settings relevant to that framework. The companion guide library, the VMware Cloud Foundation Security Configuration Guide, and related security documentation, sample scripts, and Q&amp;A are available at https://brcm.tech/vcf-security.</t>
         </is>
       </c>
     </row>
@@ -554,12 +553,28 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
+This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Copyright (c) CA, Inc. All rights reserved.
 You are hereby granted a non-exclusive, worldwide, royalty-free license under CA, Inc.'s copyrights to use, copy, modify, and distribute this software in source code or binary form for use in connection with CA, Inc. products.
@@ -568,16 +583,16 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Third Party Identifiers and Mappings</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>This document includes regulatory compliance and security control identifiers from external sources as a convenience to end users. This does not constitute endorsement, in either direction.
 There is not a one-to-one mapping of product capabilities to third-party controls. A product capability, or set of capabilities, may be applicable to multiple controls. Conversely, a control may be satisfied with the use of multiple capabilities.
@@ -853,12 +868,11 @@
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) supports least privilege through role-based access control with a defined set of predefined roles and the ability to clone and customize roles for narrower operational scope. The 9.1 release consolidates Site Recovery Manager and vSphere Replication management under a single permissions model where PNR augments vCenter roles and permissions with additional permissions that allow detailed control over PNR-specific tasks and operations. PNR also verifies permissions on the remote vCenter instance as part of its access control validation, so privilege assignments are evaluated at both sites.
-By default, PNR restricts login access to vCenter administrators; other users must be explicitly granted access by an administrator through the PNR interface. Users or user groups assigned a PNR role who are not vCenter administrators do not obtain vSphere Replication privileges, because PNR roles do not include the privileges of vSphere Replication roles. A user who is not a vCenter administrator but requires privileges to perform both PNR and vSphere Replication operations should be added to two user groups, one for each role type, to avoid granting vCenter administrator privileges.
-vSphere Replication uses role-based access control with predefined roles that can be cloned and customized by adding or removing privileges based on organizational needs. PNR supports role propagation to child objects in the inventory hierarchy, allowing administrators to extend privileges from parent objects such as folders to all virtual machines within them, or to assign permissions at specific inventory levels without propagation when narrower scope is required. When permissions are assigned without propagation, users must have at least Read-only permission on all parent objects in the vCenter inventory.
-PNR for VCF Automation access is controlled through role-based permissions assigned to Provider Administrators, Organization Administrators, Project Administrators, and Project Advanced Users, aligning RBAC with VCF Automation tenancy boundaries. Namespace unpair operations require Organization Administrator role authorization. In shared recovery site configurations, PNR restricts users from changing roles or assigning permissions for objects not dedicated to their own use, which helps prevent unauthorized privilege escalation across tenants, and the vCenter administrator manages PNR permissions so that each user has sufficient privileges to configure and use PNR but no user has access to resources belonging to other tenants.
-PNR requires separate privilege assignment for testing a recovery plan and running a recovery plan, which helps prevent unintended changes at both sites that would require significant time and effort to reverse. PNR roles that allow users to run commands on PNR Server should be assigned to trusted administrator-level users only, and PNR server access should be limited to administrators to reduce the number of accounts available to an attacker. PNR administrators can assign SrmAdministrator or SrmProtectionGroupsAdministrator roles to the automatic protection user or user groups for managing automatic protection permissions.
-For the 9.1 Clean Room Orchestrator, at least one user must be assigned the Organization Owner role to enable administrative access to all resources in the Organization, with additional roles available for narrower delegation. VCF Operations orchestrator workflows for PNR require administrator credentials to access and execute, which restricts non-administrative users from performing sensitive recovery operations through the orchestration interface.</t>
+          <t>Protection and Recovery (PNR) implements role-based access control through purpose-built roles registered in VMware vCenter and through a multi-tenant administrative model for Protection and Recovery for VCF Automation. The SRM Administrator role allows users or user groups to perform all PNR configuration and administration operations. The Protection and Recovery Administrator role can be assigned to user groups to manage permissions. Default roles provide the privileges users require to manage protection groups and perform recoveries, while restricting access to resources belonging to other users.
+For automatic protection of virtual machines within a protection group, administrators assign either the SrmAdministrator or SrmProtectionGroupsAdministrator role to the automatic protection user or user group. This scopes the protection actions performed on the user's behalf to the privileges of the assigned role.
+Each role is a collection of privileges that defines the actions a user can perform on the protection and recovery site. A user can have at most one role on an object, but roles combine when the user belongs to multiple groups that all have roles on the object. PNR supports propagating roles to child objects in the inventory hierarchy, so administrators can extend privileges from parent objects such as folders to all virtual machines within them.
+Protection and Recovery for VCF Automation introduces a multi-tenant role model with Provider Administrator, Organization Administrator, Project Administrator, and Project Advanced User. Each role has specific authorization levels for disaster recovery operations. Provider Administrators select which replication classes each Organization can use, restricting organizational access to specific recovery configurations. Organization Administrators manage the pairing of namespaces and assignment of replication classes within their tenancy.
+Underlying directory services, authentication, and enterprise identity governance are provided by VCF SSO and the broader VCF platform. PNR consumes those identities and layers its protection and recovery roles on top of them.</t>
         </is>
       </c>
       <c r="K3" s="10" t="inlineStr">
@@ -883,13 +897,11 @@
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides a native role-based access control (RBAC) system on the Avi Controller that restricts and controls privileged access to application delivery resources. The RBAC model assigns each user a role that governs their access level, with three permission states available per resource: write, read, or no access. The No Access privilege level is a distinct state that blocks users from accessing, reading, or listing resources entirely. Administrators can create custom roles through the Controller UI that grant precisely scoped access to specific system areas, with each resource configured independently. This supports least-privilege configurations tailored to distinct operational roles such as application operators, application admins, and system administrators.
-For environments requiring finer-grained control, Avi's Extended Granular RBAC applies and enforces label-based permissions on cloud objects. The restrict_cloud_read_access field in controller properties governs whether label-based access scoping applies to cloud object reads. Roles can be configured with write_access type and the resource permission_pool setting to restrict role privileges to specific pool sub-resources such as subresource_pool_enabled, providing field-level access scoping within a resource type. Auth Mapping rules can be updated to deny privileges to specific users, blocking them from obtaining any roles or tenants upon login. Multi-tenant deployments can scope access by tenant: user groups can be mapped to a limited set of tenants with read-only privileges, while separate groups hold application owner privileges within those same tenants, enabling separation of duties between groups managing different applications or environments within a shared Avi deployment.
-Avi supports TACACS+ server integration for centralized authentication and role assignment. Authorization attributes from a TACACS+ server map Avi users to roles and tenants, allowing organizations to govern privileged access through their existing network access control or identity infrastructure. The Avi Controller also supports LDAP authentication with the Administrator Bind configuration for user authentication and group membership validation. LDAP user account passwords are managed remotely and set by an administrator, not locally.
-Administrators can create custom user account security profiles with organization-specific thresholds for password history, login failure, session limits, and credential timeout policies. The Controller implements Super User Accounts as a separate user account security mechanism. The admin account is maintained as a locally authenticated account even in systems configured for remote authentication. The avidebuguser account has sudo privileges on the Avi Controller for Linux CLI access, and access to this account should be restricted to authorized personnel. Using role-based access control, the ability to export certificates and private keys must be restricted to the fewest administrators possible.
-Avi Cloud Console enforces access control through two access levels: Full Access (User Administrator or Product Administrator role) and Read-Only (Site Access role), with differentiated permissions for license visibility, management, and administration operations.
-When Avi is deployed in a VMware vCenter environment, the Cloud Connector uses a dedicated vCenter account configured with a minimal set of permissions. Two vCenter roles are required: one with global privileges and another with folder-level privileges. The Avi-Folder-Role scopes the account's permissions to the specific folders containing Service Engine VMs in the vCenter inventory. In VCF deployments with a vSphere Supervisor, the Avi Controller cloud configuration supports either a vCenter administrator account or a dedicated account with lesser, precisely defined permissions. The Cloud Connector role requires specific vCenter privileges covering Virtual Machine Guest Operations, Host Local Operations, and other provisioning capabilities, following the principle of least privilege for service account access to the underlying platform.
-Several permissions classified under Operations and Administration are not supported for per-application label-based RBAC, including L4POLICYSET, WAFPOLICYPSMGROUP, PINGACCESSAGENT, NETWORKSERVICE, and NATPOLICY, among others. These permissions remain under global administration scope and cannot be delegated to application-scoped roles.</t>
+          <t>VMware Avi Load Balancer provides role-based access control mechanisms on the Avi Controller that restrict which accounts hold privileged access. The Controller enforces Tenant and Role assignment during account creation, scoping each user's access to specific areas of the system based on their assigned role and tenant membership. Roles can be predefined or custom; administrators can create custom roles tailored to specific access requirements when predefined roles do not meet the needs of a given account. Role assignment is available at account creation or at any time thereafter through the Role drop-down menu in user account configuration.
+The admin user account is the standard administrative account for Avi Load Balancer and is authorized to perform the highest-level operations, including user creation and authorization, tenant creation, and all infrastructure operations associated with the admin tenant. The admin account is maintained as a locally authenticated account even on systems configured for remote authentication. Once a user is assigned Super User privileges, the Super User Rule takes effect: no subsequent tenant or role mapping assignments can override that access level, making superuser designation a high-consequence privilege that requires an explicit administrative action to grant or revoke.
+Within each user account, the assigned role is mapped to a tenant, so users can access resources only to the extent permitted by their role within that tenant. Privileged access in one tenant does not carry over to other tenants. This tenant-scoped role assignment allows organizations to enforce fine-grained access boundaries across multi-tenant deployments.
+In global server load balancing (GSLB) deployments, Avi Load Balancer supports creation of non-admin users with assigned roles for granular access control. Dedicated role accounts can be assigned specific GSLB roles, such as the gslbsitemembadmin account assigned the Gslb_Group_Member_Enabled role, restricting each account's capabilities to its designated function. The Avi Kubernetes Operator (AKO) extends role-based access control to Kubernetes workloads through Custom Resource Definitions (CRDs) that can be governed by Kubernetes RBAC policies, allowing stricter access control over which users can configure routing rules and related resources.
+The License Hub component within Avi Load Balancer enforces role-based access through two distinct local user accounts: an Admin account with the enterprise_admin role for full system management, and an Audit account with the auditor role scoped to system auditing purposes. This separation keeps high-privilege management access distinct from read-oriented audit access.</t>
         </is>
       </c>
     </row>
@@ -921,22 +933,15 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>VCF provides secure baseline configurations for all major platform components, consistent with industry-accepted hardening standards. The VCF Security Baseline is a purpose-built document that builds on VCF security fundamentals to address frequently requested compliance standards, regulations, and frameworks. It is designed and validated to tailor security configurations without affecting VCF's ability to meet its design objectives. Organizations can use the VCF Security Baseline to evaluate both default and non-default configurations and to secure their environments in a compliance context.
-VCF Operations includes a consolidated out-of-the-box benchmark called the VCF 9 Security Baseline, which provides a ready-to-use compliance profile for evaluating the security posture of a VCF environment. This benchmark enables automated assessment of configurations against the documented baseline, helping maintain a consistent configuration across VCF components. ISO Security Standards compliance benchmarks are also available from the VCF Operations repository as a native pack, giving organizations the ability to measure their environment against internationally recognized hardening standards. Broadcom also provides DISA Security Technical Implementation Guides (STIGs) for VCF components, including vSphere 7.0 and vSphere 8.0 STIGs, which provide detailed instructions for securing and configuring systems to meet specific security requirements.
-Individual VCF components have their own security configuration guides that document hardening recommendations. The vSphere Security Configuration Guide provides best practices for securing VMware vCenter, including securing the installation, configuring access and authentication, defining roles and permissions, and enabling auditing and logging. VMware ESX host hardening covers authentication and authorization settings, disabling unnecessary services, enabling security features such as Secure Boot and Trusted Platform Module (TPM), and implementing network security measures. The vSphere Security Configuration Guide documents specific STIG-aligned values for the Security.PasswordQualityControlPwquality setting on ESX hosts, including parameters such as minlen=15, maxrepeat=3, maxclassrepeat=4, difok=4, and enforce_for_root. The NSX Security Configuration Guide provides recommendations for securing NSX components, including NSX nodes, NSX Controllers, and NSX Edge nodes, by configuring strong authentication, implementing role-based access control, and securing administrative access.
-VCF Operations also provides a Configure Host Security Config Data workflow that allows selective enforcement of host security hardening rules. Beyond security settings, vSphere Lifecycle Manager maintains a desired-state cluster image that defines the ESX base build, vendor add-ons, and firmware for every host in a cluster, so the software baseline stays consistent across hosts, and VCF Operations runs scheduled drift detection that flags configuration deviations from the desired state for remediation. Administrators can configure individual configuration elements under Enforce Options, enabling granular control over which baseline settings are applied and enforced across the environment. This supports reducing organizational and business risk by maintaining configuration consistency. vSphere Host Profiles provide an additional mechanism for automated and centrally managed host configuration baseline enforcement, capturing a reference host's configuration and applying it consistently across ESX hosts, covering memory, storage, networking, and other configuration aspects.
-For containerized workloads, VMware Kubernetes Service (VKS) includes preconfigured security policy templates. The Baseline security template provides a set of constraints that restrict known privilege escalations while maintaining compatibility with common containerized workloads.
-DISA STIGs for Supervisor and VKrs are available to guide hardening of the Supervisor control plane and individual VKS cluster releases, providing baseline security guidance at the same standard as the DISA STIGs applied to VCF infrastructure components. The VKS cluster management interface provides out-of-the-box security policy templates that mirror industry-standard Pod Security Standards profiles, including both Baseline and Restricted configurations. Custom VKS Cluster Management Security Policy templates are also available to fine-tune individual security context parameters and support governance controls tailored to specific organizational requirements.
-Pod Security Admission (PSA), enabled in VKr 1.25 and later, enforces pod security standards at the namespace level. Three policy profiles are defined: Privileged (unrestricted, for system-level workloads), Baseline (helps prevent known privilege escalations while allowing the default minimally specified pod configuration), and Restricted (heavily restricted, following pod hardening best practices). Three enforcement modes are available: enforce, warn, and audit. The podSecurityStandard field in the ClusterClass API encodes the intended security posture in cluster definitions, accepting these modes with specific policy versions and namespace exemptions so that baseline security configurations are applied consistently across VKS deployments. System namespaces including kube-system, tkg-system, and vmware-system-cloudprovider are excluded from pod security enforcement. The PSA admission controller can also be statically configured with default enforce, audit, and warn levels for unlabeled namespaces, so namespaces created without explicit labels still receive a defined security baseline. To support gradual policy adoption, audit and warn modes can be set to a stricter level such as restricted while enforce remains at baseline, giving administrators visibility into policy violations before full enforcement is applied. VCF Automation IaaS Resource Policies provide an additional enforcement point at the management layer, supporting requirements that Kubernetes clusters operate at a minimum baseline pod security level.
-Kubernetes-native kernel security mechanisms provide workload-level baseline hardening options. seccomp restricts the Linux kernel system call surface available inside containers using BPF-based profiles, and the RuntimeDefault seccomp profile provides a strong set of security defaults while preserving workload functionality. AppArmor and SELinux provide further kernel-level restrictions through default configurations that offer foundational protections. Kubernetes default RBAC role bindings should be reviewed as part of establishing a security baseline, as defaults may grant broader access than a hardened configuration requires. Isolating each workload in its own Kubernetes namespace allows tailored security policies to be applied per workload and restricts access to namespace-scoped resources such as ConfigMaps and Secrets.
-Harbor Registry, available as a standard package for VKS clusters, supports a controlled baseline for container artifacts entering the environment. Harbor provides vulnerability scanning, content trust, and policy-based replication, along with role-based access control and artifact security policies, supporting controlled management of the container image supply chain. For stand-alone virtual machines deployed in vSphere Supervisor environments, Content Libraries can distribute VM images created with current patches and required security settings that follow corporate security policies.
-VMware Private AI Services (PAIS) provides PAIS-specific declarative configuration mechanisms that organizations can use to define and apply baseline settings across the AI infrastructure stack on VCF.
-The primary mechanism is the PAISConfiguration custom resource. Private AI Services settings are declared in a YAML file compliant with the PAISConfiguration schema and applied with kubectl, giving administrators a single resource that captures observability, identity, and trust configuration for an organization namespace. Observability includes the spec.observability.prometheusRuntime section for Prometheus metrics collection with a configurable storage class and metrics retention period, and an llmTraces section for routing large language model traces to an OpenTelemetry Collector. The PAISConfiguration custom resource can be patched with kubectl patch and verified with kubectl get paisconfiguration, supporting baseline change control and drift detection at the AI service layer.
-Certificate trust is handled through the spec.clientTls.caBundleRefs section, which references ConfigMaps containing CA trust bundles. Private AI Services requires HTTPS trust bundles for the OIDC provider, the Harbor registry, content management systems hosting knowledge database data, and MCP servers that provide tools to models. Trust bundles can be organized per application, with periodic updates required before certificate expiration. Access scope is restricted through the authorizedGroups setting, which limits Private AI Services access to specified OIDC groups.
-Harbor registry distribution carries baseline controls for model and image artifacts. Replication rules support configurable filters, target namespace, and trigger mode, including a manual trigger mode, so administrators can align artifact replication with organizational policy for connected and disconnected sites. The Model Gallery uses Harbor project access capabilities to restrict access to sensitive training and tuning data. Air-gapped deployments capture the self-hosted registry URL and registry login credentials as part of the activation flow.
-Workload resource baselines are defined through SupervisorNamespaceClassConfig, which specifies per-zone CPU limits, CPU reservations, memory limits, and memory reservations for resource allocation across zones. GPU-capable VM classes can carry GPU reservations and be confined to a single zone or supervisor namespace, supporting isolation of GPU consumption to a specific tenant. A default storage policy selection in the Private AI Services quickstart defines storage placement and resources for the service database.
-Deep Learning VM (DL VM) baselines are captured through VCF Automation self-service catalog items that parameterize VM class, data disk size, user password, and optional SSH public key authentication for remote access. The DL VM OVF property config-json accepts a base64-encoded configuration file that controls DCGM Exporter metrics visibility through export_dcgm_to_public and JupyterLab authentication through enable_jupyter_auth, giving operators a consistent surface to define DL VM hardening parameters.
-Credentials supplied during Private AI Services activation, including the private container registry password and proxy password, are stored as secrets in VCF Automation rather than as plaintext configuration values, supporting credential hygiene as part of the deployment baseline.</t>
+          <t>VCF is built on VMware vSphere, a hypervisor-based virtualization platform where virtual machines encapsulate complete computing environments and run independently of the underlying physical hardware. Each virtual machine is a software-defined computer that runs its own operating system and applications, backed by the physical resources of a host but fully abstracted from the specific hardware configuration. This architectural approach directly supports the deployment of a diversity of operating systems and applications on shared infrastructure.
+VCF supports a broad range of guest operating systems within virtual machines. Guest customization is available for both Linux and Windows operating systems, and the guest operating system specified for a virtual machine determines the supported virtual devices and the available number of virtual CPUs. Applications that require a custom kernel or custom operating system can run in virtual machines, making VCF suitable for workloads that cannot be containerized or that depend on specific OS environments. VMware Hardware Assisted Virtualization can be exposed to guest virtual machines, enabling applications and nested hypervisors that require hardware virtualization support to run without binary translation or paravirtualization. For Windows guests, vSphere supports Windows Virtualization Based Security (VBS), which makes hardware virtualization, IOMMU, EFI, and secure boot available to the guest operating system, allowing Windows workloads to leverage VBS-dependent security features such as Credential Guard.
+VCF provides several mechanisms for standardized and repeatable deployment of diverse workloads. Virtual machines can be created by converting an existing virtual machine to a template and producing multiple clones from that template, enabling consistent provisioning of different operating system and application configurations. Virtual machines use virtual disks to store their operating system, program files, and data, and support migration between hosts, snapshots, and linked clones. Virtual applications (vApps) allow one or more virtual machines to be deployed, managed, and maintained as a single unit, encapsulating multi-tier application stacks with their operational policies and service-level definitions. vApps can be customized at the application level using the OVF environment, supporting portable packaging of complex application topologies.
+VMware Kubernetes Service (VKS) extends these virtualization capabilities into the Consumption layer by providing a unified platform for running both containerized applications and virtual machines under a single control plane embedded in the VCF platform. vSphere Supervisor embeds a Kubernetes control plane directly into VMware ESX hosts, exposing a declarative API surface that allows organizations to operate VM-based and container-based workloads with consistent infrastructure management and security policies across diverse application architectures.
+Within vSphere Supervisor, virtual machine classes are represented by the VirtualMachineClass resource, which defines the virtual hardware profile including CPU and memory for each VM in a Supervisor namespace. Platform teams can define standardized compute profiles for different workload types using these classes. VM Operator enables management of virtual machines with a Kubernetes-style, declarative API expressed through YAML files that specify the VM image, VM class, and storage class. VM images are templates that bundle an operating system, applications, and data into a reusable definition. VM Service manages the lifecycle of both standalone VMs and the VMs that make up VKS clusters within a namespace, converting the desired state specified by operations teams into the realized state against backing infrastructure resources. The VM Service guidance identifies virtual machines as the appropriate model for applications that have specific hardware requirements, depend on a custom kernel, or are better suited to running in a VM than as containers.
+VKS clusters support multiple operating systems for cluster nodes. Within a single Kubernetes release, node OS images are available for PhotonOS, Ubuntu 22.04, Ubuntu 24.04, Red Hat Enterprise Linux 9, and Microsoft Windows Server 2022, with PhotonOS as the default and alternative operating systems selectable through annotations in the cluster specification. This allows a single cluster infrastructure to serve applications packaged for different Linux distributions or for Windows without requiring separate cluster topologies. VKS clusters also support heterogeneous node pools where Linux and Windows worker nodes coexist in the same cluster, enabling containerized Windows applications and Linux applications to run together managed through the same Kubernetes API.
+For containerized workloads with stricter isolation requirements, vSphere Pods provide an additional option: each vSphere Pod is backed by a lightweight virtual machine that provides hardware-level isolation consistent with enterprise security policies, rather than the OS-level isolation of standard container runtimes. vSphere Supervisor therefore supports the full range of isolation approaches within a single environment: hardware-level VM isolation for workloads that require separate OS instances per workload, OS-level container isolation for lighter-weight workloads, and hardware-backed vSphere Pods for containerized applications that need stronger isolation boundaries.
+VCF Operations HCX extends workload diversity by supporting OS-assisted migration for virtual machines running non-vSphere guest operating systems in both Linux and Windows environments. HCX validates KVM and Hyper-V hypervisors for guest operating system migration, allowing organizations to consolidate heterogeneous workloads from other virtualization platforms onto VCF.
+VCF Operations provides OS and application monitoring capabilities that discover operating systems and applications running within provisioned guest operating systems and collect runtime metrics for monitoring and troubleshooting. This visibility spans the diverse set of workloads running on the platform, giving administrators insight into the health and performance of different operating systems and applications without requiring agents specific to each guest OS type.</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
@@ -1031,17 +1036,14 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>VCF provides built-in mechanisms for implementing and governing network security controls across the infrastructure stack, spanning virtual switching, network segmentation, policy management, role-based access control, audit logging, and documented hardening procedures.
-NSX, the networking component of VCF, delivers a hierarchical security policy framework organized around domains, security policies, and individual rules. Each rule can be configured with action, direction, IP protocol, source groups, destination groups, services, and scope, providing administrators a structured and repeatable model for defining network security posture. Security policies are organized into categories (Emergency, Infrastructure, Environment, Application) so that multiple administrators can create and manage policies without conflicts or overrides. Firewall rules within each category are organized into sections, supporting logical grouping and ordered evaluation. This hierarchical structure supports both centralized governance and delegated administration, allowing organizations to maintain consistent security standards while enabling application teams to manage policies within their assigned boundaries.
-VCF's network security governance model is built on role-based access control (RBAC) that spans networking and security functions. NSX Projects and VPCs support scoped role assignments including VPC Admin, Security Admin, Network Admin, Security Operator, and Network Operator roles. These roles can be assigned at the project or VPC level, enabling least-privilege access to network security configuration. A VPC Admin has full access to networking and security objects within their assigned VPC, while Enterprise Admins retain overarching control. NSX Advanced Network Management extends RBAC to specific networking components including static routes, locale services, segments, segment profiles, IP address pools, forwarding policies, DNS, DHCP, load balancing, and NAT. This separation of duties allows organizations to delegate day-to-day network security operations while retaining centralized oversight.
-The NSX VPC workflow provides a structured mechanism for implementing network security controls at the application level. Application owners can add subnets inside their assigned VPC and configure security policies to meet workload requirements without dependency on the Enterprise Admin. VPC Admins and Security Admins add security policies within the VPC to address the security requirements of connected workloads. Default East-West firewall rules are activated automatically when an appropriate security license is applied and can be adjusted as needed. This self-service model, bounded by RBAC, allows security policy implementation to scale across the organization while maintaining governance guardrails.
-VCF includes multiple layers of network security controls. VMware vDefend, a separately licensed product that extends NSX, provides Distributed Firewall enforcement across deployment and operational scenarios, while its Gateway Firewall provides perimeter security. Context profiles and Layer 7 access profiles enable firewall rules with application-level and domain-based attributes for both distributed and gateway firewall enforcement. For containerized workloads, the Antrea Container Network Interface (CNI) plugin in VMware Kubernetes Service (VKS) enforces Kubernetes NetworkPolicy at the namespace and pod level. The AntreaPolicy feature gate enables AntreaNetworkPolicy and ClusterNetworkPolicy objects that extend standard NetworkPolicy with richer Layer 4 rule sets; traffic not explicitly permitted is blocked by default when a policy applies to a pod. The Antrea NetworkPolicyStats feature gate collects enforcement statistics, giving operators visibility into which policies are matching traffic and at what volume to support operational monitoring and periodic policy review. A Kubernetes cluster must provide and enforce NetworkPolicy for network security controls to be effective.
-The VKS networking layer within VCF integrates directly with the broader NSX security framework. Supervisors using NSX VPC networking operate in the system VPC while VKS clusters reside in vSphere Namespace VPCs, providing topology-level isolation between the management plane and workload clusters. NSX VPC pod IP pools are configured as Private, restricting direct external accessibility of pod addresses. Antrea EgressSeparateSubnet allows egress traffic from specific workloads to originate from a subnet distinct from the default node subnet, supporting more granular traffic segmentation. The Network Control Plane (NCP) component bridges Kubernetes networking objects with NSX, realizing VirtualNetwork, VirtualNetworkInterface, and LoadBalancer resources for the VKS control plane; communication between Supervisor and NSX is secured using TLS. Kubernetes control plane services communicate using certificates by default, and connections from nodes and pods to the control plane are secured by default and can run over untrusted networks. Supervisor networking architecture requires a deliberate deployment-time choice: NSX with embedded load balancer, or vSphere Distributed Switch with external load balancer. This choice determines which network security mechanisms are available downstream, and organizational procedures should reflect which path is in use. VKS Cluster Management Custom Policies provide a governance mechanism that should be reviewed and updated to ensure policy logic reflects current security and operational requirements. The Argo CD Supervisor Service deployment implements network segmentation and firewall rules to secure communication between its components. Organizations operating service meshes alongside VKS gain OSI Layer 7 network policies based on workload identity and mutual TLS encryption for pod-to-pod traffic, providing an additional isolation layer beyond namespace boundaries.
-At the virtual infrastructure layer, vSphere Distributed Switches provide centralized management of virtual networking, handling traffic for all associated hosts in a data center. Distributed switches support network segmentation using Private VLAN (PVLAN) and VLAN-based SPAN for distributed port mirroring. Network segmentation is built into the VCF architecture: management traffic, vMotion, and storage traffic are isolated on separate networks. Network I/O Control allocates bandwidth to traffic types based on share values, and the Storage Traffic Separation network profile creates dedicated vSphere Distributed Switches with separate physical NICs for storage traffic isolation. NSX distributed port groups and uplink port groups support Traffic Filtering and Marking policies configurable at the port level, providing additional granularity for layer 2 security controls. ESX hosts also support IPsec for VMkernel network communication, with security associations and policies configurable via esxcli network ip ipsec commands, supporting both transport and tunnel mode with upper layer protocol filtering for tcp, udp, icmp6, or any traffic.
-vSphere Lifecycle Manager enforces desired-state configuration for hosts and clusters, applying and remediating configuration to match the defined software specification. This helps detect and address configuration drift that could weaken network security posture, and the remediation process can be managed programmatically through the vSphere Automation API.
-VCF publishes security baselines through the Security Configuration Guide and DISA STIGs. The NSX Security Configuration Guide provides documented procedures for securing NSX components, including NSX nodes, NSX Controllers, and NSX Edge nodes. Recommendations cover configuring strong authentication, implementing RBAC, and securing administrative access. NSX security best practices address creating and managing security groups, implementing distributed firewalling, configuring security policies, and enforcing microsegmentation to control network traffic. Security Technical Implementation Guides for Supervisor and VMware Kubernetes Release (VKr) components are available to provide hardening guidance for VKS deployments, extending the documented security baseline to the containerized workload layer. These documented hardening procedures, aligned with industry-standard best practices, give organizations a baseline for developing and updating their network security control procedures.
-Audit logging supports ongoing governance by recording security policy changes with full traceability. NSX firewall audit logs capture the user performing the operation, the module name, operation type, operation status, and modified resource details including the security policy display name, identifier, path, and rule configurations. This audit trail enables organizations to track who changed network security policies, what was changed, and when, supporting both compliance review and change management processes.
-Programmatic management capabilities, including PowerCLI cmdlets such as InvokePatchSecurityPolicyForDomain for creating distributed firewall policies, support infrastructure-as-code approaches to network security governance, enabling version-controlled and repeatable policy deployment.</t>
+          <t>VCF provides network architecture, routing topology, segmentation, and proxy capabilities that help organizations restrict or control internet access from sensitive data enclaves. Firewall enforcement at zone boundaries is delivered by VMware vDefend, a separate product layered on top of base VCF networking. Full enforcement of internet access policies also requires organizational controls beyond what VCF delivers natively.
+NSX, the networking component of VCF, implements a tiered gateway architecture that controls north-south traffic flow between internal segments and external networks. A tier-0 gateway connects to tier-1 gateways via downlinks and to physical infrastructure via external interfaces, providing the boundary between the software-defined network and the outside world. Tier-1 gateways connect to segments in the southbound direction and to a tier-0 gateway in the northbound direction. In a single-tier routing topology, the tier-0 gateway handles both east-west routing between segments and north-south connectivity to the physical network. This architecture gives administrators explicit control over which internal segments have a path to external networks. NAT rules on tier-0 and tier-1 gateways allow administrators to control how internal addresses are translated for external communication; SNAT is supported on both tier-0 and tier-1 gateways running in active-standby mode.
+The vDefend gateway firewall provides perimeter security control at the boundary between internal network segments and external networks. Administrators can create gateway firewall policies and apply them to tier-1 gateway service interfaces, defining rules that restrict or deny outbound connectivity from specific segments. Enterprise Admins and Project Admins can manage gateway firewall rules on tier-1 gateways within the context of an NSX project, giving per-tenant control over what traffic is permitted to leave the enclave. IP addresses and IP ranges can be specified in vDefend firewall rules to define which traffic is permitted to traverse network boundaries. For domain-based control, the vDefend distributed firewall supports FQDN-based rules that allow or reject traffic going to specific domains, with both a predefined list of FQDNs and custom FQDNs available for FQDN filtering policies. Gateway firewall rules do not support FQDN attributes in context profiles, so domain-based filtering is enforced through the Distributed Firewall rather than the gateway firewall. Organizations requiring stateful perimeter enforcement, microsegmentation, IDS/IPS, or traffic inspection at zone boundaries will need a vDefend license in addition to the base VCF networking capabilities.
+NSX projects enable isolation of security and networking objects across tenants within a single NSX deployment, supporting multi-tenant architectures where different security zones maintain distinct internet access policies.
+VCF Automation extends these controls through network profiles and security groups. On-demand private networks support VLAN-based isolation where segments are not connected to a tier-1 router, leaving no outbound routing path by design. For workloads that need controlled outbound connectivity, network profiles with isolation enabled by subnet or security group restrict which upstream networks are reachable. Outbound networks provide one-way access to upstream networks. A security group can define isolation settings for on-demand private or outbound networks, giving administrators granular control over which network segments have outbound access and which remain fully isolated. Two types of security groups are available: existing security groups selected from a predefined list, and on-demand security groups created through isolation policies on the Network Policies tab. An on-demand network with outbound access explicitly requires an external subnet configured with outbound access, meaning that networks without such a subnet assignment remain isolated by default.
+For environments where security policies require systems to be disconnected from internet access, VCF supports air-gapped deployments. VCF Operations HCX, for example, detects air-gap mode during installation and establishes no internet connections when that mode is selected. When limited external connectivity is needed in otherwise restricted environments, administrators can configure an internet server proxy to channel and control outbound requests rather than allowing direct internet access. VCF Automation supports HTTP proxy configuration for environments without external internet access, and the proxy must be configured for IPv4.
+At the platform level, the distributed switch includes built-in security controls that help protect traffic between workloads, and VCF Operations supports firewall hardening that restricts network access to internal services, reducing the attack surface of management components. The vSphere Distributed Switch also supports Traffic Filtering and Marking Policy, which allows administrators to configure traffic rules that allow or drop traffic on distributed port groups and uplink port groups, and Port Blocking Policies, which can selectively block specific ports from sending or receiving data on a distributed port group.
+These controls provide the infrastructure mechanisms to strictly control or prohibit internet access from secure zones. Defining and enforcing the specific access policies for each enclave, including which zones require complete isolation versus controlled outbound access, requires organizational security policy decisions and configuration of the appropriate gateway firewall rules and network profiles.</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -1051,11 +1053,14 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend provides the technical enforcement layer that underlies Network Security Control (NSC) implementation, though the procedural and governance aspects of developing and updating NSC procedures remain organizational responsibilities.
-Security Services Platform enables monitoring of traffic after publishing assets and security policies to NSX Manager, allowing administrators to refine policies and adjust security posture based on observed traffic behavior. Security Intelligence Policy Recommendations correlate observed traffic patterns within the NSX environment to assist with enforcing more dynamic security policies; these recommendations can be reviewed and published directly to the Distributed Firewall (DFW) rule set. The Security Intelligence infrastructure classification feature identifies compute entities providing network infrastructure services in the NSX environment, supporting structured policy development around infrastructure traffic categories.
-Dynamic NSGroups enable DFW and Gateway Firewall (GFW) rules to update automatically as workloads are deployed or modified in the environment. Security Services Platform provides a workflow to import data center hierarchy from CSV, which translates IP addresses to virtual machines, tags those VMs, and creates NSX groups necessary for segmentation planning. This supports the initial development of network security control structures from existing IP-based inventories.
-vDefend DFW security posture is applied to VPCs through system-defined Security Profiles accessible in NSX Manager. When a Security Profile is applied to a VPC in VCF Automation, the system automatically generates and realizes system-managed DFW rules within the NSX Project space. DFW policies extend to Bare Metal servers, with Bare Metal server groups, vDefend DFW policies, and rules defined in NSX Manager and managed through Security Services Platform. Malware Prevention Service is configured through the IDS/IPS &amp; Malware Prevention Setup wizard, which provides a guided sequence of steps to prepare the data center.
-NSX Federation Security provides centralized management of security policies across multiple sites through a Global Manager, supporting consistent policy enforcement in distributed and multi-site environments. The Security Overview dashboard in NSX Manager displays threat detection and response features, a visual summary of the overall security configuration, and the capacity of NSX objects, giving administrators visibility into the state of deployed network security controls.</t>
+          <t>VMware vDefend provides network security controls that contribute to prohibiting or strictly controlling internet access from sensitive data enclaves.
+The vDefend gateway firewall operates at the tier-0 and tier-1 gateway boundaries where north-south traffic flows between internal segments and external networks. Gateway Firewall policies can restrict or deny outbound connectivity from specific segments using Allow, Drop, or Reject actions. In VCF multi-tenant deployments, Enterprise Administrators can enforce project-level internet isolation using two Gateway Firewall strategies: VPC Isolation with Essential Services, which denies all general internet egress while permitting only essential infrastructure protocols such as DHCP, DNS, NTP, and ICMP; and Enterprise Gateway Isolation, which denies all communication between distinct projects. These strategies provide enforcement points where internet access from sensitive enclaves can be strictly controlled or prohibited entirely.
+The Gateway Firewall URL filtering capability enforces access control policies using L7 access profiles. When a URL filtering rule is configured, the L7 access profile actions determine how matched traffic is processed, allowing administrators to restrict which internet destinations workloads in a given enclave can reach.
+The vDefend distributed firewall enforces microsegmentation policies at the vNIC level within the data center. The Application Connectivity Strategy provides structured postures for egress control: the "Allow Intra, Deny Other Traffic" posture generates a default ANY/ANY/DROP rule that isolates workload groups from external communication by default. ALLOW EGRESS rules can be configured with Allow or Drop actions to control whether application entities can initiate outbound connections. Combining the Distributed Firewall for internal segmentation with the Gateway Firewall for perimeter control provides defense in depth for isolating sensitive enclaves.
+Security Intelligence in the Security Services Platform defines private IP ranges that establish the boundary between internal workloads and external traffic. Traffic that crosses this boundary is treated as external, supporting visibility into which workloads are communicating outside the data center perimeter.
+For environments where internet access from sensitive enclaves is prohibited by policy, vDefend components are designed to operate in air-gap and restricted-access configurations. The vDefend Distributed IDS/IPS can be configured for airgapped deployments where internet access is restricted or unavailable. Network Detection and Response can be configured for air-gap environments where internet connectivity to the vDefend Advanced Threat Prevention Cloud Service is not permitted. The Security Services Platform Private Mode supports highly secure, classified, or operationally sensitive environments where even manual internet access for licensing is restricted, and is commonly used in government, defense, and regulated industries where systems must operate without external connectivity.
+Administrators should note that the Malware Prevention Service requires internet access from the Security Services Platform even when files are not sent to the cloud for detailed analysis; this connectivity requirement should be factored into enclave internet restriction policies.
+Full prohibition of internet access from an enclave requires organizational policy decisions and configuration of the appropriate Gateway Firewall and Distributed Firewall rules. vDefend provides the enforcement mechanisms but does not itself define which enclaves are sensitive or what access policies should apply.</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -1295,13 +1300,9 @@
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides native, configurable cryptographic mechanisms to protect the confidentiality of data in transit at both the application data plane and the Controller management plane.
-Each virtual service in Avi is associated with an SSL/TLS Profile, which defines the accepted protocol versions, cipher suites, and their priority order. SSL/TLS Profiles are managed at Templates &gt; Security &gt; SSL/TLS Profile in the Controller UI. Predefined profile templates are available, including a System-Standard template, and administrators can create custom profiles to enforce the cipher suites and protocol versions appropriate for their environment. Elliptic Curve (EC) cryptography is available for virtual services and supports Perfect Forward Secrecy with less computational overhead than RSA-based key exchange. TLS persistence state exchanged between Service Engines when a client reconnects is carried in encrypted form. At the L4 proxy level, the Default-TLS protocol parser can be associated with a virtual service to inspect TLS handshake data using DataScript, supporting selective offload and re-encryption scenarios.
-In Kubernetes environments, the Avi Kubernetes Operator (AKO) supports a PKIProfile custom resource definition that enables certificate-based authentication and encryption for backend service communication. The System-Standard SSL Profile can be applied through the RouteBackendExtension CRD to enable SSL/TLS re-encryption for traffic to backend servers, providing modern cipher suites for Kubernetes ingress and routing scenarios. In VCF environments, the Avi load balancer uses secrets to handle encrypted HTTPS traffic, configured through the VCF IaaS Service Console.
-When FIPS mode is enabled on the Avi Controller cluster, all cryptographic operations across the Controller and Service Engines are restricted to FIPS 140-3 approved algorithms. Avi uses the OpenSSL FIPS Provider version 3.1.2 in this mode, which has been validated at FIPS 140-3 Security Level 1 and awarded Certificate #4985 by CMVP. Enabling FIPS mode is a cluster-level configuration that applies uniformly to all cryptographic material handled by the platform. FIPS mode does not support SSL Client Hello events in Avi DataScript, and post-quantum cryptographic capabilities are not available in FIPS mode.
-The Avi Controller and Service Engines use SSH for secure management communication. The SE_SECURE_CHANNEL designation classifies traffic between the Controller and Service Engines to maintain a dedicated secure communication channel. Avi also integrates with Let's Encrypt via the ACME protocol to automate certificate issuance and renewal for virtual services, and with hardware security modules such as the Thales Luna HSM for external key management. Remote server file transfer supports Secure Copy Protocol (SCP) and Secure File Transfer Protocol (SFTP). For deployments requiring hardware acceleration, Avi Service Engine integrates with Intel QuickAssist Technology to offload bulk cryptographic operations following SSL/TLS handshake completion.
-Avi DataScript exposes cryptographic functions for application-layer use cases. The avi.crypto.encrypt() function encrypts data using a caller-provided key, optional initialization vector, and algorithm parameter. The HTTP Cookie Encryption Gateway uses these functions to encrypt cookie values in HTTP responses, protecting session state carried between client and server. The avi.utils.rand_bytes function generates cryptographically secure random bytes for token and nonce generation.
-Defining which application traffic requires encryption and configuring the virtual service profiles to apply protection at the appropriate boundary are organizational data-policy decisions.</t>
+          <t>VMware Avi Load Balancer (Avi) provides application-layer transfer authorization mechanisms that verify client and service credentials before forwarding data to backend resources. For application traffic, Avi's OAuth and OpenID Connect (OIDC) integration supports the Authorization Code Grant Flow, through which the authorization server authenticates the resource owner, evaluates the client's access request, and issues access tokens only after authorization is confirmed. Clients must present a valid access token to the Avi virtual service; the Authorization Endpoint handles user-agent redirection to the authorization server, and the token endpoint validates the authorization code and authenticates the client using the client_id and client_secret before tokens are issued. This flow verifies that the requesting party holds the required authorization before any data transfer to the backend resource server is permitted.
+For more granular application-layer authorization, Avi supports Authorization Policies and DataScript within OAuth/OIDC flows. These allow administrators to define rules that evaluate token claims and request attributes, granting or denying forwarding based on whether the client meets the configured authorization criteria. This provides control over which clients and services have the write permissions or privileges required to access specific application endpoints.
+For administrative operations on the Controller, Avi's role-based access control enforces object-level write permissions. Write access to objects such as Virtual Services, Application Profiles, SSL/TLS Certificates, and Certificate Management Profiles is granted at the role and tenant level, so that only users with the requisite permissions can modify transfer-related configurations. TACACS+ integration supports centralized authorization by delivering attribute-value pairs from the TACACS+ server that map users to specific roles and tenants. The PASS_ADD and PASS_REPL statuses grant authorization to successfully authenticated users, while the FAIL status rejects those without the required attributes. Cisco ISE can be configured as a remote authentication and authorization backend for Avi, including with external identity sources such as OpenLDAP, providing centralized identity management for Avi administrative access. In Avi Load Balancer SaaS deployments, authorization tokens can be generated for service account authentication to the SaaS Controller.</t>
         </is>
       </c>
     </row>
@@ -1333,17 +1334,16 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>VCF provides integrated mechanisms for identifying, tracking, and remediating vulnerabilities across the infrastructure stack. These capabilities span automated detection, compliance monitoring, alert-driven tracking, structured remediation workflows, and lifecycle management tooling.
-VCF Diagnostics automatically detects known issues and critical vulnerabilities within the VCF software stack, providing detailed descriptions, root cause insights, and actionable remediation steps. This capability builds on several legacy diagnostics tools and operational data to deliver integrated issue detection and remediation from a single pane. Diagnostic Findings uses a library of log and property-based diagnostic rules (also called signatures) to identify known issues across the platform, giving operations teams a structured way to discover and resolve problems.
-VCF Operations extends vulnerability tracking through compliance management, which detects violations, highlights risk areas, and provides actionable remediation recommendations. When VCF Operations detects non-compliance with a defined policy, it generates alerts or notifications. Depending on the severity, administrators can configure automated remediation actions to bring objects back into compliance without manual intervention. VCF Operations also maps out-of-the-box workflows to recommendations and associates them with specific alerts, enabling automated remediation tied directly to detected conditions. To retrieve remediation recommendations for a specific virtual machine, the system must be connected to a VCF Operations instance with at least one triggered alert for that virtual machine.
-Configuration Drifts in VCF Operations provides a proactive method to monitor configuration changes across vCenter instances and vSphere clusters. Administrators can view and compare configuration drifts and identify settings that have changed over time. VCF Operations audit logging tracks each configuration change to an authenticated user who initiated the change or scheduled the job that performed the change, allowing administrators to determine who changed what and when.
-VCF lifecycle management simplifies and automates the process of applying updates and patches to software components within the VCF stack. VCF Operations includes patch planner functionality for updating or patching individual VCF core components in a VCF domain, and provides a Plan Patching capability to create patching plans for desired components. Pre-update validation runs upgrade prechecks to verify readiness before proceeding, identifying issues before the update starts. Update bundle management supports both online and offline depots; the VCF Download Tool and the lcm-bundle-transfer-util command handle bundle download, staging, and repository configuration for environments with limited or no internet connectivity.
-On the patching side, Broadcom releases security advisories for critical known vulnerabilities with step-by-step remediation instructions. Patch releases for VCF components provide time-sensitive fixes to security and catastrophic issues that affect business operations. These patches are released between major, minor, and maintenance releases and can be selectively applied based on environmental impact and operational costs.
-vSphere Lifecycle Manager (vLCM) manages desired-state configurations for ESX hosts. It can create a desired state that includes a specific version of the ESX host, compatible partner software and firmware components, and add-ons. When hosts deviate from the target specification, cluster remediation applies the desired state to each non-compliant host, with the Coordinator Manager running pre-checks to evaluate how each host is affected and whether additional steps are needed. Patches can be staged to ESX hosts before remediation begins, reducing the time hosts spend in maintenance mode during the remediation window. Remediation can also be initiated manually or scheduled as a regular task to run at a time convenient for operations teams, supporting consistent patch compliance over time. Firmware add-ons can be added, replaced, removed, upgraded, or downgraded as part of the image. The vSphere Automation REST API allows administrators to query effective global and cluster-specific remediation policies before initiating remediation, supporting a review-before-apply workflow that reduces risk during patching operations.
-VCF also provides tooling for managing remediation at scale. VCF PowerCLI supports parallel remediation with a configurable maximum number of concurrent remediations, allowing administrators to remediate multiple hosts simultaneously. Live Patching allows security updates to be applied to ESX hosts without requiring a host reboot. vCenter RDU upgrades perform automatic rollback if the upgrade fails, providing a safety net during update operations. Maintenance releases are scheduled, cumulative updates focused on platform stability and support, providing bug and security fixes, hardware enablement changes, driver updates, guest OS support, and backward-compatible new features with limited scope to minimize operational impact.
-For containerized workloads running on vSphere namespaces, VMware Kubernetes Service (VKS) extends vulnerability identification and remediation to the application layer. Harbor Registry, deployable as a standard package on VKS clusters, performs automated vulnerability scanning against container images using the Trivy vulnerability database, which can be configured to point to a custom or mirrored registry. Harbor also supports image signing to establish content trust, giving administrators a mechanism to identify images that have passed security review. Admission controls can be configured to restrict workload deployments to images sourced from a designated Harbor instance where scanning is enforced, helping constrain the image surface to scanned and trusted artifacts.
-VKS MachineHealthCheck provides automated remediation of unhealthy cluster nodes. The remediation.maxInFlight parameter controls how many concurrent node remediations may proceed simultaneously, and the triggerIf.unhealthyLessThanOrEqualTo threshold determines the condition under which remediation activates. The Kubernetes API surfaces a Remediating condition on VKS clusters, giving administrators direct visibility into the status of ongoing node remediation. DISA Security Technical Implementation Guides (STIGs) are available for both Supervisor and VKS cluster releases (VKrs), documenting known configuration weaknesses and providing step-by-step remediation guidance for hardening these deployments. The Kubernetes Security Response Committee tracks upstream Kubernetes vulnerabilities, assigns CVE identifiers, and publishes advisories through the kube-security-announce mailing list and the official Kubernetes CVE list; the committee's policy is to fully disclose vulnerabilities as soon as a user mitigation is available, with timeframes ranging from immediate to a few weeks depending on the complexity of the issue and vendor coordination requirements. Organizations running VKS can subscribe to receive these notifications and coordinate patch deployments accordingly.
-CI/CD pipelines deployed on the VCF consumption layer can incorporate Harness CI/CD with Security Testing Orchestration (STO). Harness STO integrates Wiz to perform pre-deployment vulnerability scanning across container image layers and automatically deduplicates findings, presenting each unique vulnerability, CVE, misconfiguration, or exposed secret as a single actionable item on the pipeline execution's vulnerabilities tab.</t>
+          <t>VCF provides integrated lifecycle management that addresses new threats and vulnerabilities on an ongoing basis through a structured release model, centralized update orchestration, proactive vulnerability detection, configuration drift monitoring, and automated node health remediation for containerized workloads.
+VCF follows a tiered release cadence consisting of major, minor, maintenance, and patch releases. Major and minor releases are fully synchronized across all VCF core components, following a unified consumption pattern that advances the entire platform to a new, consistent feature level. Maintenance releases are scheduled, cumulative updates focused on platform stability, providing bug and security fixes, hardware enablement changes, driver updates, guest OS support, and backward-compatible new features with limited scope to minimize operational impact. Patch releases provide time-sensitive fixes to security and catastrophic issues impacting business operations, and can be applied selectively to individual components without requiring synchronized updates across the full stack.
+VCF Operations orchestrates centralized lifecycle management for the entire VCF stack, including pre-update validation with health checks and compatibility verification, update bundle management with download and staging for both online and offline environments, and component interdependency management that respects dependencies between VCF components during updates. VCF Operations requires a precheck to succeed before scheduling upgrades, and requires acknowledgment of any errors or warnings in the precheck report before proceeding. The upgrade planner allows administrators to select any supported version for each VCF core component, including specific patch versions and VCF Bill of Materials versions. When connected to an online or offline depot, binaries for the target versions of each core component can be downloaded in preparation for upgrading or updating. VMware Kubernetes Service (VKS) cluster version upgrades are managed through this same VCF lifecycle management framework, providing a controlled path for remediating vulnerabilities in the Kubernetes control plane and node components. The VCF Automation Provider Management UI exposes a VKS cluster management interface that verifies cluster management functions and overall health status across all elements.
+For vCenter specifically, administrators can automate the installation of software updates to keep the system stable and protected, including automated checks for new updates and staging of updates through update policies that reduce waiting time. VCF Operations Marketplace displays the latest published version of each management pack by default and provides a version selector to view all available versions or choose a different version to download. VMware provides proactive notification when management packs are updated to maintain compatibility, emailing customers on older versions when a new update is released.
+VCF supports rollback capabilities for updates. vCenter RDU upgrades perform automatic rollback if the upgrade fails. VCF Operations HCX supports rollback using vSphere snapshots if an unexpected issue in a new version cannot be resolved in a timely manner. Live Patching capabilities allow security updates to be applied to ESX hosts without requiring a host reboot, reducing maintenance windows and accelerating the deployment of time-sensitive security fixes. For containerized workloads running on VKS, Kubernetes Deployments support rolling updates that allow workload operators to replace container images with patched versions while maintaining service availability; rolling update strategies limit the number of unavailable pods during an update, and Kubernetes tracks revision history to support rollback if a patched image introduces regressions.
+vSphere Lifecycle Manager (vLCM) manages the full software and firmware lifecycle for ESX hosts. vLCM images can have firmware add-ons added, replaced, removed, upgraded, or downgraded, enabling vendor-specific firmware and driver management alongside software updates. Administrators can initiate ESX host remediation manually or schedule recurring remediation tasks to run during defined maintenance windows, supporting a consistent patch deployment cadence. Build recommendations for vSAN and other components include all patches and driver updates for the current release, giving administrators a clear target for what constitutes the latest stable configuration. VCF supports Ensure Accessibility maintenance mode for vSAN storage clusters, using durability components to maintain data availability during updates.
+At the Kubernetes layer, MachineHealthCheck provides an automated remediation mechanism for VKS workload clusters that is equivalent to scheduled host remediation at the infrastructure layer. MachineHealthCheck monitors node health and automatically replaces nodes that fall outside defined health thresholds, with configurable parameters including max-unhealthy (which prevents mass remediation when the number of degraded nodes exceeds a specified absolute count or percentage), node-startup-timeout, and unhealthy-conditions to define what constitutes a degraded node. In ClusterClass-based VKS clusters, the machineHealthCheck.enabled parameter activates this capability. The VCF CLI provides vcf cluster machinehealthcheck node get and vcf cluster machinehealthcheck control-plane get commands to inspect the current health status of worker and control plane nodes, and MachineHealthCheck specifications can be updated via kubectl patch with JSON merge patch for ongoing policy adjustments.
+VCF Operations Diagnostics automatically detects known issues and critical vulnerabilities within the VCF software stack, providing descriptions, root cause insights, and actionable remediation steps. Broadcom publishes security advisories for critical known vulnerabilities with step-by-step remediation instructions. VCF documentation explicitly recommends keeping infrastructure up to date by running current component versions as part of operations best practices, noting that running outdated components that are too far behind the latest version can cause support problems, upgrade problems, and higher operating costs, and that fixes for known issues are often only available in later versions. The vSphere documentation also recommends that organizations run vulnerability scans against their systems and applications on a defined schedule and document the frequency of scanning as part of ongoing vulnerability management. This guidance extends to individual platform services, with specific recommendations to run the latest version of VCF Operations for Networks for security fixes for all known vulnerabilities, and to upgrade VCF Operations HCX when updated releases become available to have the most recent fixes and security patches. At the container image level, the Harbor registry integrated with the VKS Supervisor cluster provides vulnerability scanning, content trust, and policy-based replication to support the security and integrity of containerized workloads. Kubernetes operational guidance recommends that container images be regularly scanned during creation and in deployment and that known vulnerable software be patched as part of an ongoing practice. VKS Cluster Management Policy Insights surface compliance findings with direct links to the affected cluster, project, and policy to streamline the remediation workflow. VCF Supervisor documentation also recommends creating VM images with the latest patches and required security settings for production environments.
+VCF uses Configuration Profiles and Image-Based Lifecycle Management to periodically assess host configuration against a desired state. VCF Operations provides unified configuration management that enables scheduled drift detection for vCenter and cluster objects to proactively detect configuration deviations from the desired state. When drift is detected, the system alerts administrators. VCF Operations compliance management detects violations, highlights risk areas, and provides actionable remediation recommendations. Depending on the severity of non-compliance, administrators can configure automated remediation actions to bring objects back into compliance.
+Security and operations teams can use the management interface, CLI tools, and APIs to automate security posture assessment and remediation workflows, including integration with third-party monitoring and SIEM tools for continuous vulnerability awareness.</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -1353,14 +1353,10 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) contributes to vulnerability remediation by providing network-level threat detection and structured response mechanisms that identify, track, and contain exploitation attempts across protected workloads.
-vDefend Distributed IDS/IPS continuously monitors east-west traffic for known vulnerability exploits using signature-based detection. In 9.1, IDS/IPS event monitoring displays CVE reference information and Common Vulnerability Scoring System (CVSS) scores for vulnerabilities targeted by detected exploits, enabling security teams to correlate detected traffic with the specific vulnerability being exploited and prioritize response based on severity. Administrators can search the signature database by CVE ID, making it possible to verify detection coverage for a newly disclosed vulnerability and identify which IDS signatures apply before system signature updates are deployed.
-Custom signatures extend detection to application-specific and zero-day threats. vDefend IDS/IPS supports custom signatures that can be exported, edited, and re-uploaded to the system. Before publication, the system validates custom signatures and identifies those tagged as Invalid or Warning, preventing deployment of malformed detection rules. Custom IDS/IPS profiles can include custom signatures with assigned severity levels. Administrators can exempt known false positives from inspection when internal applications use protocols that resemble attacks but are not malicious, reducing alert noise without degrading detection coverage.
-The Security Services Platform (SSP) provides a structured remediation workflow for detected security events. When vDefend IDS/IPS, Malware Prevention, or Network Detection and Response (NDR) identifies a threat, administrators can apply remediation actions that automatically create Distributed Firewall rules or IDS/IPS policies to block the attack vector. Two remediation strategies are available: Targeted remediation creates surgically scoped rules that address the specific threat with potentially lower effectiveness, while Comprehensive remediation creates broader policies that protect against similar attack patterns with potentially lower safety margins. The Response and Remediation feature in SSP performs automated creation of policy based on user role and permissions. Intelligent Assist automates selection between these strategies and handles creation of the necessary groups, security profiles, rules, and policies. For Malware events, Targeted remediation enables all IDS signatures for the affected workload, and Comprehensive remediation creates Distributed Firewall policies. Remediations detected on the Gateway Firewall are applied on the Distributed Firewall, extending protection to east-west traffic. Applied remediation policies can be verified in NSX Manager at Security &gt; IDS/IPS &amp; Malware Prevention &gt; Emergency Threat Rules.
-SSP manages IDS policy lifecycle by extracting all active policies, rules, and security profiles to support multiple concurrent remediations, identify stale policies for cleanup, and suggest additions that avoid conflicts with existing rules. The Security Services Platform also identifies vulnerable workloads that could be exploited for lateral movement, helping administrators understand exposure before a threat can propagate across segments.
-Remediations are not automatically applied. Administrators must review and manually apply suggested remediations through the NSX Manager UI, and objects generated during remediation that encounter errors require manual cleanup. This manual review step gives security teams control over which containment actions are deployed.
-The Malware Prevention Service can deny access to suspicious files or delete files confirmed as malicious directly on the protected endpoint, providing a remediation path that extends beyond network policy to the file level.
-These capabilities complement VCF's infrastructure-level vulnerability and patch management by providing a network security layer that can detect active exploitation and apply containment actions while patches are being evaluated and deployed.</t>
+          <t>VMware vDefend (VMware vDefend) contributes to continuous vulnerability remediation by providing network-level threat detection and automated remediation capabilities that address known and emerging threats across protected workloads.
+vDefend Distributed IDS/IPS detects known attack signatures across east-west traffic within the data center. The IDS/IPS engine supports CVE-based signature searches, allowing administrators to identify and enable signatures that address specific newly disclosed vulnerabilities. Knowledge-based signatures cover attacks that are already known and documented; for custom applications and zero-day scenarios, administrators can author custom IDS/IPS signatures that extend detection beyond the standard signature set. This combination of vendor-maintained and custom signatures allows organizations to respond to new vulnerability disclosures by deploying detection rules that identify exploitation attempts before patches can be applied.
+Security Services Platform's Security Assessment generates Security Segmentation Reports and Blast Radius Reports that identify at-risk workloads, communication chains, and network flows, providing the visibility needed to plan and prioritize remediation activities. Security Services Platform identifies vulnerable workloads that could be exploited for lateral movement and evaluates whether workloads are protected by environment-specific segmentation policies such as Dev, Prod, and Test. Security Services Platform provides remediation workflows that translate detected threats into actionable security policy changes. When IDS/IPS or Gateway Firewall events identify malicious activity, administrators can apply remediation actions that create or modify Distributed Firewall rules and IDS/IPS policies to block the identified attack vectors. Two remediation strategies are available: Targeted remediations create narrow, precise policies that address the specific threat with minimal impact to existing workloads, while Comprehensive remediations create broader policies that defend against similar attack patterns. Intelligent Assist automates the selection between these strategies and handles the creation of groups, security profiles, rules, and policies needed to implement the remediation. The Response and Remediation feature performs automated policy creation based on user role and permissions.
+Security Services Platform supports ongoing security posture management through asset inventory classification and traffic monitoring. Security Intelligence continuously monitors for new flows between environments and alerts administrators to unauthorized or unexpected traffic, enabling ongoing policy adjustments as workload communication patterns change. Security Intelligence generates microsegmentation recommendations by analyzing inventory assets to create or update vDefend sections. The Security Segmentation Score Breakdown report details protection coverage across environment pairs and highlights pairs that lack inter-environment policies, making coverage gaps easier to identify and address.</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -1380,11 +1376,14 @@
       </c>
       <c r="L8" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) contributes to the vulnerability remediation process primarily through its software update mechanisms and compliance tracking features. DSM does not provide vulnerability scanning or external CVE tracking; those functions require organizational processes and tools outside the platform.
-DSM supports software remediation through update bundles that apply patches to DSM appliances and managed database versions. The DSM controller manages component dependencies through status monitoring and automated remediation, helping maintain a consistent update baseline across the environment. Database engines, including PostgreSQL and MySQL, can be upgraded to new minor and major versions through the DSM interface; upgrade operations during the maintenance window may include CVE fixes, bug fixes, and performance improvements, allowing operators to remediate known vulnerabilities by updating to patched releases.
-To support issue identification, DSM surfaces database alerts with mitigation suggestions so that operators can resolve operational issues without disrupting database services. Operators should verify VM status and infrastructure health when resolving alerts to identify underlying causes. The platform can generate and download log bundles that aggregate relevant logs from database VMs to support faster diagnosis when a service faces a problem. Operators can also review active VMware vCenter infrastructure alarms through DSM troubleshooting guidance and resolve the underlying problems causing those alarms.
-Data service policies in DSM include a compliance tab that tracks whether deployed databases conform to the policy. When a data service policy is deleted, the associated services are marked as non-compliant, providing visibility into configuration drift. These policies can be enforced across different tenants, supporting consistent configuration standards across the environment.
-DSM handles the patching and software update aspects of vulnerability remediation within its own scope and provides monitoring and compliance visibility. The broader requirements of the control, including external vulnerability scanning to identify CVEs in database software, a centralized vulnerability tracking system for prioritization and assignment, and defined organizational remediation timelines and escalation procedures, must be addressed through organizational processes and tools that operate alongside DSM.</t>
+          <t>VMware Data Services Manager (DSM) supports continuous vulnerability remediation through software update management, patch scheduling controls, and infrastructure health monitoring, though the broader organizational processes for vulnerability identification, tracking, and lifecycle management fall outside DSM's direct scope.
+DSM provides a Maintenance Policy that controls the scheduling and duration of software updates to the DSM plug-in. Administrators configure this policy from the vSphere Client under "Managing Data Services Manager Plug-in Software Updates," setting the duration window for applying software updates. Upgrade operations performed during the maintenance window may include CVE fixes, bug fixes, and performance improvements, making the maintenance window the primary vehicle for applying security-relevant patches to the database platform. The documentation also recommends always using database versions with the latest DSM components to maintain optimal performance and security.
+Administrators who deploy DSM through VCF Automation can configure maintenance windows with greater granularity. The Monthly Occurrences setting allows selection of a specific day and one or more occurrences of that day within the month; if no specific occurrence is selected, the maintenance window runs on a weekly cadence by default.
+For SQL Server workloads, DSM introduces per-engine maintenance windows for operating system patching, configurable by SQL Server administrators within the DSM UI. The documentation recommends that SQL Server instances follow the Cumulative Update (CU) branch, which packages functional, performance, and security updates for each major version, keeping the data service current with vendor-issued fixes.
+The DSM controller monitors component and feature dependencies continuously, performing automated remediation when dependency status violations are detected. This mechanism also manages compatibility requirements when upgrading DSM within a VCF environment.
+For ongoing health visibility, DSM generates alerts across multiple categories that surface conditions requiring remediation attention. Administrators can configure alert threshold values for CPU Health, Data Disk Health, System Disk Health, and Max Connections parameters, with separate thresholds for warning and critical severity. Infrastructure compliance is monitored through alerts such as INFRASTRUCTURE_POLICY_VC_ALARMS, which fires when active infrastructure resource alarms are detected in vCenter. When alerts trigger, DSM provides guidance to help administrators identify underlying causes; administrators are advised to verify active vCenter alarms before performing maintenance or scale operations and to resolve active CPU or memory alarms on ESX hosts before scaling database instances.
+DSM integrates with VCF Operations, which automatically discovers and monitors PostgreSQL and MySQL database clusters in the Ready state. When configured, VCF Operations displays performance data at three levels: cluster-level for overall health, node-level for infrastructure resource utilization, and database-level for KPIs such as Active Connections, Commits, Rollbacks, and Deadlocks. This integration provides operational visibility that supports remediation workflows.
+Continuous vulnerability remediation also depends on activities outside DSM's direct scope. Identifying new CVEs and vulnerabilities in the database engines that DSM manages (PostgreSQL, MySQL, SQL Server, MinIO), evaluating their applicability to a specific deployment, prioritizing remediation, and tracking remediation status all require organizational vulnerability management processes and tools. Organizations should integrate DSM update notifications with their broader patch management workflows and maintain a vulnerability management program covering both the DSM management plane and the database engines it provisions.</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr">
@@ -1541,17 +1540,15 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>VCF provides several capabilities that contribute to maintaining network architecture diagrams and data flow documentation, though the organizational process of creating, maintaining, reviewing, and governing formal diagram artifacts remains a customer responsibility.
-VCF Operations for Networks includes an end-to-end interactive network map that displays a detailed model of both physical and virtual devices in the environment, including physical switches, physical firewalls, routers, load balancers, transport nodes, and NSX virtual entities. The Network Map Summary presents a view of the data center that includes these entities along with an alert chart showing alert status across the inventory. Users can scope the view to focus on specific portions of the network. Because the map updates based on data collected from configured sources, it reflects the discovered state of the monitored infrastructure rather than a static diagram, providing a foundation for understanding the current network architecture and validating formal network diagrams.
-NSX network connectivity workflows include a built-in topology visualization that correlates user configuration inputs with the resulting network topology, helping administrators understand the architecture before committing changes and reducing the risk of misconfiguration by providing a view of the entire setup. The NSX Manager Network Topology feature allows users to view network connectivity by zooming in to see details about logical entities and their logical paths, along with the services configured on those entities. The NSX Main Dashboard displays the topology of a selected object and how it connects to elements in the network, with a view of related alerts. The vSphere Client provides topology views of compute, storage, and network relationships, displaying logical and physical components such as segments, transport zones, and resource dependencies. The vSphere Distributed Switch topology diagram specifically shows information about the physical adapter connecting virtual adapters to the external network, with filters that default to displaying up to 32 port groups, 32 hosts, and 1,024 virtual machines.
-The vSphere Network Inventory Dashboard provides a dedicated topology view of the vSphere network inventory, including information related to vSphere environments, vCenter instances, data centers, distributed vSwitches, distributed port groups, virtual machines, and associated properties and metrics. The Network Configuration Dashboard displays key configuration information including bar charts focused on critical security settings for vSphere distributed switches, providing visibility into the security-relevant configuration state of the network infrastructure.
-For data flow analysis, VCF Operations for Networks collects flow data defined by 5-tuple values: source IP address, source port, destination IP address, destination port, and protocol. At the virtual switch level, vSphere Distributed Switches also support NetFlow export, configured with an Observation Domain ID that identifies the switch within the flow collection infrastructure, so flow data can be sent to external collectors for analysis alongside data collected by VCF Operations for Networks. The Access Flow Insight page in Network Operations allows analysis of all flows available in the environment, where each dot in the graph represents multiple flows and users can drill into individual flow details. The Custom Analysis section within Flow Insight provides two-dimensional visualization of flow data on user-selected dimensions to identify outliers in network traffic patterns. Flow metrics display traffic flow data collected from flow-enabled data sources, aggregated to show metrics such as total bytes and traffic rate. Flow analytics can also be run to understand bandwidth and packet rates.
-VCF Operations for Networks supports flow-based application discovery, accessible by navigating to Infrastructure Operations, then Analyze, and selecting the Flows tab. This allows administrators to discover applications by analyzing traffic patterns and network flows in the environment, with the ability to modify the scope, naming preference, and duration of the discovery process. The application topology map displays traffic flows between application tiers, internet endpoints, shared services, and other applications, showing how data moves between workload groups. The map shows tier overviews, lists of members (including VMs, Kubernetes services, and physical IPs), flows between tiers, and the physical IPs and shared services that applications depend on.
-VCF Operations for Networks also provides a Security Planning capability that analyzes flows and displays traffic flow patterns and micro-segmentation views. This feature supports security assessment by making it possible to see how traffic moves through the environment, which is directly relevant to documenting sensitive or regulated data flows and assessing the security posture of the network architecture. The platform also provides planning and recommendations for implementing micro-segmentation security, and the micro-segmentation flow analysis interface allows filtering by protection status to view allowed and blocked flows.
-VCF Operations for Networks includes a PCI Compliance page that presents a network flow diagram showing data flow paths, firewall placements, connections, and other details associated with the network. This built-in visualization is oriented toward compliance assessment and can supplement organizational network architecture documentation.
-For multi-site environments, VCF Operations for Networks supports flow visualization for SDDC-to-SDDC communication through VMware Transit Connect via the VMware Managed Transit Gateway (VTGW), providing visibility into cross-data-center network flows. The Streaming Databus supports cross-data center network flow analysis by grouping query results by source data center, destination data center, and flow type.
-Firewall rules can be exported to CSV files using the run_fw_rule_export CLI command, producing files that can be transferred via secure copy for integration into formal documentation. VCF also documents its own internal network ports and protocols at ports.broadcom.com, which provides reference material for documenting the platform's own communication paths.
-While VCF provides tools for network topology visualization, flow analysis, application discovery, and security-oriented network views, the control requires a formal organizational process for maintaining network architecture diagrams and data flow diagrams that are kept current and contain sufficient detail for security assessment. VCF's capabilities provide the underlying data and visualization tools that inform these diagrams, but the creation, review, approval, and maintenance lifecycle of the formal documentation is an organizational responsibility.</t>
+          <t>VCF provides multiple layers of access control list (ACL) mechanisms and network traffic restriction capabilities that contribute to data flow enforcement, though full ACL governance across physical and virtual infrastructure requires organizational processes and may benefit from VMware vDefend for advanced stateful firewall rule sets.
+At the network infrastructure layer, VCF uses vSphere Distributed Switches to centrally manage VLAN assignments, port group policies, and traffic shaping rules across all hosts in a workload domain. Distributed switches support traffic shaping policies that limit the bandwidth of incoming traffic, helping restrict which traffic types and volumes can traverse each network segment. Distributed port groups and uplink port groups also support a Traffic Filtering and Marking Policy, where per-rule actions can be set to Allow, Drop, or Tag traffic based on defined match criteria, providing rule-based traffic enforcement at the virtual switch level. Traffic segmentation is built into VCF's architecture: management, vMotion, vSAN, and NFS traffic each run on dedicated VLANs and VMkernel ports, and the vMotion network must be distinct from the vSAN network. This separation restricts which traffic types can traverse each segment by design. Private VLANs (PVLANs) provide additional Layer 2 isolation within a single VLAN through virtual network segmentation on distributed virtual switches, limiting communication between VMs even on the same segment. Distributed switches also support VLAN-based SPAN (VSPAN) for virtual distributed port mirroring, which aids in monitoring and validating traffic flows. At the ESX host level, a built-in firewall operates on a deny-by-default basis, closing all ports except those an administrator explicitly designates as authorized, giving each host an independent network access control point.
+NSX extends these capabilities with software-defined networking constructs including segments, Tier-0 and Tier-1 gateways, and Virtual Private Clouds (VPCs). NSX Tier-0 gateways can be configured with linked Tier-1 gateways to create multi-tier topologies, enabling route-based traffic restrictions between network tiers. NSX edge gateways handle north-south routing. With vDefend deployed, North-South Firewall Rules on these gateways provide traffic protection, and an NSX project's default gateway firewall and distributed firewall rules (a vDefend capability) govern the default behavior of north-south and east-west traffic for workloads in that project. VPCs are self-contained virtual network environments that provide an abstraction layer for setting up isolated virtual private cloud networks with their own topology, IP address management, and permission models, allocatable to discrete projects in a self-service consumption model. NSX Manager enforces approved authorizations for controlling the flow of management information within network devices based on information flow control policies.
+NSX also provides data flow enforcement at the load balancer tier through its Access List Control (ALC) feature. The NSX load balancer compares all traffic flowing through it with ACL statements, which either drop or allow the traffic based on configured rules. This gives administrators another enforcement point for restricting network traffic to only what is authorized.
+At the Consumption layer, VMware Kubernetes Service (VKS) and the Supervisor extend ACL enforcement to containerized workloads through Kubernetes NetworkPolicy resources, which function as Layer 3/4 ACLs for pod-level traffic. NetworkPolicy objects specify allowed ingress and egress traffic by pod selector, namespace selector, IP block, port, and protocol; pods not selected by any NetworkPolicy receive no restriction by default, making explicit policy deployment necessary to enforce a default-deny posture across a cluster. VKS clusters run Antrea as the default CNI plugin, which implements NetworkPolicy enforcement through the AntreaPolicy feature gate and provides per-policy and per-rule packet and byte count statistics through the NetworkPolicyStats capability, giving administrators visibility into which policies are actively restricting traffic. For VKS clusters using NSX VPC networking, NSX-backed network policies apply distributed ACLs at the hypervisor level, extending enforcement beyond the CNI layer. The ovn-kubernetes Transparent network mode similarly supports distributed ACLs applied via Kubernetes NetworkPolicy resources. For Layer 7 traffic control within VKS clusters, the Istio service mesh standard package provides a pluggable policy layer and configuration API supporting access controls, rate limits, and quotas based on workload identity; when deployed in ambient mode with strict mutual TLS, all service-to-service traffic within the mesh is subject to authentication before authorization checks apply, restricting lateral movement to explicitly permitted paths.
+For file-level and storage data flow isolation, the Supervisor uses ACLs to isolate file share access within supervisor namespaces, restricting data access between workloads running in different namespaces. vSAN file services support managing ACLs on SMB shares using the MMC tool, giving administrators granular control over which users and systems can access shared storage resources. Administrators should be aware that ACL-based file share isolation in the Supervisor carries a risk of IP spoofing, which should be addressed through complementary network controls when deploying file shares in multi-tenant environments. Argo CD deployments on the Supervisor implement network segmentation and firewall rules to control communication between Argo CD components, following the principle of restricting inter-component traffic to only what each component requires. The Harbor container registry standard package enforces role-based access control over artifact access, complementing network-layer ACLs with image-level access restrictions.
+For object-level access control, VCF Automation maintains an ACL table that defines which users can access specific defined entities. System administrators with the Manage General ACL right can create, modify, and remove ACL entries through the accessControls API. Those with the View General ACL right can audit ACL assignments on specific entities. Access to runtime defined entities is controlled through rights bundles and ACL entries. This ACL mechanism works alongside role-based access controls so that rights determine what actions a user can perform while ACLs determine which objects those actions apply to.
+VCF Operations for Networks supports ACL visibility through its network assurance and verification capabilities, which allow administrators to validate that ACL configurations are applied as intended across the managed environment. This includes the ability to verify ACL configurations on supported physical network equipment such as Cisco ASR routers, helping validate that physical and virtual network access controls are consistent.
+For workload-level traffic enforcement with stateful firewall rules, microsegmentation, and deep packet inspection, VMware vDefend and Gateway Firewall extend VCF's networking foundation with fine-grained Layer 2-7 policy enforcement. Organizations that require ACL governance beyond what VCF provides natively should establish processes for ACL review cycles, change management for firewall rules, and regular validation of both physical and virtual network access controls.</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -1561,11 +1558,10 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend's Security Intelligence capability, delivered through the Security Services Platform (SSP), provides live network traffic flow visualization and security posture mapping that directly support the creation and maintenance of network architecture diagrams and data flow documentation. While maintaining formal network diagrams is an organizational responsibility, Security Intelligence generates interactive visualizations of network traffic patterns, security group relationships, and Distributed Firewall (DFW) rule coverage that serve as authoritative inputs to those diagrams.
-Security Intelligence collects and displays network flow data through a visualization canvas covering groups, computes, destination ports, and Layer 7 application IDs. The visualization displays network traffic flows with color-coded indicators: red-hued dashed lines for unprotected flows, blue-hued solid lines for blocked flows, and green-hued solid lines for allowed flows. The Flow Details dialog shows completed network flows and the firewall rules in effect associated with each flow, linking observed traffic patterns to the policies governing them. Flow data includes the groups flows belong to, services used, Layer 7 application ID, and FQDN information. Network flow data is analyzed within a 15-minute window for near-real-time security status, and administrators can select a time period parameter to examine historical traffic flow data for architecture documentation.
-Network traffic flows displayed in Security Intelligence are based on DFW rules in effect and observed traffic during the selected period, covering all traffic matching stateful Layer 4 DFW rules using IPv4 or IPv6. This directly supports the control's requirement that architecture diagrams reflect the current network environment and document how traffic flows through it. The Flow Insights Dashboard categorizes network objects into Rules, Groups, Computes, Destination Ports, and Layer 7 Application IDs, providing a structured multi-dimensional view of the environment's traffic architecture. Security Intelligence also monitors network flows between application pairs and tracks Policy Protection Status to indicate which application communication paths are being monitored.
-Security Intelligence generates DFW security policy recommendations for application and environment categories based on analysis of traffic flows over a specified time period. These recommendations, grounded in observed traffic patterns, provide data-driven support for documenting how data flows through the environment and what security controls apply to those flows.
-Network Detection and Response (NDR) extends this visibility by collecting and presenting detection events representing security-relevant activity in the network, helping security analysts understand threat patterns and the paths through which activity traverses the environment.</t>
+          <t>VMware vDefend (DFW) and Gateway Firewall enable network-level policy enforcement that restricts east-west and north-south connections, including outbound transfers to unauthorized or geographically prohibited destinations. Gateway Firewall rules can deny all inter-project communication except for infrastructure protocols such as DHCP, DNS, NTP, and ICMP, providing a mechanism to prevent sensitive workloads from transferring data to unauthorized external destinations. URL filtering and TLS inspection extend these controls by enabling policy-based blocking or inspection of outbound connections based on category, reputation, or destination.
+Security Intelligence, part of the Security Services Platform (SSP), provides flow visibility and audit capabilities that support compliance documentation for data transfer governance. The Export All Flows capability exports network flow data to a CSV file for analysis and compliance documentation. Security Intelligence also exports user-defined label assignments, which associate compute entities with classification tags, to CSV, supporting audit documentation of which workloads are subject to data handling policies. Policy recommendations generated by Security Intelligence can be exported in JSON or CSV format for further analysis. SSP stores processed, enriched, and correlated flow data, with aggregated flow records updated every six hours.
+Network Detection and Response (NDR) anonymizes sensitive customer information when sharing data to cloud services, providing a privacy control over what platform telemetry leaves the environment. SSP regions can also be associated with security and network policies to control policy scope across multiple geographic locations, supporting governance of which security rules apply where.
+vDefend operates at the network layer and does not enforce data residency, contractual, or legal compliance obligations directly. Those obligations require complementary governance frameworks and organizational processes that extend beyond network-level enforcement.</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
@@ -1604,14 +1600,9 @@
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) contributes to this control through application-layer mechanisms that restrict which clients receive application data and how sensitive information is handled within Avi's own logs and analytics.
-At the application access control layer, Avi's DataScript scripting engine supports credential-based authorization enforcement at the proxy boundary. DataScript can check incoming client credentials or user IDs against string groups configured with key-value pair whitelists and redirect unauthenticated users to a login page, enforcing need-to-know access at the point where requests enter the Avi Service Engine. DataScript also supports blocklist-based access control, checking client IP addresses against named IP groups and terminating connections from listed addresses.
-Avi's tenant isolation model provides data plane separation between tenants. Tenants configured in Tenant Context receive both control plane and data plane isolation, scoping which workloads and data are accessible within each tenant boundary. Tenants in Provider Context receive control plane isolation only, which is a relevant consideration when planning multi-tenant deployments that carry sensitive application traffic.
-Avi's controller RBAC limits administrative disclosure by restricting which users and teams can read configuration and operational data. Extended granular RBAC uses markers to restrict user permissions to specific resources based on label matching. Label-based permissions for cloud objects are enforced through the restrict_cloud_read_access field in controller properties, scoping which users can read cloud configuration data.
-Avi supports OAuth and OIDC for client authentication, allowing applications to use delegated access without requiring users to share their credentials directly with third-party applications. The identity provider issues tokens to authorized applications, limiting credential exposure at the application layer.
-Avi's Analytics Profile supports a sensitive log profile that controls how sensitive data appears in client-facing logs. Operators can configure this profile to mask or remove sensitive HTTP headers, including cookies and authorization tokens, from application log records, reducing the risk of exposing user credentials and identity data through log access. Avi also supports masking of personally identifiable information (PII) in application logs by removing or masking matched fields in URI and header content.
-Avi's Central Licensing service collects only the data outlined in the Privacy document, with no additional data collected by or for the licensing service, which limits administrative data exposure through that channel.
-Organizational data classification processes, data handling policies, and the broader platform-level access controls provided by VCF are also required to fully satisfy this control, which is why coverage is Contributes rather than Meets.</t>
+          <t>VMware Avi Load Balancer (Avi) provides application-layer transfer authorization mechanisms that verify client and service credentials before forwarding data to backend resources. For application traffic, Avi's OAuth and OpenID Connect (OIDC) integration supports the Authorization Code Grant Flow, through which the authorization server authenticates the resource owner, evaluates the client's access request, and issues access tokens only after authorization is confirmed. Clients must present a valid access token to the Avi virtual service; the Authorization Endpoint handles user-agent redirection to the authorization server, and the token endpoint validates the authorization code and authenticates the client using the client_id and client_secret before tokens are issued. This flow verifies that the requesting party holds the required authorization before any data transfer to the backend resource server is permitted.
+For more granular application-layer authorization, Avi supports Authorization Policies and DataScript within OAuth/OIDC flows. These allow administrators to define rules that evaluate token claims and request attributes, granting or denying forwarding based on whether the client meets the configured authorization criteria. This provides control over which clients and services have the write permissions or privileges required to access specific application endpoints.
+For administrative operations on the Controller, Avi's role-based access control enforces object-level write permissions. Write access to objects such as Virtual Services, Application Profiles, SSL/TLS Certificates, and Certificate Management Profiles is granted at the role and tenant level, so that only users with the requisite permissions can modify transfer-related configurations. TACACS+ integration supports centralized authorization by delivering attribute-value pairs from the TACACS+ server that map users to specific roles and tenants. The PASS_ADD and PASS_REPL statuses grant authorization to successfully authenticated users, while the FAIL status rejects those without the required attributes. Cisco ISE can be configured as a remote authentication and authorization backend for Avi, including with external identity sources such as OpenLDAP, providing centralized identity management for Avi administrative access. In Avi Load Balancer SaaS deployments, authorization tokens can be generated for service account authentication to the SaaS Controller.</t>
         </is>
       </c>
     </row>
@@ -1748,29 +1739,25 @@
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>VCF implements cryptographic protections across its component stack using publicly standardized, validated cryptographic modules and algorithms.
-Multiple VCF components rely on cryptographic modules validated through the NIST Cryptographic Module Validation Program (CMVP) to FIPS 140-2 and FIPS 140-3 standards. NSX is configured to use FIPS 140-3 validated cryptographic modules by default, and NSX Manager uses FIPS 140 approved algorithms for authentication to its cryptographic module. Specific NSX validated modules include IKE with Rambus Safezone 2.0 (Certificate #4898), VMware OpenSSL 3.0.9 (Certificate #4861), VMware BouncyCastle 2.0.0 (Certificate #4986), and VMware BoringCrypto 6.0 (Certificate #4694). VCF Automation uses the BouncyCastle FIPS 2.0.0 cryptographic module, which holds FIPS 140-3 Certificate #4743. VCF Operations for Networks uses BC-FJA (Bouncy Castle FIPS Java API) version 2.0.0 with FIPS 140-2 Certificate #37009 as its validated cryptographic module. This consistent use of FIPS-validated modules across the platform means that organizations deploying VCF in regulated environments can rely on cryptographic implementations that have undergone independent validation against well-known public standards. The VMware Kubernetes Service (VKS) consumption layer also supports FIPS mode: VKS ClusterClass configurations include a fips.enabled variable that, when set, restricts cryptographic operations on cluster nodes to approved algorithm implementations. FIPS-enabled Kubernetes release images, identified by a -fips suffix in the release reference name, are available for organizations that require FIPS-validated cryptography across their containerized workloads.
-At the protocol and algorithm level, VCF enforces modern cryptographic standards throughout. Starting in vSphere 9.0, all TLS profiles are FIPS compliant; the COMPATIBLE profile supports modern TLS cipher suites with standardized elliptic curves. Monitoring infrastructure such as Telegraf enforces a modern TLS minimum version for secure communication. The NSX L2 VPN FIPS compliance suite uses AES-GCM encryption with Perfect Forward Secrecy and Diffie-Hellman Group 20. NSX also supports ECDSA (Elliptic Curve Digital Signature Algorithm) encryption for environments with high-assurance cryptographic requirements. VCF Operations for Networks supports several encryption algorithms and ciphers for its data sources. VCF Operations provides a FIPS Security Mode that, when enabled, applies additional algorithm and cipher prerequisites across the management domain. All system management network communications are encrypted by default using standardized cipher suites. At the VKS layer, Kubernetes control plane components expose parameters for restricting permitted TLS configurations: the kube-apiserver --tls-cipher-suites parameter, the kubelet tlsCipherSuites configuration field, and the equivalent parameter on the kube-scheduler each restrict the set of permitted cipher suites, allowing administrators to exclude deprecated or weak algorithms. The kubelet tlsMinVersion field and the --tls-min-version parameter on the kube-apiserver enforce a minimum TLS protocol version floor for inbound connections. The Antrea networking component and vSphere Cloud Provider Interface on VKS clusters also support configurable TLS cipher suites for component-to-component communication. Kubernetes hardening guidance identifies specific preferred cipher suites and calls out cipher suite configuration on the kube-scheduler as a required hardening step. VKS clusters support the Istio service mesh package, which provides mutual TLS between workloads within the mesh; the meshMTLS.minProtocolVersion setting controls the minimum protocol version for inter-service communication, defaulting to TLS 1.2 with support for configuring TLS 1.3.
-Data-in-transit protections using TLS have customizable PKI keypair and certificate options. These range from fully automated within VCF to semi-automated using certificates from enterprise PKI infrastructure or fully custom certificates installed manually. Automated certificate issuance is supported with Microsoft Active Directory Certificate Services. Trust establishment uses standard PKI management with multiple certificate options including Root CA certificates, CSR-based certificates, and direct certificate uploads. VCF Operations provides centralized certificate lifecycle management for all VCF components, enabling automated certificate renewal, monitoring, and replacement across the infrastructure. Organizations should be aware that if self-signed certificates and private keys are generated using OpenSSL, those certificates and private keys are not FIPS-compatible. Environments operating under FIPS requirements should use certificate authorities and key generation methods that produce FIPS-compliant artifacts. For FIPS environments, certificates should use key sizes of 2048 or 3072 bits; key sizes greater than 3072 bits have not been tested with FIPS. At the VKS layer, the cert-manager package manages the lifecycle of certificates issued to workloads and ingress endpoints. VKS clusters maintain TLS certificates for component-to-component communication across their control and data planes. The Contour ingress package supports minimum TLS version configuration through the tls.minimum-protocol-version parameter. Harbor, when deployed as a Supervisor Service, accepts custom TLS certificate configuration through the tlsCertificate.tls.crt and tlsCertificate.tls.key fields, allowing organizations to supply certificates from their enterprise certificate authority rather than relying on self-signed certificates. The Supervisor secret injection agent automatically configures mutual TLS for communication with the vault-agent-injector service using auto-generated certificates.
-Data-at-rest encryption uses vSAN cluster-based encryption or VM Encryption on non-vSAN storage. vSAN encryption uses AES-NI CPU offloading for efficient processing, and VMware ESX hosts encrypt vSAN disk data using the industry standard AES-256 XTS mode. Encryption keys are managed through KMIP 1.1-compatible external Key Management Servers (KMS) or vSphere Native Key Provider (NKP), which is included in all vSphere editions and does not require an external key server. VCF implements a three-element domain of trust comprising the key provider, VMware vCenter, and vSAN hosts. Key Encryption Keys (KEK) wrap Disk Encryption Keys (DEK) for secure key management; ESX hosts use the KEK to encrypt their internal keys and store only the encrypted internal keys on disk, not the KEK itself.
-VCF Standard Key Providers have key wrapping capabilities that let organizations store a single wrapping key in their KMS, protecting multiple Key Encryption Keys within the VCF environment. This creates a three-tier key hierarchy: the Data Encryption Key encrypts object data, the Key Encryption Key protects the DEK, and the wrapping key protects the KEK. This approach reduces the number of keys stored in external KMS systems while maintaining cryptographic separation. Key wrapping includes automatic key rotation with configurable intervals from 30 days to 10 years.
-With key persistence enabled, ESX hosts can persist encryption keys in the Trusted Platform Module (TPM) across reboots, allowing encryption operations to continue when the key server is unavailable. Each ESX host obtains the encryption keys initially and retains them in its key cache; if the ESX host has a TPM, the encryption keys are persisted in the TPM across reboots. Key persistence can be enabled using the esxcli system security keypersistence enable command.
-VCF supports guest-level security features including virtual Trusted Platform Module (vTPM) 2.0 for VMs. This enables in-guest encryption capabilities such as Windows BitLocker, Linux disk encryption, and other operating system-native security features. Secure Boot provides UEFI verification to help ensure only signed and trusted code runs during the VM boot process. These features work independently of or in combination with infrastructure-level encryption, allowing organizations to implement defense-in-depth strategies.
-vSAN offers Data-in-Transit (DIT) encryption as a cluster-wide setting that encrypts all data and metadata traffic as it transits across hosts. For vSAN Original Storage Architecture (OSA), data-at-rest encryption occurs at the Local Object Manager (LSOM) layer on the target host, making DIT encryption strongly recommended to restrict network-level interception. For vSAN Express Storage Architecture (ESA) in HCI mode, data is encrypted at the VM host before network transmission, making DIT encryption optional based on compliance requirements and risk tolerance. DIT encryption operates without requiring external key management servers and provides independent key rotation from data-at-rest encryption.
-Encrypted vSphere vMotion secures confidentiality, integrity, and authenticity of data transferred during VM migrations. For encrypted VMs, vMotion always uses encryption. For unencrypted VMs, encrypted vMotion can be set to Disabled, Opportunistic (default), or Required. Cross-vCenter vMotion is supported when using shared key providers or backup/import of Native Key Provider. VCF uses one-time keys (nonces) for each migration session so that captured traffic cannot be replayed or decrypted after migration completes.
-Memory Tiering encryption provides protection for tiered memory without requiring external key management. VCF generates random 256-bit AES-XTS keys at the kernel level during VM power-on, unique to each VM instance or per host depending on configuration.
-VM Encryption provides protection across all datastore types including vSAN, iSCSI, NFS, and Fibre Channel. Disk encryption uses XTS-AES-256 keys as the disk encryption key. This encryption occurs before data reaches the storage layer, providing both data-at-rest and data-in-transit protection.
-Kubernetes on VKS supports encryption at rest for data stored within the control plane. Operators configure the encryption provider and manage key access for control plane secrets; when relying on a managed key provider, administrators retain responsibility for access controls over the managed key material. The VCF Automation consumption layer includes VCF Encryption Management, which grants organization administrators the ability to use encryption keys from their own key providers for encryption of virtual machines and disks in their VCF environment, extending the platform's cryptographic key management to tenant-level operations.
-For storage protocols, VCF provides varying levels of native encryption support. iSCSI includes CHAP for session authentication. Fibre Channel Gen 7 supports end-to-end encryption with secure HBAs. For NFS datastores, version 4.1 supports Kerberos authentication with three security levels: krb5 (authentication only), krb5i (authentication plus integrity checking), and krb5p (authentication plus privacy with full encryption).
-ESX stores configuration data in encrypted form on boot devices. When the host has a TPM 2.0 enabled and configured, the configuration encryption key is stored in the TPM. The encryption mode can be configured using the esxcli system settings encryption set command with the --mode=TPM parameter.
-Cryptographic operations are controlled through fine-grained privileges in vCenter. Only users assigned the Cryptographic Operations privileges can perform cryptographic operations. A dedicated No Cryptography Administrator role enables standard VM and infrastructure management while restricting unauthorized encryption changes. This role can be cloned and customized to grant only specific Cryptographic Operations privileges, such as allowing encryption but not decryption, supporting the principle of least privilege for encryption tasks. The CryptoManager and CryptoManagerKmip managed objects provide programmatic interfaces for handling cryptographic keys and integrating with key management server infrastructure. vSAN encryption key management requires specific permissions including Cryptographer.ManageEncryptionPolicy, Cryptographer.ManageKeyServers, and Cryptographer.ManageKeys.
-vSAN includes secure disk wipe capabilities for proper media sanitization when decommissioning storage, supporting the Erase disks before use option during encryption configuration and disk management operations.
-Defining the organization's cryptographic policy (algorithm selection, key strength, rotation schedules, KMS architecture, FIPS-mode activation decisions) and the key lifecycle management standards that govern key creation, distribution, storage, archive, and destruction sit with the organization above the platform. VCF supplies the validated cryptographic modules and protocol enforcement; the organizational cryptographic governance program determines how those mechanisms apply across the environment. Security Technical Implementation Guides (STIGs) for Supervisor and VKS releases are available to guide cryptographic hardening of the consumption layer.
-VMware Private AI Services (PAIS) provides cryptographic controls across its AI infrastructure components, building on the cryptographic foundation of VCF.
-GPU-accelerated VMware Kubernetes Service (VKS) clusters deployed for PAIS workloads use a FIPS-enabled Kubernetes runtime. The VKS cluster topology version applied to both control plane and worker deployments uses a FIPS-enabled VKR build running on Ubuntu 24.04, so AI workloads on PAIS VKS clusters operate within a FIPS-compliant Kubernetes runtime.
-PAIS endpoints use TLS for service communication. The PAISConfiguration custom resource supports configurable CA bundle references through spec.clientTls.caBundleRefs for OIDC provider and Harbor registry authentication. The Supervisor endpoint communication for PAIS uses HTTPS on port 6443 with certificate-based authentication. The PAIS Prometheus metrics endpoint uses self-signed certificate authentication with TLS, where the CA certificate is retrieved from the pais-ingress-default Secret in the PAIS namespace and configured in base64-decoded form. Prometheus TLS client authentication and certificate validation are off by default; auditors should verify that client authentication is enabled in production deployments where mutual certificate validation is required.
-PAIS requires CA trust bundles to be configured for all external HTTPS connections, including OIDC providers, Harbor registries, content management systems used as data sources in the Data Indexing and Retrieval service (such as Confluence or SharePoint), MCP servers that provide tools to agents, and the pgvector database server used for vector storage. Trust bundle material is obtained from each external system's administrator either as a certificate file or as a ConfigMap stored in the namespace where PAIS is deployed, and PAIS recommends maintaining separate trust bundles per application with periodic updates before certificate expiration. Administrators add trusted certificates through the VCF Automation Provider Management UI under Certificate Management and Trusted Certificates. The issuer certificate of the Harbor registry must also be added to the certificate trust store on Deep Learning VMs that pull models from the registry. When connecting to an MCP server over HTTPS, the MCP server issuer certificate must be added as a CA trust bundle.
-The underlying cryptographic algorithms, cipher suites, and platform-level key management are provided by VCF and VKS. Organizations are responsible for selecting and enforcing approved cryptographic standards at the VCF and infrastructure level, while PAIS provides the certificate management and trust chain configuration mechanisms specific to AI service endpoints.</t>
+          <t>VCF provides cryptographic protection for data in transit across management, compute, storage, and inter-site networks. The architecture applies encryption at multiple layers using validated cryptographic modules and current TLS protocol versions.
+VCF management and monitoring communications use TLS as the transport protocol. VCF Operations for Networks supports modern TLS protocol versions, with the ability to restrict cryptographic module usage to FIPS-validated modules by enabling FIPS mode for external connections. Telegraf, the metrics collection agent, is configured to require a modern minimum TLS version for its communication channels. When using the databus for on-premises environments, HTTPS is the recommended transport to protect data during transmission and to verify subscriber authenticity. The TLS implementation includes customizable PKI options ranging from fully automated certificate management within VCF to integration with enterprise PKI infrastructure such as Microsoft Active Directory Certificate Services. VCF Operations provides centralized certificate lifecycle management across VCF components, supporting auto-renewal for VMCA, MSCA, and OpenSSL CA, handling automated renewal, monitoring, and replacement. Machine SSL certificates can be renewed through the API for a specified period up to 730 days. Starting in vSphere 9.0, all vSphere TLS profiles are FIPS compliant, and the COMPATIBLE profile supports modern TLS cipher suites and elliptic curves. The vCenter appliance uses VMware's Boring Crypto Module version 6.0, which provides FIPS-validated cryptographic operations including AES, ECDSA, HMAC, RSA, and SHA-2 variants.
+NSX, which provides networking services within VCF, uses FIPS 140-3 validated cryptographic modules by default. These modules are validated through the NIST Cryptographic Module Validation Program. NSX Manager uses FIPS 140 approved algorithms for authentication to its cryptographic module. For site-to-site connectivity, the NSX L2 VPN FIPS compliance suite uses FIPS-approved encryption with Perfect Forward Secrecy enabled and standardized Diffie-Hellman key exchange, providing transmission confidentiality for tunneled traffic. VCF Operations for Networks supports modern ECDSA and RSA signature algorithms for data source connections.
+VCF Automation uses the BouncyCastle FIPS 2.0.0 cryptographic module, which is compliant with FIPS 140-3 (Certificate #4743). VCF Operations for Networks uses the BC-FJA (Bouncy Castle FIPS Java API) version 2.0.0 with FIPS 140-2 Certificate #37009. These validated modules underpin the cryptographic operations used for securing communications across the automation and operations components.
+At the storage layer, vSAN provides data-in-transit (DIT) encryption that protects data as it moves between hosts within the cluster. DIT encryption is a cluster-wide setting that, when enabled, encrypts all data and metadata traffic across hosts. Forward secrecy is enforced for vSAN data-in-transit encryption, meaning that compromise of a long-term key does not expose previously encrypted traffic. DIT encryption operates independently of data-at-rest encryption and does not require external key management servers. The behavior differs by storage architecture: in vSAN Original Storage Architecture (OSA), data-at-rest encryption occurs at the target host's Local Object Manager layer, so data traverses the network before encryption, making DIT encryption strongly recommended. In vSAN Express Storage Architecture (ESA) in HCI mode, data is encrypted at the VM host before network transmission, making DIT encryption optional based on compliance requirements.
+VM Encryption provides confidentiality protection across all datastore types including vSAN, iSCSI, NFS, and Fibre Channel. VM encryption is implemented on the ESX host rather than on the storage array, so it protects data both at rest and in transit to the storage backend. Disk encryption uses AES-256 as the disk encryption key.
+Encrypted vSphere vMotion protects VM data during live migrations. For encrypted VMs, vMotion always uses encryption and cannot be disabled. For unencrypted VMs, encrypted vMotion offers three settings: Disabled, Opportunistic (default, uses encryption when supported), and Required. AES-NI significantly improves encryption performance for these operations. Cross-vCenter vMotion supports encryption when source and destination use shared key providers; vCenter Crypto Manager provides an importProvider method to import a vSphere Native Key Provider configuration between sites. vSphere Fault Tolerance log traffic, which synchronizes VM state between primary and secondary instances, can also be encrypted to protect this synchronization data in transit.
+Storage protocol support varies by type. vSAN File Service supports NFS4 Kerberos authentication with security options krb5, krb5i, and krb5p, where krb5p provides authentication plus encryption of data in transit. iSCSI uses CHAP for session authentication but does not encrypt data natively, so VM Encryption or in-guest encryption is needed for confidentiality on iSCSI networks. Fibre Channel Gen 7 supports end-to-end encryption with secure Host Bus Adapters.
+HCX Network Extension services support transport encryption for data between site pairs, and this encryption is enabled by default. VCF Operations HCX tunnel encryption similarly uses transport encryption by default to protect Network Extension data and migration traffic between sites. This default-on approach reduces the risk of data being transmitted in cleartext during workload migrations or network extensions.
+High-quality entropy generation on ESX hosts supports the proper functioning of security-related operations such as generating encryption keys for secure network communication. This foundational capability helps maintain the strength of cryptographic keys used across all transmission encryption functions in the platform.
+VMware Kubernetes Service (VKS), which runs on vSphere Supervisor, applies TLS encryption across all control-plane communication paths. The Kubernetes API server enforces encrypted transmission within the control plane and between the control plane and its clients by default, so all API server interactions travel over TLS. Cipher suites are configurable at each component layer: the kube-apiserver `--tls-cipher-suites` parameter accepts a comma-separated list of permitted cipher suites; the kube-scheduler exposes the same `tls-cipher-suites` parameter to keep its API endpoint aligned; and the kubelet exposes `tlsCipherSuites` and `tlsMinVersion` settings in `KubeletConfiguration` to scope the permitted cipher algorithms and minimum protocol version at the node level. Antrea, the CNI plugin included with Supervisor, supports configurable TLS cipher suites for its own secure communication channels through the `tlsCipherSuites` setting, and the vSphere Cloud Provider Interface (CPI) exposes the same capability through a configurable cipher suite list.
+For environments with strict cryptographic requirements, VKS supports FIPS mode through the ClusterClass variable `fips.enabled`, which controls which encryption algorithms are permitted at the node level. TanzuKubernetesRelease references carrying the `-fips.1` suffix indicate that FIPS cryptographic modules are active for that node pool. The Istio service mesh package, available as a standard package on VKS clusters, ships with FIPS compliance and supports mutual TLS (mTLS) between pods within the mesh; the `meshMTLS.minProtocolVersion` setting controls the minimum acceptable protocol version for all inter-service traffic. Ingress-layer encryption for workloads is handled by the Contour package, which exposes `tls.minimum-protocol-version` and `tls.maximum-protocol-version` settings so operators can define a bounded range of acceptable protocol versions for inbound HTTPS traffic. The Supervisor secret injection agent automatically configures mutual TLS for its communication with the vault agent injector service using auto-generated certificates. Harbor, available as a Supervisor Service, accepts custom TLS certificates through its `tlsCertificate.tls.crt` and `tlsCertificate.tls.key` configuration fields, supporting encrypted access to the container registry for image distribution.
+Defining the encryption policy for customer workload traffic, selecting cipher and FIPS configurations for environments with stricter requirements, and validating that data transmitted from customer applications and containerized workloads meets confidentiality standards are organizational data-policy decisions.
+VMware Private AI Services (PAIS) provisions VKS clusters using a FIPS-enabled Kubernetes build for cryptographic compliance across both control plane and worker node communications. The VKS cluster topology version is v1.33.1--vmware.1-fips-vkr.2 with FIPS compliance enabled, running on an Ubuntu 24.04 OS image, covering the cryptographic modules that protect data in transit within the cluster fabric.
+PAIS, activated through the PAISConfiguration custom resource on the Supervisor, requires HTTPS for all external integrations. The spec.clientTls.caBundleRefs section of the PAISConfiguration YAML references CA trust bundles supplied as ConfigMap resources. Operators must configure HTTPS trust bundles for the OIDC provider, the Harbor container registry, content management systems hosting Knowledge Base data sources, MCP servers providing tools to models, and the pgvector database. Separate trust bundles are recommended per application, with periodic updates required before certificate expiration.
+The PAIS Supervisor endpoint uses HTTPS on port 6443 with certificate-based authentication. The PAIS ingress endpoint is protected by a self-signed certificate stored in the pais-ingress-default Kubernetes Secret. Administrators retrieve the CA certificate using `kubectl get secrets/pais-ingress-default -o yaml` and distribute it to clients that connect to the service, including Grafana when configured to scrape the PAIS Prometheus endpoint. CA trust bundles for external entity connections are managed through ConfigMaps and updated as certificate content changes.
+VCF Automation Provider Management for PAIS uses a base64-encoded certificate (TM_CERT_BASE64) obtained by running openssl s_client against the VCF Automation FQDN on port 443, enabling authenticated HTTPS communication between AI catalog tooling and the PAIS environment. MCP server integrations require the MCP server's issuer certificate to be added as a CA trust bundle before connecting over HTTPS using either Streamable HTTP or Server-Sent Events transport.
+Telemetry sent from PAIS to the OpenTelemetry Collector is authenticated using a Kubernetes Secret containing Authorization Bearer tokens and custom authorization headers. LLM trace transport to the collector uses HTTP/protobuf or gRPC, both protecting trace traffic in transit.
+One configuration detail that auditors should verify: PAIS Prometheus TLS client authentication and certificate validation are turned off by default (the tls-client-authentication setting on the Prometheus endpoint). Organizations should review this setting and enable mutual TLS where their policy requires it. The underlying network transport encryption between VMs and workload domains is provided by VCF and is documented in VCF Coverage.</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -1780,14 +1767,10 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to the implementation of cryptographic protection controls by using known public standards and trusted cryptographic technologies across its component stack for securing inter-component communications and providing cryptographic inspection capabilities for network traffic.
-Security Services Platform (SSP), the control-plane component of vDefend, secures communications between vDefend product components using certificates and current TLS protocol versions with approved cipher suites. SSP and the SSP Installer deploy with the most current TLS version by default and also support the prior major TLS version. The TLS versions and cipher suites allowed on SSP Installer and SSP are fixed and cannot be modified, which enforces a consistent cryptographic baseline across deployments.
-SSP components, including the SSP Installer and the NDR Sensor for vDefend, implement FIPS 140-2 and FIPS 140-3 cryptographic module standards. SSP uses the VMware BouncyCastle Module (NIST CMVP Certificate #4943) and the VMware OpenSSL FIPS provider Object Module (NIST CMVP Certificate #4861) for its cryptographic operations. SSP actively enforces cryptographic hygiene by rejecting any certificate or TLS configuration that uses deprecated algorithms, short keys, or legacy protocol versions, returning a validation error rather than permitting degraded connections.
-Certificate management within SSP provides lifecycle controls including certificate export, certificate signing request (CSR) generation, and CA-signed certificate replacement. SSP monitors and manages several certificate types used to identify client and host machines, establish trust between components, secure communications, and control access levels. Administrators can retrieve and validate LDAP certificates using standard tools to establish secure LDAPS connections for platform authentication. These capabilities allow organizations to integrate vDefend into their broader PKI infrastructure and follow standard certificate lifecycle practices.
-vDefend provides TLS Inspection capabilities that allow the firewall to decrypt, inspect, and re-encrypt TLS-protected traffic. Without TLS Inspection, encrypted traffic cannot be examined or enforced against security policies even when other advanced security features are enabled. With TLS Inspection enabled, vDefend gains visibility into encrypted traffic flows, supporting more effective access control and threat detection. TLS Inspection also supports importing or generating trusted and untrusted proxy certificate authorities for external decryption profiles, giving administrators control over the CA chain used in inspection.
-TLS Inspection includes a Crypto Enforcement option within decryption action profiles that allows administrators to set minimum and maximum protocol version and cipher suite constraints for both client and server connections. Profiles can be configured in Transparent or Enforce modes; the Enforce mode requires compliance with the configured cryptographic constraints.
-vDefend IDS/IPS signature rules extend cryptographic visibility by supporting protocol version matching and certificate Subject field matching, enabling enforcement decisions based on certificate metadata in encrypted traffic. IDS/IPS rules also support storing TLS/SSL certificates to disk for forensic analysis and threat investigation. SSP guidance recommends that organizations restrict or block protocols that carry data in cleartext and enforce minimum secure protocol versions as part of their network security practices.
-vDefend does not itself provide the underlying key management infrastructure (KMS), platform-wide PKI lifecycle management, or the broader VCF platform's cryptographic controls; those responsibilities belong to VCF. However, vDefend's consistent use of approved cryptographic standards for its own operations and its ability to perform cryptographic inspection of network traffic contribute to an organization's overall implementation of cryptographic protection controls.</t>
+          <t>VMware vDefend contributes to transmission confidentiality through inspection, visibility, and enforcement mechanisms at the network layer, while the underlying cryptographic protection of data in transit is the responsibility of endpoint applications and infrastructure components.
+TLS Inspection uses a transparent TLS proxy to intercept and analyze encrypted traffic flows traversing the environment. This allows security policy to be applied to traffic that would otherwise be opaque and supports detection of threats embedded within encrypted sessions. TLS Inspection can be deployed to provide visibility into encrypted connections while preserving end-to-end encryption for flows not subject to a decryption policy, and supports both inbound and outbound inspection profiles.
+Security Intelligence, integrated within the Security Services Platform (SSP), surfaces workloads communicating over application protocols that transport data without encryption. The Security Segmentation Report identifies communication chains containing at-risk unprotected members and quantifies the number of unprotected data flows hitting default-allow rules across observed traffic. Administrators can use this reporting to identify and prioritize remediation of encryption coverage gaps, including restricting or blocking cleartext protocols.
+The Security Services Platform and its component services use FIPS 140-2 and FIPS 140-3 validated cryptographic modules for their own communications. Network Detection and Response (NDR) Sensors connect to the SSP using mutual TLS authentication (mTLS), with a dedicated certificate for each sensor signed by an intermediate certificate authority on the SSP. The SSP can be configured to forward log messages to a syslog server over TLS, and Malware Prevention Service remote logging likewise uses TLS to transmit log data to a remote log server. NDR also supports SSL verification for event logs sent over HTTPS. When NDR shares data to the cloud, it anonymizes sensitive customer information before transmission.</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
@@ -1797,11 +1780,10 @@
       </c>
       <c r="J12" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) implements cryptographic protections for disaster recovery workflows using known public standards and trusted cryptographic technologies.
-PNR uses modern TLS by default for all connections to the PNR server. The minimum TLS protocol version is configurable through the envoy-proxy-config.json file by editing the tls_minimum_protocol_version parameter. When the minimum protocol version is modified, PNR requires that the change be applied consistently across all relevant configuration occurrences in the system. Administrators can verify the TLS version in use on the Site Recovery Manager component using standard OpenSSL tooling.
-The PNR Appliance requires an SSL/TLS certificate as the endpoint certificate for all TLS connections to the PNR server. PNR supports custom certificates signed by a certificate authority as an alternative to self-signed certificates. Custom SSL/TLS server endpoint certificates must meet specific requirements, including x509v3 Extended Key Usage indicating TLS Web Server Authentication. The Appliance Management Interface allows administrators to import CA-signed server certificates and custom root CA certificates, and to replace the appliance certificate. PNR uses TLS certificates and private keys to protect network communication and establish authentication with other servers. Certificate verification error messages are logged in security-related log files, and operational log files do not contain sensitive information such as private keys or passwords.
-For encrypted virtual machine replication, PNR requires that the recovery and protected sites use a common Key Management Server (KMS) or that the KMS clusters at both sites share common encryption keys. Replication of encrypted virtual machines also requires Secure LWD support to be available on the virtual machine. This supports data-at-rest encryption continuity for virtual machines through the recovery lifecycle.
-Defining the organization's cryptographic policy, including KMS architecture decisions, minimum TLS version selection, certificate management standards, and key lifecycle practices, sits with the organization above the DR layer. PNR supplies the cryptographic mechanisms needed for DR-specific traffic and operations; the organizational cryptographic governance program determines how those mechanisms apply across the environment.</t>
+          <t>VCF Protection and Recovery (PNR) provides cryptographic protection for data transmitted during disaster recovery operations, covering management communications and replication data flows.
+All communications between the PNR server and VMware vCenter (vCenter) instances take place over TLS connections. PNR requires an SSL/TLS certificate, with x509v3 Extended Key Usage indicating TLS Web Server Authentication, as the endpoint certificate for all TLS connections to the PNR server. PNR defaults to the current TLS version for all communication endpoints and supports administrative configuration of the minimum acceptable protocol version. Administrators configure the minimum TLS protocol version by editing the tls_minimum_protocol_version parameter in the envoy-proxy-config.json file; when changing the minimum version, the update must be applied consistently across all occurrences in the system. PNR uses TLS certificates and private keys to protect network communication and authenticate with other servers.
+For replication data, vSphere Replication encrypts replication traffic in transit for both new and existing replications. Network encryption is mandatory when using vSphere Replication 9.0.3 and later and is enabled by default. PNR also supports configuring network encryption of replication traffic as an option for replication scenarios where mandatory encryption does not apply automatically. PNR supports protection and recovery of encrypted virtual machines through both array-based and vSphere Replication protection groups, allowing VM disk encryption to persist through the replication process. Recovery of encrypted virtual machines requires that the protected and recovery sites share a common Key Management Server (KMS), or that the KMS clusters at both sites use common encryption keys, to maintain key availability after failover.
+Defining the encryption policy for environments with stricter requirements and validating that workload traffic running on protected virtual machines meets confidentiality standards are organizational data-policy decisions.</t>
         </is>
       </c>
       <c r="K12" s="10" t="inlineStr">
@@ -1811,12 +1793,10 @@
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) implements cryptographic protections across multiple layers of its architecture, applying standard cryptographic technologies for data in transit, certificate trust management, and credential storage.
-Starting with DSM, the platform enforces FIPS 140-3 compliant cryptographic standards and validates certificates during upload, rejecting unsupported algorithms or parameters. Only RSA and ECDSA public key algorithms are accepted for certificates. The Ed25519 elliptic curve signature algorithm is rejected because it does not comply with FIPS 140-3. Custom trusted certificates should use ECDSA P-256 or P-384 algorithms; RSA certificates must meet a minimum key size of 2048 bits per FIPS requirements. DSM's latest certificate validation mode enforces strict cryptographic and KeyUsage validations across all DSM endpoints, including the Provider VM and data service clusters.
-For connections to database clusters, DSM requires TLS for all client traffic. PostgreSQL database instances enforce a minimum TLS protocol version through the ssl_min_protocol_version setting. MySQL enforces minimum TLS versions on both the main connection interface and the administrative interface; these settings are fixed and cannot be modified by users, which helps maintain a consistent cryptographic baseline across deployments. MySQL also exposes the group_replication_recovery_tls_version setting to specify the TLS protocol used during distributed recovery connections. DSM supports SQL Server clusters, which use TLS to encrypt communication between clients and the cluster; the network.tlsProtocols custom engine setting defines the allowed TLS versions for client connections, and a minimum TLS version must be included for the DSM operator to manage the cluster. DSM supports TLS verification during PostgreSQL database migration, covering replication traffic between source and target clusters.
-DSM's certificate management capabilities support standard PKI practices. Administrators configure custom TLS certificates for database clusters through the DSM UI or API, providing certificates in PEM format with associated private keys and CA certificates. Supported private key algorithms are RSA and ECDSA with key sizes of 256 and 384 bits. When present, the X509v3 KeyUsage extension on a custom certificate must include the DigitalSignature capability; DSM also accepts certificates that omit the KeyUsage extension entirely, treating absent KeyUsage as permitting all usages in accordance with RFC 5280. To establish secure connections to database clusters and to the DSM Provider VM, clients add the CA to the operating system trust store or the trusted CA list. DSM's API provides a mechanism to retrieve the CA certificate from a custom certificate secret. The Consumption Operator, which enables self-service database provisioning, requires a TLS certificate for its communication with the DSM provider. Certificate management can also be handled through Kubernetes cert-manager, which manages various issuer types and outputs Kubernetes TLS Secrets in the format DSM requires.
-DSM supports TLS for connections to external systems. When configuring log forwarding to an SMTP server, DSM supports Auto TLS to establish a secure connection. For private container registries, DSM supports CA certificate validation for untrusted registries.
-For local user credential storage, DSM encrypts passwords using PGP symmetric encryption through the PGCrypto library, with dedicated encryption keys stored using the PGCRYPTO_PASSWORD and PGCRYPTO_ALGORITHM keys. MySQL has FIPS mode available on the client side through the ssl_fips_mode setting. PostgreSQL databases include the pgcrypto extension, which provides cryptographic functions that applications can use directly within the database. The DSM Provider Appliance includes virtual machine encryption, which activates when a Key Management Server is configured in the environment.</t>
+          <t>VMware Data Services Manager (DSM) applies TLS-based encryption across multiple communication paths, covering database client connections, management interfaces, service-to-service communication, and data migration traffic. Starting with DSM, the platform enforces FIPS 140-3 compliant cryptographic standards and validates certificates during upload, rejecting unsupported algorithms such as Ed25519.
+For database client connections, DSM enforces a minimum TLS protocol version across all supported database engines. PostgreSQL instances enforce a configurable minimum TLS protocol version via the `ssl_min_protocol_version` setting and support certificate-based authentication with CA verification. PostgreSQL replication connections support SSL/TLS encryption with a configurable `sslmode` parameter to secure data in transit between source and target databases, and DSM validates SSL trust before establishing replication. MySQL locks TLS protocol enforcement at the platform level so users cannot weaken it. MySQL has `require_secure_transport` set to ON by default, which requires all client connections to use encrypted transport. MySQL supports FIPS mode via the `ssl_fips_mode` setting. DSM adds SQL Server as a supported database engine; SQL Server clusters use TLS to encrypt client connections, require a minimum TLS version for DSM operator management, and expose the `network.tlsProtocols` engine setting to configure the set of allowed TLS versions.
+For management and service-to-service communication, the DSM Provider exposes an HTTPS endpoint. The Consumption Operator requires a TLS certificate for secure communication with the DSM provider. In network-isolated deployments, Consumption Operator image transfers to a private registry support optional TLS certificate authentication. Metrics forwarding from DSM to VCF Operations supports mutual TLS (mTLS) authentication, requiring a client certificate and private key. DSM SMTP settings include an Auto TLS option that establishes a secure connection to the SMTP server.
+DSM provides certificate management capabilities to support the TLS infrastructure. Custom certificates are validated for FIPS 140-3 compliance at upload time; accepted key types are ECDSA P-256, ECDSA P-384, and RSA with a minimum key size of 2048 bits, and Ed25519 keys are rejected as non-compliant. Trusted root certificates added through the DSM UI must comply with FIPS requirements.</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
@@ -1826,12 +1806,13 @@
       </c>
       <c r="N12" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides configurable SSL/TLS profiles that control which cipher suites, protocol versions, and key exchange algorithms are permitted for application traffic termination. The SSL/TLS Profile, configured under Templates &gt; Security &gt; SSL/TLS Profile, contains the accepted protocol version list and a prioritized cipher suite list applied to virtual services. Administrators can create custom profiles or select from built-in templates; the documentation notes that the choice of accepted ciphers and protocol versions involves trade-offs between security, client compatibility, and computational expense. SSL profiles in 9.1 include a Post Quantum Cryptography section with support for modern cipher suites. Controller SSL/TLS certificates support elliptic curve (EC) or RSA algorithms, with EC recommended for new deployments.
-For environments subject to cryptographic module validation requirements, Avi supports a FIPS mode backed by the OpenSSL FIPS Provider, which has been validated at FIPS 140-3 Security Level 1 and awarded Certificate #4985 by the Cryptographic Module Validation Program (CMVP). When FIPS mode is activated on the Controller cluster, Avi restricts cryptographic operations to FIPS-compliant algorithms only. FIPS 140-3 also requires stricter handling of sensitive security parameters including keys, authentication data, and random number generation. FIPS mode is enabled at the Controller cluster level through the Controller settings. Note that FIPS mode does not support SSL Client Hello events in Avi DataScript, which may affect certain scripted traffic inspection use cases.
-Avi Controller allows administrators to restrict specific key exchange algorithms and ciphers for management session access. The Allowed Ciphers field restricts management session ciphers to a specified subset, and the kex_algorithm_exclude field under Controller Settings excludes specific key exchange methods for SSH-based administrative access. Internal communications between the Avi Controller and Service Engines also use SSL/TLS, and custom certificates can be selected for this Secure Channel connection via the Access tab certificate field.
-For certificate management, Avi integrates with Hardware Security Modules (HSMs), including the Thales Luna (formerly SafeNet Luna) HSM, for cryptographic key storage and management. The Controller is set up as an HSM client and can create keys and certificates directly on the HSM through client libraries, supporting high-availability HSM configurations. Automated certificate lifecycle management is available through Let's Encrypt integration using the ACME protocol. Avi's App Transport Security feature supports integration with the Venafi Trust Protection Platform for certificate administration across tenants, with the Trust Protection Platform pushing signed certificates and required chain certificates to Avi Load Balancer.
-For Kubernetes deployments, the Avi Kubernetes Operator (AKO) supports PKIProfile-based certificate validation and trust management for backend services. The PKIProfile, configured through custom resources, enables secure communication with backend services through certificate-based authentication and encryption. In VCF environments, the Avi PKI Profile defines the list of trusted certificate authorities permitted to sign client certificates and can be used to implement Zero Trust security between servers and clients.
-Data-at-rest encryption for Avi Controller and Service Engine VMs is provided by VCF at the platform layer, not by Avi itself. Organizations must configure Avi SSL/TLS profiles, select appropriate cipher suites, and enable FIPS mode where cryptographic module validation requirements apply to activate these controls.</t>
+          <t>VMware Avi Load Balancer (Avi) provides native, configurable cryptographic mechanisms to protect the confidentiality of data in transit at both the application data plane and the Controller management plane.
+Each virtual service in Avi is associated with an SSL/TLS Profile, which defines the accepted protocol versions, cipher suites, and their priority order. SSL/TLS Profiles are managed at Templates &gt; Security &gt; SSL/TLS Profile in the Controller UI. Predefined profile templates are available, including a System-Standard template, and administrators can create custom profiles to enforce the cipher suites and protocol versions appropriate for their environment. Elliptic Curve (EC) cryptography is available for virtual services and supports Perfect Forward Secrecy with less computational overhead than RSA-based key exchange. TLS persistence state exchanged between Service Engines when a client reconnects is carried in encrypted form. At the L4 proxy level, the Default-TLS protocol parser can be associated with a virtual service to inspect TLS handshake data using DataScript, supporting selective offload and re-encryption scenarios.
+In Kubernetes environments, the Avi Kubernetes Operator (AKO) supports a PKIProfile custom resource definition that enables certificate-based authentication and encryption for backend service communication. The System-Standard SSL Profile can be applied through the RouteBackendExtension CRD to enable SSL/TLS re-encryption for traffic to backend servers, providing modern cipher suites for Kubernetes ingress and routing scenarios. In VCF environments, the Avi load balancer uses secrets to handle encrypted HTTPS traffic, configured through the VCF IaaS Service Console.
+When FIPS mode is enabled on the Avi Controller cluster, all cryptographic operations across the Controller and Service Engines are restricted to FIPS 140-3 approved algorithms. Avi uses the OpenSSL FIPS Provider version 3.1.2 in this mode, which has been validated at FIPS 140-3 Security Level 1 and awarded Certificate #4985 by CMVP. Enabling FIPS mode is a cluster-level configuration that applies uniformly to all cryptographic material handled by the platform. FIPS mode does not support SSL Client Hello events in Avi DataScript, and post-quantum cryptographic capabilities are not available in FIPS mode.
+The Avi Controller and Service Engines use SSH for secure management communication. The SE_SECURE_CHANNEL designation classifies traffic between the Controller and Service Engines to maintain a dedicated secure communication channel. Avi also integrates with Let's Encrypt via the ACME protocol to automate certificate issuance and renewal for virtual services, and with hardware security modules such as the Thales Luna HSM for external key management. Remote server file transfer supports Secure Copy Protocol (SCP) and Secure File Transfer Protocol (SFTP). For deployments requiring hardware acceleration, Avi Service Engine integrates with Intel QuickAssist Technology to offload bulk cryptographic operations following SSL/TLS handshake completion.
+Avi DataScript exposes cryptographic functions for application-layer use cases. The avi.crypto.encrypt() function encrypts data using a caller-provided key, optional initialization vector, and algorithm parameter. The HTTP Cookie Encryption Gateway uses these functions to encrypt cookie values in HTTP responses, protecting session state carried between client and server. The avi.utils.rand_bytes function generates cryptographically secure random bytes for token and nonce generation.
+Defining which application traffic requires encryption and configuring the virtual service profiles to apply protection at the appropriate boundary are organizational data-policy decisions.</t>
         </is>
       </c>
     </row>
@@ -1863,17 +1844,15 @@
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>VCF provides integrated mechanisms for identifying, tracking, and remediating vulnerabilities across the infrastructure stack. These capabilities span automated detection, compliance monitoring, alert-driven tracking, structured remediation workflows, and lifecycle management tooling.
-VCF Diagnostics automatically detects known issues and critical vulnerabilities within the VCF software stack, providing detailed descriptions, root cause insights, and actionable remediation steps. This capability builds on several legacy diagnostics tools and operational data to deliver integrated issue detection and remediation from a single pane. Diagnostic Findings uses a library of log and property-based diagnostic rules (also called signatures) to identify known issues across the platform, giving operations teams a structured way to discover and resolve problems.
-VCF Operations extends vulnerability tracking through compliance management, which detects violations, highlights risk areas, and provides actionable remediation recommendations. When VCF Operations detects non-compliance with a defined policy, it generates alerts or notifications. Depending on the severity, administrators can configure automated remediation actions to bring objects back into compliance without manual intervention. VCF Operations also maps out-of-the-box workflows to recommendations and associates them with specific alerts, enabling automated remediation tied directly to detected conditions. To retrieve remediation recommendations for a specific virtual machine, the system must be connected to a VCF Operations instance with at least one triggered alert for that virtual machine.
-Configuration Drifts in VCF Operations provides a proactive method to monitor configuration changes across vCenter instances and vSphere clusters. Administrators can view and compare configuration drifts and identify settings that have changed over time. VCF Operations audit logging tracks each configuration change to an authenticated user who initiated the change or scheduled the job that performed the change, allowing administrators to determine who changed what and when.
-VCF lifecycle management simplifies and automates the process of applying updates and patches to software components within the VCF stack. VCF Operations includes patch planner functionality for updating or patching individual VCF core components in a VCF domain, and provides a Plan Patching capability to create patching plans for desired components. Pre-update validation runs upgrade prechecks to verify readiness before proceeding, identifying issues before the update starts. Update bundle management supports both online and offline depots; the VCF Download Tool and the lcm-bundle-transfer-util command handle bundle download, staging, and repository configuration for environments with limited or no internet connectivity.
-On the patching side, Broadcom releases security advisories for critical known vulnerabilities with step-by-step remediation instructions. Patch releases for VCF components provide time-sensitive fixes to security and catastrophic issues that affect business operations. These patches are released between major, minor, and maintenance releases and can be selectively applied based on environmental impact and operational costs.
-vSphere Lifecycle Manager (vLCM) manages desired-state configurations for ESX hosts. It can create a desired state that includes a specific version of the ESX host, compatible partner software and firmware components, and add-ons. When hosts deviate from the target specification, cluster remediation applies the desired state to each non-compliant host, with the Coordinator Manager running pre-checks to evaluate how each host is affected and whether additional steps are needed. Patches can be staged to ESX hosts before remediation begins, reducing the time hosts spend in maintenance mode during the remediation window. Remediation can also be initiated manually or scheduled as a regular task to run at a time convenient for operations teams, supporting consistent patch compliance over time. Firmware add-ons can be added, replaced, removed, upgraded, or downgraded as part of the image. The vSphere Automation REST API allows administrators to query effective global and cluster-specific remediation policies before initiating remediation, supporting a review-before-apply workflow that reduces risk during patching operations.
-VCF also provides tooling for managing remediation at scale. VCF PowerCLI supports parallel remediation with a configurable maximum number of concurrent remediations, allowing administrators to remediate multiple hosts simultaneously. Live Patching allows security updates to be applied to ESX hosts without requiring a host reboot. vCenter RDU upgrades perform automatic rollback if the upgrade fails, providing a safety net during update operations. Maintenance releases are scheduled, cumulative updates focused on platform stability and support, providing bug and security fixes, hardware enablement changes, driver updates, guest OS support, and backward-compatible new features with limited scope to minimize operational impact.
-For containerized workloads running on vSphere namespaces, VMware Kubernetes Service (VKS) extends vulnerability identification and remediation to the application layer. Harbor Registry, deployable as a standard package on VKS clusters, performs automated vulnerability scanning against container images using the Trivy vulnerability database, which can be configured to point to a custom or mirrored registry. Harbor also supports image signing to establish content trust, giving administrators a mechanism to identify images that have passed security review. Admission controls can be configured to restrict workload deployments to images sourced from a designated Harbor instance where scanning is enforced, helping constrain the image surface to scanned and trusted artifacts.
-VKS MachineHealthCheck provides automated remediation of unhealthy cluster nodes. The remediation.maxInFlight parameter controls how many concurrent node remediations may proceed simultaneously, and the triggerIf.unhealthyLessThanOrEqualTo threshold determines the condition under which remediation activates. The Kubernetes API surfaces a Remediating condition on VKS clusters, giving administrators direct visibility into the status of ongoing node remediation. DISA Security Technical Implementation Guides (STIGs) are available for both Supervisor and VKS cluster releases (VKrs), documenting known configuration weaknesses and providing step-by-step remediation guidance for hardening these deployments. The Kubernetes Security Response Committee tracks upstream Kubernetes vulnerabilities, assigns CVE identifiers, and publishes advisories through the kube-security-announce mailing list and the official Kubernetes CVE list; the committee's policy is to fully disclose vulnerabilities as soon as a user mitigation is available, with timeframes ranging from immediate to a few weeks depending on the complexity of the issue and vendor coordination requirements. Organizations running VKS can subscribe to receive these notifications and coordinate patch deployments accordingly.
-CI/CD pipelines deployed on the VCF consumption layer can incorporate Harness CI/CD with Security Testing Orchestration (STO). Harness STO integrates Wiz to perform pre-deployment vulnerability scanning across container image layers and automatically deduplicates findings, presenting each unique vulnerability, CVE, misconfiguration, or exposed secret as a single actionable item on the pipeline execution's vulnerabilities tab.</t>
+          <t>VCF provides several built-in capabilities that support routine vulnerability scanning and configuration error detection across the infrastructure stack, though a complete vulnerability management program requires integration with dedicated scanning tools for guest operating systems and applications.
+VCF Operations includes a diagnostics engine that automatically detects known issues and critical vulnerabilities within the VCF software stack. The engine scans the platform against VMware best practices, logs, and properties to identify diagnostic findings that match known issues, providing detailed descriptions, root cause insights, and actionable remediation steps. The Diagnostic Findings feature provides a consolidated view of known product issues, VMware Security Advisory (VMSA)-based security exposures, and best-practice recommendations across the environment. The Findings Catalog displays the complete list of diagnostic signatures checked at any given time, allowing administrators to see exactly what conditions are being evaluated. Administrators can manage diagnostics parameters through a JSON solution configuration file to customize which rules are active, adjust defaults, and control how findings are handled. These diagnostics build on the capabilities of several legacy tools and operational data to provide integrated issue detection and remediation.
+VCF Operations also supports advanced query capabilities that can identify virtual machines running vulnerable operating systems, including specific detection for end-of-life platforms such as Microsoft Windows Server 2003, Microsoft Windows Server 2008, Red Hat Enterprise Linux 5 and 6, and SUSE Linux Enterprise 10. These queries can group results by VLAN for security assessment and compliance monitoring purposes.
+The Security Operations dashboard consolidates user and infrastructure security elements into a single view, helping administrators identify areas that require attention. This dashboard highlights security-relevant findings across the VCF environment, providing a centralized starting point for security posture review.
+For configuration error detection, VCF Operations monitors configuration errors generated from infrastructure components such as NSX networking, grouping findings by hostname. Alert definitions can be created to monitor virtual machines and hosts with custom symptom parameters, enabling identification of configuration problems before users encounter them. The Configuration Drifts feature in VCF Operations provides proactive monitoring of configuration changes across vCenter instances and vSphere clusters, comparing current values against configuration templates to identify drift. vSphere Configuration Profiles must be enabled on clusters to view drift status. Configuration drift detection compares each vCenter instance's current configuration against the defined template values, and the Configuration Drift dashboard allows administrators to view and monitor drift statuses across the environment.
+For patch compliance scanning, vSphere Lifecycle Manager manages all hosts in a cluster collectively with a single image and tracks the current state of each host against the desired cluster image specification, reporting compliance status. The compliance check capability compares the current image on a host against the desired image and reports compatibility status. PowerCLI provides cmdlets for scanning virtual machines and hosts against defined baselines, including the Test-Compliance command to scan entities against downloaded patches and identify which hosts or components are missing security updates. Dynamic baselines update automatically based on specified criteria each time new patches are downloaded, allowing ongoing comparison of system state against current patch levels. The vCenter appliance can also be configured to perform automatic checks for available patches from a configured repository URL, enabling timely awareness of patch availability for the management plane itself. This automatic checking is configured through the vCenter Management Interface (the Check-for-updates-automatically setting) and supports proxy server configuration for environments without direct repository access.
+VMware releases security advisories (VMSAs) for critical known vulnerabilities with step-by-step remediation instructions. VCF Operations Diagnostic Findings provides a consolidated view of VMSA-based security exposures alongside best-practice recommendations, connecting advisory information directly to the operational environment.
+The DISA STIG Viewer tool provides automated checking of system configurations against STIG requirements, helping identify security vulnerabilities and configuration deviations for environments that follow DISA hardening guidance. This offers a structured approach to configuration compliance scanning against industry-standard best practices.
+While VCF provides vulnerability detection and compliance scanning for its own infrastructure stack, scanning of guest operating systems and applications running on VCF requires integration with third-party vulnerability scanning tools. VCF's REST APIs and PowerCLI support enable integration with external scanners and security information and event management platforms to extend scanning coverage beyond the infrastructure layer.</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -1883,14 +1862,10 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) contributes to vulnerability remediation by providing network-level threat detection and structured response mechanisms that identify, track, and contain exploitation attempts across protected workloads.
-vDefend Distributed IDS/IPS continuously monitors east-west traffic for known vulnerability exploits using signature-based detection. In 9.1, IDS/IPS event monitoring displays CVE reference information and Common Vulnerability Scoring System (CVSS) scores for vulnerabilities targeted by detected exploits, enabling security teams to correlate detected traffic with the specific vulnerability being exploited and prioritize response based on severity. Administrators can search the signature database by CVE ID, making it possible to verify detection coverage for a newly disclosed vulnerability and identify which IDS signatures apply before system signature updates are deployed.
-Custom signatures extend detection to application-specific and zero-day threats. vDefend IDS/IPS supports custom signatures that can be exported, edited, and re-uploaded to the system. Before publication, the system validates custom signatures and identifies those tagged as Invalid or Warning, preventing deployment of malformed detection rules. Custom IDS/IPS profiles can include custom signatures with assigned severity levels. Administrators can exempt known false positives from inspection when internal applications use protocols that resemble attacks but are not malicious, reducing alert noise without degrading detection coverage.
-The Security Services Platform (SSP) provides a structured remediation workflow for detected security events. When vDefend IDS/IPS, Malware Prevention, or Network Detection and Response (NDR) identifies a threat, administrators can apply remediation actions that automatically create Distributed Firewall rules or IDS/IPS policies to block the attack vector. Two remediation strategies are available: Targeted remediation creates surgically scoped rules that address the specific threat with potentially lower effectiveness, while Comprehensive remediation creates broader policies that protect against similar attack patterns with potentially lower safety margins. The Response and Remediation feature in SSP performs automated creation of policy based on user role and permissions. Intelligent Assist automates selection between these strategies and handles creation of the necessary groups, security profiles, rules, and policies. For Malware events, Targeted remediation enables all IDS signatures for the affected workload, and Comprehensive remediation creates Distributed Firewall policies. Remediations detected on the Gateway Firewall are applied on the Distributed Firewall, extending protection to east-west traffic. Applied remediation policies can be verified in NSX Manager at Security &gt; IDS/IPS &amp; Malware Prevention &gt; Emergency Threat Rules.
-SSP manages IDS policy lifecycle by extracting all active policies, rules, and security profiles to support multiple concurrent remediations, identify stale policies for cleanup, and suggest additions that avoid conflicts with existing rules. The Security Services Platform also identifies vulnerable workloads that could be exploited for lateral movement, helping administrators understand exposure before a threat can propagate across segments.
-Remediations are not automatically applied. Administrators must review and manually apply suggested remediations through the NSX Manager UI, and objects generated during remediation that encounter errors require manual cleanup. This manual review step gives security teams control over which containment actions are deployed.
-The Malware Prevention Service can deny access to suspicious files or delete files confirmed as malicious directly on the protected endpoint, providing a remediation path that extends beyond network policy to the file level.
-These capabilities complement VCF's infrastructure-level vulnerability and patch management by providing a network security layer that can detect active exploitation and apply containment actions while patches are being evaluated and deployed.</t>
+          <t>VMware vDefend contributes to vulnerability awareness through Security Services Platform analytics and IDS/IPS threat detection, though it does not perform host-based or authenticated application-layer vulnerability scanning.
+The Security Services Platform generates Security Segmentation Reports and Blast Radius Reports as part of the vDefend Security Assessment workflow. The Security Segmentation Report assesses security posture by analyzing network traffic over a configurable time range, identifying workloads running obsolete operating systems and using risky protocols, and providing specific improvement recommendations. Blast Radius Reports break down at-risk workloads, communication chains, and network flows to support protection planning. The Security Services Platform also provides an application monitoring view that displays information about running applications and identifies potential security risks, enabling assessment and remediation planning.
+The IDS/IPS subsystem contributes vulnerability-specific context by detecting exploitation attempts against known vulnerabilities. IDS/IPS event monitoring records Common Vulnerability Scoring System (CVSS) scores and CVE reference information for vulnerabilities targeted by active exploits. Administrators can search the signature library by specific CVE IDs to assess whether detection coverage is in place for known vulnerabilities. The Security Services Platform provides IDS/IPS performance metrics to monitor detection readiness across the environment.
+Because vDefend operates at the network layer, dedicated host-based and authenticated application-layer scanning tools are required to fully satisfy this control. Coverage remains at Contributes.</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
@@ -1924,12 +1899,12 @@
       </c>
       <c r="N13" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides several mechanisms that support an organization's vulnerability identification and remediation processes for application delivery infrastructure.
-For application-layer vulnerability identification, Avi's Web Application Firewall (WAF) supports virtual patching through integration with Dynamic Application Security Testing (DAST) tools. Organizations can import scanner results into Avi to identify vulnerable application endpoints. The WAF creates Positive Security rules for each identified vulnerability, restricting requests to known-good parameters without requiring changes to the protected application. This allows organizations to limit exposure to identified vulnerabilities while application-level remediation is underway.
-In 9.1, the Avi Cloud Console adds a Live Security Threat Intelligence service, which includes an Application Rules Service providing rules targeting known application vulnerabilities identified by CVE. The service covers over 5,000 applications and automatically synchronizes rule database updates, keeping CVE-based protections current without manual rule management. When the service is temporarily unavailable, Avi Controllers continue to operate using the cached rule database.
-For tracking and documentation, the Avi Application Security Report generates a downloadable PDF documenting WAF security findings and pre-check results, supporting both technical review and organizational documentation requirements.
-The WAF Recommendation system supports the tuning portion of the vulnerability management process by proposing configuration changes to address false positives, with reasoning and risk assessment accompanying each suggested change. WAF Log Analytics supports creation of exceptions at the group or rule level for false positive remediation. Alert Actions can trigger ControlScripts in response to system events, enabling automated remediation responses to detected conditions in place of manual administrator intervention.
-For platform-level vulnerabilities in the Avi Controller and Service Engines, Avi supports patch application and rollback. After upgrading to a new version, old root partitions that may contain packages with known CVEs can be removed to reduce residual exposure. If a patch introduces instability, rollback features allow operators to return the Controller and all Service Engine groups to the prior version via CLI commands (rollback system, rollbackpatch system) or the REST API (POST api/rollback). The REST API also supports non-disruptive SE-group-specific rollback, allowing selective rollback of individual Service Engine groups. Organizations can lock the Avi Controller Linux system to a specific OS version to avoid CVE scanner false positives from inactive, unused package versions.</t>
+          <t>VMware Avi Load Balancer (Avi) supports vulnerability detection for web applications through its Web Application Firewall (WAF) Dynamic Application Security Testing (DAST) integration. The Avi SDK includes a DAST vulnerability scanner script, delivered in the DAST directory on the Avi Controller, which integrates with OWASP ZAP Attack Proxy and Qualys Web App Scanning to assess web application vulnerabilities and drive virtual patching. When a DAST scan identifies vulnerabilities, the avi-iwaf-vpatch.py tool automates virtual patch creation by generating Positive Security location rules for each vulnerable URL and Positive Security rules for each supported issue type. This allows the WAF to block requests targeting known vulnerable application paths while underlying code remediation proceeds.
+In 9.1, the Avi Cloud Console adds an Application Rules service that provides rules specifically designed to block attacks on known application vulnerabilities, many correlated with CVE identifiers, and automatically updates those rules on the Avi Controller. This complements DAST-driven virtual patching with a continuously refreshed, CVE-mapped rule set covering known application vulnerability classes.
+The DAST integration has acknowledged limitations: it does not detect all cookie-related security issues, and some flagged vulnerabilities may require manual remediation rather than automated virtual patching. Organizations should validate scan results and supplement Avi's application-layer DAST capability with platform-level scanning of the Avi Controller infrastructure through VCF platform vulnerability management tooling.
+Avi also supports configuration error detection through its inventory fault monitoring system. The Controller's inventoryfaultconfig setting allows independent tracking of license faults, migration faults, backup scheduler faults, SSL profile faults, and deprecated API version faults, with alert generation on configured conditions. This supports detection of misconfigured components before they affect application delivery.
+The Avi Application Security Report consolidates security findings for a selected virtual service. The report includes ranked lists of top attack types such as SQL injection and cross-site scripting, lists of top attacking IP addresses, and trend summaries showing total and flagged requests. Reports can be generated through the Avi UI or the Avi Controller CLI and downloaded in PDF format, supporting auditor review and periodic vulnerability assessment documentation workflows.
+Organizations running Avi on VCF should also lock the Avi Controller Linux OS to a specific version to reduce false-positive CVE scanner findings that arise from inactive OS package versions present on the system but no longer in active use.</t>
         </is>
       </c>
     </row>
@@ -1961,22 +1936,15 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>VCF provides multiple layers of access control, identity federation, tenant isolation, and monitoring to mitigate risks associated with third-party access to infrastructure assets, applications, services, and data.
-VCF SSO integrates with federated identity providers through standards-based protocols, supporting SAML 2.0, OIDC, and AD/LDAP as authentication sources. LDAP-based directory services such as Active Directory are supported for identity management across the platform, including NSX Manager, which supports both Active Directory over LDAP and Open LDAP as identity sources. This allows organizations to extend their existing identity governance to VCF rather than maintaining separate credential stores for third-party users.
-Role-based access control enforces least-privilege principles across the platform. VCF local accounts support configurable roles such as superAdmin, and VCF Automation assigns host switch-level permissions through the Cloud Administrator group (Cloudadmin role). The administrators role in VCF Operations is restricted to specific users who need access to objects and actions across the entire environment. For Kubernetes workloads, vSphere Supervisor namespaces support role-based access control with EDIT, VIEW, and OWNER roles that grant specific privileges to users or groups. The Namespace Owner/Edit/View role scopes consumers of a vSphere Namespace to provisioning VKS clusters and vSphere Pods using kubectl, while vSphere Administrator and Supervisor Administrator roles have broader access to cluster and namespace resources. This layered role model restricts third-party access to specific workload boundaries.
-VCF Automation implements a provider-and-consumer model that separates the operators of services from the organizations that consume them. Partner services from external vendors are integrated through this model, where providers manage services and organizations consume the resulting business outcomes such as self-service provisioning of Kubernetes clusters, databases, and other resources. Service providers control the publication scope of service instances to selected organizations and decide which roles, rights bundles, and UI plug-ins to include when publishing services. Provider Consumption Organizations offer additional administrative capabilities on top of standard organizations, allowing provider administrators to provision workloads while maintaining separation from consumer tenants. This architectural separation limits third-party visibility and access to only the resources they need to operate.
-For third-party application integration, VCF Automation supports dedicated service accounts that automate access for third-party applications. Organizations can generate and issue API access tokens that applications use on their behalf, providing a controlled mechanism for programmatic access rather than requiring shared user credentials. The VCF Operations orchestrator presents an open architecture for plugging in external third-party applications, with integration points managed through the platform rather than through direct infrastructure access.
-Tenant isolation is enforced through VCF Automation Organizations, which provide secure infrastructure isolation, quotas, and chargeback across multiple tenants. Within each organization, further isolation exists at the project and namespace levels. IT teams and cloud service providers can monitor resource usage, control permissions, and provide managed services through these organizations while network isolation at the NSX segment level restricts lateral movement between tenants. An Enterprise Admin can share resources with projects in a controlled manner, making objects available for consumption only within designated boundaries. App isolation policies in VCF Automation allow deployments that require on-demand security groups to enforce vDefend firewall rules at the application level. Data-in-transit communications default to TLS encryption for platform services.
-VCF Operations monitors resource usage and policy compliance across the environment, providing visibility into third-party activity. VCF Operations supports firewall hardening that restricts network access to internal services, limiting the network paths available to third-party integrations. Service Discovery identifies permanent listening TCP ports and established UDP connections, and service discovery dashboards provide ongoing visibility into the services operating in the environment. VCF also provides capabilities to discover objects that are not compliant with a security standard, supporting ongoing risk identification for configurations affected by third-party access.
-VMware Private AI Services (PAIS) provides technical mechanisms that contribute to mitigating risks associated with third-party access to AI-related assets, services, and data. These mechanisms operate at the trust validation, authentication, authorization, and content approval layers.
-Trust Establishment for External Integrations
-PAIS uses a CA trust bundle to establish secure HTTPS communication with external services and databases. Administrators must import CA trust bundles for the OIDC provider, Private Harbor registry, content management systems used as data sources in Data Indexing and Retrieval, MCP servers providing tools for agents, and the database server when those entities are not supplied at activation. Without an explicitly configured CA trust bundle, PAIS will not establish connections to those services, so third-party integrations require deliberate administrative action rather than automatic open access. PAIS supports updating certificate content for trusted entities through the same trust bundle mechanism, allowing administrators to refresh trust material as provider certificates change.
-Access Control for Services and Data
-PAIS access is controlled through OIDC group-based authorization. User accounts must be members of specified authorized groups (configured via the authorizedGroups setting) to access the service, and the oidc-groups-claim setting controls which OIDC claim is consulted for group identification in the organization namespace. PAIS requires HTTPS-based communication for OIDC provider integration. SharePoint data sources used as Knowledge Base inputs require user name and password authentication, with support limited to SharePoint On-Premises deployments, so the credential and connectivity posture for that integration is explicit rather than implicit.
-Harbor Access and Model Storage
-The Model Gallery uses Harbor project access capabilities to restrict access to the sensitive data used to train and tune models. PAIS integrates with Harbor registries as a model storage backend, requiring authentication and certificate-based trust for model retrieval. These controls help administrators scope which users and workloads can push to or pull from a registry used by PAIS.
-Model Validation Before Deployment
-Before uploading a model to a PAIS Model Gallery, the platform recommends evaluating the model's performance and safety for the intended business use case, including examining inference requests for malicious behavior and performing hands-on functional tests. PAIS guidance directs administrators to distribute models within the organization that have been validated on a Deep Learning VM rather than models pulled from the Internet, which could contain malicious code or be tuned for malicious behavior. This workflow helps administrators verify third-party or externally sourced models before they become available for production use.</t>
+          <t>VCF provides several capabilities that support the identification and documentation of critical technology assets, applications, services, and data within a virtualized infrastructure.
+VMware vCenter maintains a real-time inventory of all managed objects, including hosts, VMs, clusters, datastores, and networks, and supports linking multiple vCenter instances for centralized inventory management. The vCenter inventory tracks multiple instances of ClusterComputeResource, ComputeResource, Datacenter, Datastore, DistributedVirtualSwitch, and Folder objects, providing a structured view of all infrastructure components. VCF Operations can export lists of resources, such as powered-off virtual machines, to CSV files for offline documentation and review.
+VCF Operations includes a Business Applications feature that allows administrators to group related infrastructure objects and assign business criticality classifications. Each Business Application can be tagged with a criticality level of Critical, Medium, or Low, with Medium as the default. The Object Summary card within VCF Operations displays details including the application's source, application tag, environment, and business criticality rating. This classification capability allows infrastructure teams to maintain a structured view of which applications and their underlying resources are most important to the organization.
+VCF Operations Service Discovery automatically detects running services across the environment. Service Discovery displays a list of all supported services that can be discovered and those currently discovered on VMs once configured. It also discovers performance metrics for individual service objects and service type objects, maintaining a catalog of known services and their relationships to underlying infrastructure. This automated discovery reduces manual effort in maintaining an accurate asset inventory.
+VCF Operations also provides alert definitions with configurable Impact and Criticality metadata. The Impact setting can be configured to values such as Risk to indicate potential problems, while the Criticality setting can be set to values like Immediate for proper alert prioritization. Alert notifications can be filtered by impact category and criticality level, helping teams classify infrastructure resources by their importance and focus attention on the most important infrastructure components. VCF Operations Insights data tracks resource capacity and can notify project owners of changes affecting their assets.
+VCF Automation provides complementary asset identification capabilities through its resource discovery and tagging system. The discovery process automatically identifies machines, storage volumes, networks, load balancers, and security groups for each cloud account region that has been added. Once discovered, these resources can be organized using tags that facilitate search and identification. Tags placed on cloud zones, network profiles, storage profiles, and individual infrastructure resources function as capability tags that define desired capabilities and support governance by expressing capabilities and constraints. Using logical, human-readable tags for storage, network, and infrastructure items is recommended to facilitate search and identification functions.
+VCF Automation organizes infrastructure through projects, which link users, catalog items, and IaaS resources to the locations where items are deployed. The Overview tab displays infrastructure and consumption metrics, providing a consolidated view of resource usage. Resource details views support filtering based on attributes such as project membership, enabling administrators to locate and review specific subsets of the infrastructure.
+Blueprints in VCF Automation allow users to model complex IT services by visually designing infrastructure components such as VMs, networks, storage, and software components. Resource objects in blueprints represent the infrastructure components and services that are provisioned and managed, providing an architectural record of how assets support business functions.
+Together, these inventory, discovery, classification, tagging, and visualization capabilities give operations teams the tools to identify, classify, and document the technology assets that support essential business functions. However, VCF provides the technical tooling for asset identification and classification rather than the organizational processes needed to define which assets are critical to the business mission. Establishing criticality criteria, maintaining asset documentation, and conducting periodic reviews of critical asset designations require organizational processes that operate alongside the platform's capabilities.</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -1986,12 +1954,13 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to mitigating risks from third-party access to organizational technology assets, applications, services, and data through network-level access controls, threat detection, and security posture reporting. Identity governance, authentication, and administrative access controls are handled by other VCF components (VMware vCenter, VCF SSO). vDefend enforces the network security boundary that constrains what third parties can reach once they have been granted access.
-vDefend enforces microsegmentation policies at the vNIC level, allowing administrators to define granular network access rules that restrict third-party workloads or connections to only the specific application tiers and services they require. Context-aware rules allow policies to incorporate workload-level attributes, limiting the network reach of third-party connections to defined sets of addresses, ports, and protocols. In multi-tenant VCF environments, the VPC Isolation with Essential Services strategy allows enterprise administrators to enforce strict inter-project isolation at the Distributed Firewall level while delegating more granular control to application owners within each project. This architecture is suited to environments where third-party development teams or external service providers operate within shared infrastructure, because Distributed Firewall policy at the project boundary can be set independently of what individual tenants configure inside their own VPCs.
-vDefend provides north-south traffic filtering at the perimeter of logical network segments. Enterprise administrators can enforce isolation between projects by denying inter-project communication except for specified infrastructure protocols, adding an enforcement point for controlling inbound and outbound access from external or third-party networks. This policy layer applies regardless of what routing exists at the NSX level, giving security teams a dedicated control plane for third-party network boundaries.
-vDefend IDS/IPS monitors east-west and north-south traffic for malicious activity, detecting exploitation attempts that may arise from compromised third-party connections. Signature rules support storing TLS and SSL certificates on disk for forensic analysis and threat investigation. Custom signature sources, including those derived from cybersecurity advisories, can be deployed to address threats specific to proprietary or custom applications that third parties introduce into the environment.
-Security Services Platform Security Segmentation capabilities identify risky application protocols, including HTTP, Telnet, FTP, TFTP, LDAP, POP3, and IMAP, in use across the environment. This flags workloads, including those operated by third parties, that transport data without encryption, and allows administrators to restrict or block them as part of the security baseline. The Security Segmentation Report identifies at-risk workloads across categories including Public Traffic, Obsolete OS, Risky Application Protocols, and Inter VDI Server Connections, providing a structured view of workload-level risk that is directly relevant to understanding the exposure introduced by third-party access. Application monitoring in Security Services Platform surfaces security risks identified across workloads, allowing administrators to take targeted remediation steps against risky or non-compliant third-party workloads.
-Security Services Platform certificate management supports importing CA bundles and web proxy certificates to establish trust for external service connections, including those used by the Malware Prevention Service. This controls which external services the platform can reach and provides a configuration point for managing trust relationships with third-party service endpoints.</t>
+          <t>VMware vDefend contributes to identifying and documenting critical technology assets through the Security Services Platform (SSP) and its Security Intelligence feature, which provide asset inventory, classification, and visualization capabilities oriented toward network security segmentation planning.
+Security Services Platform maintains a Platform Inventory of infrastructure assets, collecting status information for each asset including identification of assets that are timed out or out of sync. The inventory view provides filtering by Name and Status to locate specific infrastructure assets and identify their operational state. Tags assigned to each infrastructure asset are displayed for verification of tag assignments.
+Security Intelligence gathers infrastructure services and servers from CSV files and discovers additional services and servers based on traffic flows analyzed from ESX hosts. During CSV import, Security Intelligence parses and validates the content format and inventory asset data. Security Intelligence also maps discovered unique assets during segmentation analysis, including workloads, groups, IP addresses, distributed virtual port groups (DVPGs), segments, tiers, infrastructure services, and infrastructure servers.
+Security Services Platform identifies and publishes application assets, classifying them as either critical or regular applications. This criticality classification supports the identification of mission-critical technology assets within the environment. The inventory hierarchy spans regions, zones, environments, applications, and tiers, with each level displaying the total number of assets within its scope.
+Security Intelligence organizes discovered and imported assets into structured Asset Collections: groups, infrastructure assets, environments (such as Production, Non-Prod, DMZ, PCI, and Development), applications, and application tiers. The Environment Asset Collection maps security zones to the operational contexts that support business functions. Application Asset Collections group workloads that provide enterprise functionalities, linking infrastructure resources to the business services they support. The Infrastructure Asset Collection node covers core networking services that enterprise workloads depend on, including LDAP, DNS, NTP, and DHCP. An Unknown Asset Collection surfaces compute entities that are not in the NSX inventory but are present in the data center and communicating to NSX entities, supporting discovery of assets that should be formally inventoried.
+Security Intelligence Workload Classification can be set to "Infrastructure Service" to indicate that a compute entity provides infrastructure services such as DNS, DHCP, LDAP, and Syslog. Inferred infrastructure classifications for compute entities can be reviewed, accepted, or modified through the Monitor &amp; Plan &gt; Security Explorer interface.
+These capabilities contribute to the control but do not fully satisfy it. vDefend's asset identification is scoped to network security segmentation planning rather than the enterprise-wide technology asset catalog this control requires. Identifying all critical technology assets, applications, services, and data across an organization requires broader inventory and configuration management capabilities within VCF, such as VCF Operations business application views, VMware vCenter inventory exports, and VCF Automation project tagging, which provide the enterprise-wide asset catalog that vDefend's security-focused inventory complements.</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
@@ -2051,98 +2020,57 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>VCF provides multiple layers of data protection controls spanning encryption, storage resilience, backup and recovery, disaster recovery, centralized monitoring, and access management.
-For data at rest, vSAN encryption protects data on storage devices so that if a device is physically removed from the cluster, the data remains unreadable. At the virtual machine level, VM encryption protects NVRAM, swap (VSWP), and snapshot (VMSN) files, providing per-VM granularity independent of the underlying storage encryption. For data in transit, vSAN data-in-transit encryption protects data as it moves between hosts and file service inter-host connections within a vSAN cluster, with forward secrecy enforced. TLS protects data in transit between other VCF components. Both vSAN and VM encryption integrate with external Key Management Server (KMS) infrastructure for key lifecycle management, requiring a trust relationship established through certificate and key file exchange. VCF components use FIPS-validated cryptographic modules: NSX cryptographic modules are validated to FIPS 140-3 standards, vSphere uses FIPS-validated cryptographic modules matching the FIPS 140-2 standard, and VCF Automation runs in FIPS-compliant mode by default using FIPS 140-3 validated modules.
-vSAN implements erasure coding through RAID-5 storage policies, which split data into blocks with parity information to protect against component failures. vSAN includes failure indication and data rebuild mechanisms that detect storage failures and automatically reconstruct unavailable data. Virtual machines on vSAN datastores can be assigned storage policies that define specific data protection and performance characteristics, giving administrators granular control over how data is protected at the workload level.
-VCF supports backup methods for its management components at multiple levels. VMware vCenter file-based daily backups are configured through the vCenter Management Interface for each vCenter instance. vCenter file-based backup supports optional password-based encryption of backup files, and backup files are stored off-appliance on servers accessible via FTP, FTPS, HTTP, HTTPS, SFTP, NFS, or SMB. When vSphere Native Key Provider is configured, vCenter backups contain the Key Derivation Key and must be stored in a secure, access-controlled location. VCF Operations backups support both file-based and image-based methods. NSX Manager backup is configured automatically during the bring-up process. For vSphere Supervisor environments, control plane backup and restore can be performed from the Workload Management UI, and Supervisor control plane backup can also be included as an option in vCenter file-based backup schedules. vSAN Data Protection uses native snapshots stored locally on vSAN Express Storage Architecture (ESA) clusters to help recover virtual machines from operational failure or ransomware attacks.
-For Kubernetes workloads, VMware Kubernetes Service (VKS) provides dedicated data protection capabilities built into the VCF platform. VKS cluster node VMs are backed up through Supervisor state backup using the vCenter backup feature available in the vCenter Management Interface, so Supervisor state is covered by the same vCenter backup workflow used for the management plane. When data protection is activated for a VKS cluster, VKS cluster management installs the data protection extension, selected plugins, and Velero on the cluster; activation requires an Organization Administrator or Project Administrator role. Backup and restore operations are managed through the VCF Automation Tenant Portal under Manage &amp; Govern &gt; VCF Services &gt; Kubernetes Management &gt; Clusters &gt; Data Protection. Two backup methods are available: vSphere Plugin Snapshot performs block-level backup writing directly to object storage and is faster for workloads with large numbers of small files, while File System Backup operates at the file system level and supports incremental backups. The vSphere Plugin Snapshot method performs full backups on each run since it does not support changed block tracking, so organizations that require incremental backups should use the File System Backup method. Both methods support stateless and stateful workloads. Backup scope is configurable to the entire cluster, selected namespaces, or specific resources identified by label, and VKS cluster backups include file system backups in the restore by default. Velero 1.17 supports scheduled backups, allowing organizations to configure automated backup cadences. Backup repositories support deduplication, compression, and encryption of backup data. The Velero Plugin for vSphere backs up and restores both stateless and stateful applications running on vSphere Pods in the Supervisor. VKS Backup and Restore Hooks enable execution of pre- and post-operation scripts for granular control over the data protection lifecycle, supporting application consistency and custom automation during recovery. Cross-cluster restore is available through the Restore from another cluster option in the Data Protection tab of the VCF Automation Tenant Portal. Data protection account credentials are scoped to users with Organization Administrator or Project Administrator roles, restricting who can configure backup target locations; VCF Automation enables platform teams to create target locations pointing to self-provisioned storage environments, supporting both cloud-hosted accounts and on-premises endpoints. VCF Automation also supports snapshotting VM groups, where each member VM receives a distinct snapshot, and restoring a VM group snapshot restores each member of the group.
-Kubernetes cluster state is stored in etcd, and two backup methods are available for the etcd datastore: the built-in snapshot method and volume snapshot. The etcdctl snapshot save command creates a backup by specifying the endpoint, CA certificate, client certificate, and client key, providing authenticated access to the backup operation. Snapshots can be restored from a snapshot file or from a remaining data directory. During kubeadm upgrades, backup folders for etcd state and cluster manifests are written automatically to /etc/kubernetes/tmp with timestamped names, providing a recovery point in case of upgrade failure. Storage policy-based data management is available through Kubernetes StorageClass objects that reference vSphere storage policies via Storage Policy Based Management (SPBM); those policies may include encryption settings, allowing organizations to apply consistent encryption-at-rest requirements to persistent volumes through standard Kubernetes StorageClass configuration. CSI-based data protection for VKS requires a validated configuration between VKS and the underlying storage infrastructure.
-VKS clusters on the Supervisor also support the Kubernetes VolumeSnapshot API, which provides VolumeSnapshotContent and VolumeSnapshot resources as a native point-in-time snapshot mechanism for persistent volumes. Volume snapshots can be provisioned dynamically from a PersistentVolumeClaim using a VolumeSnapshotClass that specifies storage provider parameters and the deletion policy for snapshot content. Restoring from a snapshot is performed by creating a new PersistentVolumeClaim with the target VolumeSnapshot as its dataSource, referenced via the snapshot.storage.k8s.io API group. Kubernetes PersistentVolumes have a configurable reclaim policy; setting the policy to Retain preserves volume data in a Released state after the associated PersistentVolumeClaim is deleted, allowing administrators to recover or migrate the data before the underlying storage is reclaimed.
-Kubernetes Secrets provide a mechanism for storing sensitive configuration data separately from application code, reducing the risk of accidental exposure in container workloads. Applications consuming Secrets from environment variables or mounted volumes should avoid logging secret values in the clear or transmitting them to untrusted parties. Using short-lived Secrets helps limit the impact of accidental or intentional exposure. Kubernetes and applications can take additional precautions with Secrets, such as avoiding writing sensitive data to non-volatile storage.
-vSphere APIs for Data Protection provide an integration point for third-party backup software to perform nondisruptive full, differential, and incremental image backups using VMFS snapshot capabilities, without requiring virtual machines to be powered off or placing backup processing overhead on VMware ESX hosts. For virtual machines running supported Microsoft Windows operating systems, these APIs integrate with Microsoft Volume Shadow Copy Services (VSS) to maintain application consistency during backup operations.
-VMware Live Site Recovery extends data protection with orchestrated disaster recovery across sites. Replication can be configured with recovery point objectives as low as 60 seconds, with options for network compression, multiple point-in-time recovery, and automatic replication of new disks. vSphere Replication provides configurable RPO settings for VM-level replication to local or remote datastores. Application-level high availability and disaster recovery mechanisms combine real-time availability with sitewide disaster recovery, with data replication to secondary sites providing recovery options in case of catastrophic failure.
-VCF Operations Data and Site Resiliency Monitoring provides centralized visibility into data protection metrics across private clouds, enabling administrators to track the status of data protection controls from a single view. This monitoring layer helps organizations verify that their data protection configurations remain in place and functioning as expected.
-For Kubernetes workloads on VKS clusters, volume health status is reported through volumehealth.storage.kubernetes.io/messages annotations on PersistentVolumeClaims, giving administrators granular visibility into whether individual persistent volumes are accessible.
-Management of data protection settings is restricted through role-based access controls. VCF Operations uses privilege-based access controls that restrict visibility based on user roles, limiting which accounts can view sensitive operational data. For VKS clusters, managing data protection requires assignment of an Organization Administrator or Project Administrator role. VCF documentation includes storage security best practices covering securing access to storage devices, implementing storage encryption, and protecting virtual machine data as part of an overall data protection posture.
-Selecting which of these data protection mechanisms apply to specific datasets, defining protection policies and recovery objectives, and configuring the relevant features to match those decisions remain organizational responsibilities. VCF supplies the technical mechanisms; organizations define what to protect, to what recovery point, and with which retention and access controls.
-VMware Private AI Services (PAIS) contributes to data protection by applying access controls, authenticated connectivity, and credential management to AI workloads, model repositories, knowledge bases, and associated data assets that the platform handles.
-The Model Gallery uses Harbor project access capabilities to restrict access to the sensitive data used to train and tune models. PAIS integrates with Harbor registries as a model storage backend, requiring authentication and certificate-based trust for model retrieval. PAIS is also compatible with OCI-compliant registries from other vendors, so organizations using an alternate backend can apply equivalent registry-level access controls.
-Access to PAIS itself is gated by OIDC group-based authorization. Only user accounts that are members of the groups specified in the authorizedGroups configuration can access the service, and the OIDC group claim name is configurable to match the identity provider in use. PAIS uses a CA trust bundle for secure communication with external services and databases, and supports CA trust bundle management for secure connections with external registries and content management systems by uploading or referencing certificate files. VCF Automation Provider Management requires trusted certificate import for vCenter validation before integration with PAIS, restricting integration paths to validated endpoints.
-For retrieval-augmented generation, PAIS Knowledge Bases link to external data sources through stored credentials, scoping indexed-data retrieval to defined service identities, and Data Indexing and Retrieval handles automatic collection and indexing of updates from those linked sources over time. Personal access tokens generated from user account settings provide programmatic access to Knowledge Bases and data sources. SharePoint data sources for PAIS Knowledge Bases require user name and password authentication, with support limited to SharePoint On-Premises deployments.
-PAIS observability also flows through authenticated paths: the Grafana integration uses OIDC provider authentication for metrics visualization, and LLM traces can be sent to an OpenTelemetry Collector for monitoring.
-PAIS DSM database resource allocation is controlled through an infrastructure policy that defines the quality and quantity of resources the database can consume from vSphere clusters, with associated storage policies and VM classes. A default storage policy can be selected to define storage placement for the database in PAIS, and storage policy and VM class selections should be chosen to suit RAG workloads when the database supports RAG use cases.
-Organizations connecting external data sources or registries to PAIS should examine the capabilities and parameters of those integrations and approve only those suitable for use, since unreviewed connectors can affect what data models access or expose.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) contributes to data protection controls by providing network-level security mechanisms that protect data in transit and restrict unauthorized network access to systems where data is stored or processed.
-The vDefend distributed firewall (DFW) enforces microsegmentation policies at the vNIC level, restricting which workloads can communicate with data stores, databases, and application tiers. By segmenting the data center network into isolated security zones, vDefend limits the blast radius of a compromise and restricts lateral movement toward systems that hold sensitive data. Administrators define granular firewall rules based on workload identity, security tags, and application-level attributes, limiting access to data repositories to authorized services. Identity Firewall extends policy enforcement to user identity, allowing administrators to define access controls based on which authenticated user initiated the connection rather than solely the source workload, strengthening data access controls in environments with user-based authorization requirements. Security policies are defined, propagated, and enforced across Bare Metal servers through the Security Services Platform (SSP), extending microsegmentation protections beyond virtualized workloads to physical infrastructure connected to the environment.
-The SSP includes Security Intelligence, which identifies risky application protocols that transport data in clear text, including HTTP, Telnet, FTP, TFTP, LDAP, POP3, and IMAP. This visibility allows administrators to detect and remediate unencrypted data flows that could expose sensitive information in transit. Security Intelligence administrators can monitor traffic leakage between environments, establish exceptions, and implement lockdown protection rules to control inter-environment flows. Security Intelligence also enables administrators to generate policy recommendations and deploy them in monitor-before-enforcement mode, allowing observation of traffic patterns before applying restrictive rules. The SSP summary panel displays the number of services that are fully protected, partially protected, or not protected, giving administrators a dashboard view of segmentation coverage gaps across the environment.
-IDS/IPS profiles attach to Distributed Firewall and Gateway Firewall rules to inspect east-west and north-south network traffic for signatures and behaviors associated with data theft, command-and-control communication, and exploitation of vulnerabilities in data-handling services. In vDefend, IDS/IPS signature rules support storing TLS/SSL certificates on disk for forensic analysis and threat investigation, providing durable artifacts for post-incident review of potential data exfiltration events.
-Malware Prevention profiles attach to DFW and Gateway Firewall rules and can be configured to send files to the cloud for detailed analysis or to process files locally without cloud connectivity, accommodating environments with data-residency or air-gap requirements. Malware Prevention collects file analysis data including file hash submissions and assigns an Analyst UUID to each submission to track its analysis lifecycle. The Malware Prevention dashboard displays trends of malicious, suspicious, and suppressed file events across the data center, and file verdict filtering allows operators to focus on specific verdict categories such as malicious-only views.
-Network Detection and Response (NDR) anonymizes sensitive customer information when sharing telemetry data to cloud services, providing a built-in data privacy mechanism for environments that enable cloud-assisted threat detection.
-These network security controls complement the data-at-rest encryption, backup, replication, and access management capabilities provided by other VCF components. vDefend does not perform data encryption, classification, backup, or recovery itself, but it protects the network paths and access patterns through which data is stored, replicated, and retrieved.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides replication-based data protection for virtual machine workloads across sites. Protection groups allow administrators to organize virtual machines and datastores under consistent snapshot and replication policies at scale, covering both local recovery via vSAN snapshots and cross-site recovery via vSphere Replication or array-based replication. Protection group membership can be modified after creation, and virtual machines can be automatically enrolled for protection using storage tag selection on designated datastores, reducing manual overhead in maintaining protection coverage across a growing environment.
-PNR introduces an immutability mode for protection groups that, when enabled, prevents the data protection group from being modified or deleted. This mechanism allows administrators to safeguard protection configurations against inadvertent or unauthorized changes. PNR Health monitoring provides consolidated visibility into data protection service health, operation issues for local and replication snapshots, storage utilization, and protection group membership changes, giving administrators a current view of protection posture across the environment.
-Site Recovery Manager (SRM) integrates with vSphere Replication to provide orchestrated failover with configurable recovery point objectives, giving organizations control over acceptable data loss thresholds for protected workloads. PNR supports additional site topologies, including shared recovery site configurations where protected site resources are mapped to isolated datacenters, networks, folders, and datastores on the recovery site. Inventory mappings allow administrators to define resource configurations once and apply them consistently across protection groups.
-vSAN Snapshots and Replication is a native, integrated snapshot-based backup capability for virtual machines running on vSAN datastores, managed through the vSphere Client. It provides VM restore and clone operations from existing snapshots, supporting both rapid recovery from operational failures and ransomware recovery scenarios. Test failover operations allow administrators to validate that recovery configurations are functional before an actual recovery event occurs.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) provides several mechanisms that support data protection for managed database instances, covering PostgreSQL, MySQL, and SQL Server databases.
-The most direct contribution is DSM's automated backup framework, which administrators can enable on a per-database basis or through data service policies. When configured, DSM performs scheduled full and incremental backups of database content and stores them in S3-compatible object storage at a configurable backup location. Backup retention is configurable (backup-retention-period), and DSM retains backups of deleted databases until the configured retention period expires, supporting recovery from accidental deletion. For point-in-time recovery, DSM restores a backup to a newly created database VM with a user-specified name and datastore location, and can target the most recent timestamp or a specific point in time. DSM archives binary logs in backup storage as part of its backup protection mechanism. Administrators can also initiate manual on-demand backups of primary PostgreSQL databases to safeguard data before high-impact operations or as immediate protection after major changes. For PostgreSQL multi-site deployments, DSM performs a full backup automatically during a promotion event before resuming the regular schedule.
-Data service policies give administrators control over backup behavior across all databases governed by a policy. Policies can require that databases have automated backups enabled, allow users to opt in, or disallow automated backups entirely. The allowed-backup-locations setting in the data service policy restricts users to selecting from approved backup locations, reducing the risk of backup misconfiguration. Policies can be enforced across multiple tenants and across different namespaces and namespace labels, supporting consistent data protection posture in multi-tenant deployments. A Compliance tab on data service policies displays compliance reports and allows administrators to expand each policy violation to view the noncompliant database, data service, and namespace, giving administrators visibility into where data protection requirements are not being met. In 9.1, data service policies extend to SQL Server databases in addition to MySQL and PostgreSQL.
-DSM implements role-based access control that separates administrative and user-level database access. DSM Admins can create, monitor, and manage all data services in the environment; DSM Users can only manage and monitor the data services they own. This access model limits who can modify backup configurations and policy settings. Infrastructure policies govern which storage resources are available for database VMs, including CPU, memory, storage policies, IP pool, and VM classes, giving administrators control over the storage environment in which data resides.
-Control plane recovery requires that a Provider Backup Repo has been configured at installation time. If the Provider VM fails, the restore-provider command restores it to the latest timestamp. In the VCF Automation context, tenants can perform point-in-time restores directly through the VCF Automation UI, broadening restore access to self-service scenarios.
-One limitation applies: if an incremental backup in the backup chain is deleted, DSM cannot restore the full data; a successful restore from an incremental chain requires the last full backup and all following incremental backups. Organizations must protect the integrity of the backup chain through access controls on the backup storage.
-DSM provides configurable backup, recovery, and policy enforcement mechanisms for managed database instances. The broader data protection program requires organizational decisions about backup schedules, retention periods, backup storage security, and off-site management that DSM does not prescribe on its own.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N15" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides several application-layer mechanisms that support the implementation of data protection controls within a VCF deployment.
-At the transport layer, Avi performs TLS termination with configurable SSL/TLS profiles for connections between clients and virtual services. The SSL/TLS protocol at the Avi proxy secures data in transit by reducing the risk of unauthorized parties reading or modifying information transferred between end users and application workloads. SSL/TLS profiles are configurable through the Avi Controller UI under Templates &gt; Security &gt; SSL/TLS Profile. Management interface access is further restricted through configuration of allowed ciphers and HMACs for management sessions.
-Avi integrates with Hardware Security Modules (HSMs), including the Thales Luna (formerly SafeNet Luna) HSM, for cryptographic key storage and management. This allows organizations to store the private keys used in TLS termination and other cryptographic operations within a dedicated hardware key store rather than in software. The Avi Controller also stores sensitive configuration data encrypted in a local database, and backup files can be protected with a passphrase that encrypts the keys included in the backup. Backup and restore operations verify that the FIPS mode of the backup configuration matches the target controller environment.
-Avi's Web Application Firewall (WAF) applies both positive and negative security models to inspect and filter HTTP/HTTPS application traffic. WAF policies support ModSecurity rules for application protection and a Positive Security model that learns application behavior to define allowed request patterns. The Application Rules service, available through the Avi Cloud Console, provides WAF rules specifically designed to address known application vulnerabilities including CVE-tracked issues, with automatic updates to keep rules current. WAF configuration is accessible through the Controller UI under Templates &gt; Security &gt; WAF Policy.
-Avi DataScript provides a programmable layer for enforcing additional data protection behaviors at the proxy boundary. DataScripts are Lua-based scripted rules that allow inspection and manipulation of client HTTP requests and server HTTP responses, supporting content switching, redirection, header manipulation, and logging. DataScript can be used to enforce cipher suite policies by denying clients connecting with unsupported ciphers. DataScript also supports blocklist-based access control by checking client IP addresses against named IP groups and terminating connections from blocked sources while logging the violation. XML-based DataScript use cases can extract client identifiers from request payloads and compare them against configured string groups to restrict access to authorized clients.
-Access to Avi configuration objects is restricted through granular role-based access control (RBAC). Avi supports extended granular RBAC using label-based markers to restrict user permissions to specific resources based on key-value pair matching. The RBAC model differentiates Read and Write access across objects such as SSL/TLS Profiles, PKI Profiles, Authentication Profiles, IP Address Groups, and Health Monitors, allowing organizations to scope access to data protection-relevant configuration to authorized roles only. Roles can also be scoped to tenants through label group associations.
-These mechanisms address data protection at the application delivery layer. Broader organizational data protection controls, including data classification policies, data handling procedures, and data-at-rest protection beyond the Avi proxy boundary, require organizational governance and platform-level capabilities that Avi does not provide as an application delivery controller.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -2274,98 +2202,57 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>VCF provides multiple layers of data protection controls spanning encryption, storage resilience, backup and recovery, disaster recovery, centralized monitoring, and access management.
-For data at rest, vSAN encryption protects data on storage devices so that if a device is physically removed from the cluster, the data remains unreadable. At the virtual machine level, VM encryption protects NVRAM, swap (VSWP), and snapshot (VMSN) files, providing per-VM granularity independent of the underlying storage encryption. For data in transit, vSAN data-in-transit encryption protects data as it moves between hosts and file service inter-host connections within a vSAN cluster, with forward secrecy enforced. TLS protects data in transit between other VCF components. Both vSAN and VM encryption integrate with external Key Management Server (KMS) infrastructure for key lifecycle management, requiring a trust relationship established through certificate and key file exchange. VCF components use FIPS-validated cryptographic modules: NSX cryptographic modules are validated to FIPS 140-3 standards, vSphere uses FIPS-validated cryptographic modules matching the FIPS 140-2 standard, and VCF Automation runs in FIPS-compliant mode by default using FIPS 140-3 validated modules.
-vSAN implements erasure coding through RAID-5 storage policies, which split data into blocks with parity information to protect against component failures. vSAN includes failure indication and data rebuild mechanisms that detect storage failures and automatically reconstruct unavailable data. Virtual machines on vSAN datastores can be assigned storage policies that define specific data protection and performance characteristics, giving administrators granular control over how data is protected at the workload level.
-VCF supports backup methods for its management components at multiple levels. VMware vCenter file-based daily backups are configured through the vCenter Management Interface for each vCenter instance. vCenter file-based backup supports optional password-based encryption of backup files, and backup files are stored off-appliance on servers accessible via FTP, FTPS, HTTP, HTTPS, SFTP, NFS, or SMB. When vSphere Native Key Provider is configured, vCenter backups contain the Key Derivation Key and must be stored in a secure, access-controlled location. VCF Operations backups support both file-based and image-based methods. NSX Manager backup is configured automatically during the bring-up process. For vSphere Supervisor environments, control plane backup and restore can be performed from the Workload Management UI, and Supervisor control plane backup can also be included as an option in vCenter file-based backup schedules. vSAN Data Protection uses native snapshots stored locally on vSAN Express Storage Architecture (ESA) clusters to help recover virtual machines from operational failure or ransomware attacks.
-For Kubernetes workloads, VMware Kubernetes Service (VKS) provides dedicated data protection capabilities built into the VCF platform. VKS cluster node VMs are backed up through Supervisor state backup using the vCenter backup feature available in the vCenter Management Interface, so Supervisor state is covered by the same vCenter backup workflow used for the management plane. When data protection is activated for a VKS cluster, VKS cluster management installs the data protection extension, selected plugins, and Velero on the cluster; activation requires an Organization Administrator or Project Administrator role. Backup and restore operations are managed through the VCF Automation Tenant Portal under Manage &amp; Govern &gt; VCF Services &gt; Kubernetes Management &gt; Clusters &gt; Data Protection. Two backup methods are available: vSphere Plugin Snapshot performs block-level backup writing directly to object storage and is faster for workloads with large numbers of small files, while File System Backup operates at the file system level and supports incremental backups. The vSphere Plugin Snapshot method performs full backups on each run since it does not support changed block tracking, so organizations that require incremental backups should use the File System Backup method. Both methods support stateless and stateful workloads. Backup scope is configurable to the entire cluster, selected namespaces, or specific resources identified by label, and VKS cluster backups include file system backups in the restore by default. Velero 1.17 supports scheduled backups, allowing organizations to configure automated backup cadences. Backup repositories support deduplication, compression, and encryption of backup data. The Velero Plugin for vSphere backs up and restores both stateless and stateful applications running on vSphere Pods in the Supervisor. VKS Backup and Restore Hooks enable execution of pre- and post-operation scripts for granular control over the data protection lifecycle, supporting application consistency and custom automation during recovery. Cross-cluster restore is available through the Restore from another cluster option in the Data Protection tab of the VCF Automation Tenant Portal. Data protection account credentials are scoped to users with Organization Administrator or Project Administrator roles, restricting who can configure backup target locations; VCF Automation enables platform teams to create target locations pointing to self-provisioned storage environments, supporting both cloud-hosted accounts and on-premises endpoints. VCF Automation also supports snapshotting VM groups, where each member VM receives a distinct snapshot, and restoring a VM group snapshot restores each member of the group.
-Kubernetes cluster state is stored in etcd, and two backup methods are available for the etcd datastore: the built-in snapshot method and volume snapshot. The etcdctl snapshot save command creates a backup by specifying the endpoint, CA certificate, client certificate, and client key, providing authenticated access to the backup operation. Snapshots can be restored from a snapshot file or from a remaining data directory. During kubeadm upgrades, backup folders for etcd state and cluster manifests are written automatically to /etc/kubernetes/tmp with timestamped names, providing a recovery point in case of upgrade failure. Storage policy-based data management is available through Kubernetes StorageClass objects that reference vSphere storage policies via Storage Policy Based Management (SPBM); those policies may include encryption settings, allowing organizations to apply consistent encryption-at-rest requirements to persistent volumes through standard Kubernetes StorageClass configuration. CSI-based data protection for VKS requires a validated configuration between VKS and the underlying storage infrastructure.
-VKS clusters on the Supervisor also support the Kubernetes VolumeSnapshot API, which provides VolumeSnapshotContent and VolumeSnapshot resources as a native point-in-time snapshot mechanism for persistent volumes. Volume snapshots can be provisioned dynamically from a PersistentVolumeClaim using a VolumeSnapshotClass that specifies storage provider parameters and the deletion policy for snapshot content. Restoring from a snapshot is performed by creating a new PersistentVolumeClaim with the target VolumeSnapshot as its dataSource, referenced via the snapshot.storage.k8s.io API group. Kubernetes PersistentVolumes have a configurable reclaim policy; setting the policy to Retain preserves volume data in a Released state after the associated PersistentVolumeClaim is deleted, allowing administrators to recover or migrate the data before the underlying storage is reclaimed.
-Kubernetes Secrets provide a mechanism for storing sensitive configuration data separately from application code, reducing the risk of accidental exposure in container workloads. Applications consuming Secrets from environment variables or mounted volumes should avoid logging secret values in the clear or transmitting them to untrusted parties. Using short-lived Secrets helps limit the impact of accidental or intentional exposure. Kubernetes and applications can take additional precautions with Secrets, such as avoiding writing sensitive data to non-volatile storage.
-vSphere APIs for Data Protection provide an integration point for third-party backup software to perform nondisruptive full, differential, and incremental image backups using VMFS snapshot capabilities, without requiring virtual machines to be powered off or placing backup processing overhead on VMware ESX hosts. For virtual machines running supported Microsoft Windows operating systems, these APIs integrate with Microsoft Volume Shadow Copy Services (VSS) to maintain application consistency during backup operations.
-VMware Live Site Recovery extends data protection with orchestrated disaster recovery across sites. Replication can be configured with recovery point objectives as low as 60 seconds, with options for network compression, multiple point-in-time recovery, and automatic replication of new disks. vSphere Replication provides configurable RPO settings for VM-level replication to local or remote datastores. Application-level high availability and disaster recovery mechanisms combine real-time availability with sitewide disaster recovery, with data replication to secondary sites providing recovery options in case of catastrophic failure.
-VCF Operations Data and Site Resiliency Monitoring provides centralized visibility into data protection metrics across private clouds, enabling administrators to track the status of data protection controls from a single view. This monitoring layer helps organizations verify that their data protection configurations remain in place and functioning as expected.
-For Kubernetes workloads on VKS clusters, volume health status is reported through volumehealth.storage.kubernetes.io/messages annotations on PersistentVolumeClaims, giving administrators granular visibility into whether individual persistent volumes are accessible.
-Management of data protection settings is restricted through role-based access controls. VCF Operations uses privilege-based access controls that restrict visibility based on user roles, limiting which accounts can view sensitive operational data. For VKS clusters, managing data protection requires assignment of an Organization Administrator or Project Administrator role. VCF documentation includes storage security best practices covering securing access to storage devices, implementing storage encryption, and protecting virtual machine data as part of an overall data protection posture.
-Selecting which of these data protection mechanisms apply to specific datasets, defining protection policies and recovery objectives, and configuring the relevant features to match those decisions remain organizational responsibilities. VCF supplies the technical mechanisms; organizations define what to protect, to what recovery point, and with which retention and access controls.
-VMware Private AI Services (PAIS) contributes to data protection by applying access controls, authenticated connectivity, and credential management to AI workloads, model repositories, knowledge bases, and associated data assets that the platform handles.
-The Model Gallery uses Harbor project access capabilities to restrict access to the sensitive data used to train and tune models. PAIS integrates with Harbor registries as a model storage backend, requiring authentication and certificate-based trust for model retrieval. PAIS is also compatible with OCI-compliant registries from other vendors, so organizations using an alternate backend can apply equivalent registry-level access controls.
-Access to PAIS itself is gated by OIDC group-based authorization. Only user accounts that are members of the groups specified in the authorizedGroups configuration can access the service, and the OIDC group claim name is configurable to match the identity provider in use. PAIS uses a CA trust bundle for secure communication with external services and databases, and supports CA trust bundle management for secure connections with external registries and content management systems by uploading or referencing certificate files. VCF Automation Provider Management requires trusted certificate import for vCenter validation before integration with PAIS, restricting integration paths to validated endpoints.
-For retrieval-augmented generation, PAIS Knowledge Bases link to external data sources through stored credentials, scoping indexed-data retrieval to defined service identities, and Data Indexing and Retrieval handles automatic collection and indexing of updates from those linked sources over time. Personal access tokens generated from user account settings provide programmatic access to Knowledge Bases and data sources. SharePoint data sources for PAIS Knowledge Bases require user name and password authentication, with support limited to SharePoint On-Premises deployments.
-PAIS observability also flows through authenticated paths: the Grafana integration uses OIDC provider authentication for metrics visualization, and LLM traces can be sent to an OpenTelemetry Collector for monitoring.
-PAIS DSM database resource allocation is controlled through an infrastructure policy that defines the quality and quantity of resources the database can consume from vSphere clusters, with associated storage policies and VM classes. A default storage policy can be selected to define storage placement for the database in PAIS, and storage policy and VM class selections should be chosen to suit RAG workloads when the database supports RAG use cases.
-Organizations connecting external data sources or registries to PAIS should examine the capabilities and parameters of those integrations and approve only those suitable for use, since unreviewed connectors can affect what data models access or expose.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) contributes to data protection controls by providing network-level security mechanisms that protect data in transit and restrict unauthorized network access to systems where data is stored or processed.
-The vDefend distributed firewall (DFW) enforces microsegmentation policies at the vNIC level, restricting which workloads can communicate with data stores, databases, and application tiers. By segmenting the data center network into isolated security zones, vDefend limits the blast radius of a compromise and restricts lateral movement toward systems that hold sensitive data. Administrators define granular firewall rules based on workload identity, security tags, and application-level attributes, limiting access to data repositories to authorized services. Identity Firewall extends policy enforcement to user identity, allowing administrators to define access controls based on which authenticated user initiated the connection rather than solely the source workload, strengthening data access controls in environments with user-based authorization requirements. Security policies are defined, propagated, and enforced across Bare Metal servers through the Security Services Platform (SSP), extending microsegmentation protections beyond virtualized workloads to physical infrastructure connected to the environment.
-The SSP includes Security Intelligence, which identifies risky application protocols that transport data in clear text, including HTTP, Telnet, FTP, TFTP, LDAP, POP3, and IMAP. This visibility allows administrators to detect and remediate unencrypted data flows that could expose sensitive information in transit. Security Intelligence administrators can monitor traffic leakage between environments, establish exceptions, and implement lockdown protection rules to control inter-environment flows. Security Intelligence also enables administrators to generate policy recommendations and deploy them in monitor-before-enforcement mode, allowing observation of traffic patterns before applying restrictive rules. The SSP summary panel displays the number of services that are fully protected, partially protected, or not protected, giving administrators a dashboard view of segmentation coverage gaps across the environment.
-IDS/IPS profiles attach to Distributed Firewall and Gateway Firewall rules to inspect east-west and north-south network traffic for signatures and behaviors associated with data theft, command-and-control communication, and exploitation of vulnerabilities in data-handling services. In vDefend, IDS/IPS signature rules support storing TLS/SSL certificates on disk for forensic analysis and threat investigation, providing durable artifacts for post-incident review of potential data exfiltration events.
-Malware Prevention profiles attach to DFW and Gateway Firewall rules and can be configured to send files to the cloud for detailed analysis or to process files locally without cloud connectivity, accommodating environments with data-residency or air-gap requirements. Malware Prevention collects file analysis data including file hash submissions and assigns an Analyst UUID to each submission to track its analysis lifecycle. The Malware Prevention dashboard displays trends of malicious, suspicious, and suppressed file events across the data center, and file verdict filtering allows operators to focus on specific verdict categories such as malicious-only views.
-Network Detection and Response (NDR) anonymizes sensitive customer information when sharing telemetry data to cloud services, providing a built-in data privacy mechanism for environments that enable cloud-assisted threat detection.
-These network security controls complement the data-at-rest encryption, backup, replication, and access management capabilities provided by other VCF components. vDefend does not perform data encryption, classification, backup, or recovery itself, but it protects the network paths and access patterns through which data is stored, replicated, and retrieved.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides replication-based data protection for virtual machine workloads across sites. Protection groups allow administrators to organize virtual machines and datastores under consistent snapshot and replication policies at scale, covering both local recovery via vSAN snapshots and cross-site recovery via vSphere Replication or array-based replication. Protection group membership can be modified after creation, and virtual machines can be automatically enrolled for protection using storage tag selection on designated datastores, reducing manual overhead in maintaining protection coverage across a growing environment.
-PNR introduces an immutability mode for protection groups that, when enabled, prevents the data protection group from being modified or deleted. This mechanism allows administrators to safeguard protection configurations against inadvertent or unauthorized changes. PNR Health monitoring provides consolidated visibility into data protection service health, operation issues for local and replication snapshots, storage utilization, and protection group membership changes, giving administrators a current view of protection posture across the environment.
-Site Recovery Manager (SRM) integrates with vSphere Replication to provide orchestrated failover with configurable recovery point objectives, giving organizations control over acceptable data loss thresholds for protected workloads. PNR supports additional site topologies, including shared recovery site configurations where protected site resources are mapped to isolated datacenters, networks, folders, and datastores on the recovery site. Inventory mappings allow administrators to define resource configurations once and apply them consistently across protection groups.
-vSAN Snapshots and Replication is a native, integrated snapshot-based backup capability for virtual machines running on vSAN datastores, managed through the vSphere Client. It provides VM restore and clone operations from existing snapshots, supporting both rapid recovery from operational failures and ransomware recovery scenarios. Test failover operations allow administrators to validate that recovery configurations are functional before an actual recovery event occurs.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) provides several mechanisms that support data protection for managed database instances, covering PostgreSQL, MySQL, and SQL Server databases.
-The most direct contribution is DSM's automated backup framework, which administrators can enable on a per-database basis or through data service policies. When configured, DSM performs scheduled full and incremental backups of database content and stores them in S3-compatible object storage at a configurable backup location. Backup retention is configurable (backup-retention-period), and DSM retains backups of deleted databases until the configured retention period expires, supporting recovery from accidental deletion. For point-in-time recovery, DSM restores a backup to a newly created database VM with a user-specified name and datastore location, and can target the most recent timestamp or a specific point in time. DSM archives binary logs in backup storage as part of its backup protection mechanism. Administrators can also initiate manual on-demand backups of primary PostgreSQL databases to safeguard data before high-impact operations or as immediate protection after major changes. For PostgreSQL multi-site deployments, DSM performs a full backup automatically during a promotion event before resuming the regular schedule.
-Data service policies give administrators control over backup behavior across all databases governed by a policy. Policies can require that databases have automated backups enabled, allow users to opt in, or disallow automated backups entirely. The allowed-backup-locations setting in the data service policy restricts users to selecting from approved backup locations, reducing the risk of backup misconfiguration. Policies can be enforced across multiple tenants and across different namespaces and namespace labels, supporting consistent data protection posture in multi-tenant deployments. A Compliance tab on data service policies displays compliance reports and allows administrators to expand each policy violation to view the noncompliant database, data service, and namespace, giving administrators visibility into where data protection requirements are not being met. In 9.1, data service policies extend to SQL Server databases in addition to MySQL and PostgreSQL.
-DSM implements role-based access control that separates administrative and user-level database access. DSM Admins can create, monitor, and manage all data services in the environment; DSM Users can only manage and monitor the data services they own. This access model limits who can modify backup configurations and policy settings. Infrastructure policies govern which storage resources are available for database VMs, including CPU, memory, storage policies, IP pool, and VM classes, giving administrators control over the storage environment in which data resides.
-Control plane recovery requires that a Provider Backup Repo has been configured at installation time. If the Provider VM fails, the restore-provider command restores it to the latest timestamp. In the VCF Automation context, tenants can perform point-in-time restores directly through the VCF Automation UI, broadening restore access to self-service scenarios.
-One limitation applies: if an incremental backup in the backup chain is deleted, DSM cannot restore the full data; a successful restore from an incremental chain requires the last full backup and all following incremental backups. Organizations must protect the integrity of the backup chain through access controls on the backup storage.
-DSM provides configurable backup, recovery, and policy enforcement mechanisms for managed database instances. The broader data protection program requires organizational decisions about backup schedules, retention periods, backup storage security, and off-site management that DSM does not prescribe on its own.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides several application-layer mechanisms that support the implementation of data protection controls within a VCF deployment.
-At the transport layer, Avi performs TLS termination with configurable SSL/TLS profiles for connections between clients and virtual services. The SSL/TLS protocol at the Avi proxy secures data in transit by reducing the risk of unauthorized parties reading or modifying information transferred between end users and application workloads. SSL/TLS profiles are configurable through the Avi Controller UI under Templates &gt; Security &gt; SSL/TLS Profile. Management interface access is further restricted through configuration of allowed ciphers and HMACs for management sessions.
-Avi integrates with Hardware Security Modules (HSMs), including the Thales Luna (formerly SafeNet Luna) HSM, for cryptographic key storage and management. This allows organizations to store the private keys used in TLS termination and other cryptographic operations within a dedicated hardware key store rather than in software. The Avi Controller also stores sensitive configuration data encrypted in a local database, and backup files can be protected with a passphrase that encrypts the keys included in the backup. Backup and restore operations verify that the FIPS mode of the backup configuration matches the target controller environment.
-Avi's Web Application Firewall (WAF) applies both positive and negative security models to inspect and filter HTTP/HTTPS application traffic. WAF policies support ModSecurity rules for application protection and a Positive Security model that learns application behavior to define allowed request patterns. The Application Rules service, available through the Avi Cloud Console, provides WAF rules specifically designed to address known application vulnerabilities including CVE-tracked issues, with automatic updates to keep rules current. WAF configuration is accessible through the Controller UI under Templates &gt; Security &gt; WAF Policy.
-Avi DataScript provides a programmable layer for enforcing additional data protection behaviors at the proxy boundary. DataScripts are Lua-based scripted rules that allow inspection and manipulation of client HTTP requests and server HTTP responses, supporting content switching, redirection, header manipulation, and logging. DataScript can be used to enforce cipher suite policies by denying clients connecting with unsupported ciphers. DataScript also supports blocklist-based access control by checking client IP addresses against named IP groups and terminating connections from blocked sources while logging the violation. XML-based DataScript use cases can extract client identifiers from request payloads and compare them against configured string groups to restrict access to authorized clients.
-Access to Avi configuration objects is restricted through granular role-based access control (RBAC). Avi supports extended granular RBAC using label-based markers to restrict user permissions to specific resources based on key-value pair matching. The RBAC model differentiates Read and Write access across objects such as SSL/TLS Profiles, PKI Profiles, Authentication Profiles, IP Address Groups, and Health Monitors, allowing organizations to scope access to data protection-relevant configuration to authorized roles only. Roles can also be scoped to tenants through label group associations.
-These mechanisms address data protection at the application delivery layer. Broader organizational data protection controls, including data classification policies, data handling procedures, and data-at-rest protection beyond the Avi proxy boundary, require organizational governance and platform-level capabilities that Avi does not provide as an application delivery controller.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -2469,22 +2356,15 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>VCF provides secure baseline configurations for all major platform components, consistent with industry-accepted hardening standards. The VCF Security Baseline is a purpose-built document that builds on VCF security fundamentals to address frequently requested compliance standards, regulations, and frameworks. It is designed and validated to tailor security configurations without affecting VCF's ability to meet its design objectives. Organizations can use the VCF Security Baseline to evaluate both default and non-default configurations and to secure their environments in a compliance context.
-VCF Operations includes a consolidated out-of-the-box benchmark called the VCF 9 Security Baseline, which provides a ready-to-use compliance profile for evaluating the security posture of a VCF environment. This benchmark enables automated assessment of configurations against the documented baseline, helping maintain a consistent configuration across VCF components. ISO Security Standards compliance benchmarks are also available from the VCF Operations repository as a native pack, giving organizations the ability to measure their environment against internationally recognized hardening standards. Broadcom also provides DISA Security Technical Implementation Guides (STIGs) for VCF components, including vSphere 7.0 and vSphere 8.0 STIGs, which provide detailed instructions for securing and configuring systems to meet specific security requirements.
-Individual VCF components have their own security configuration guides that document hardening recommendations. The vSphere Security Configuration Guide provides best practices for securing VMware vCenter, including securing the installation, configuring access and authentication, defining roles and permissions, and enabling auditing and logging. VMware ESX host hardening covers authentication and authorization settings, disabling unnecessary services, enabling security features such as Secure Boot and Trusted Platform Module (TPM), and implementing network security measures. The vSphere Security Configuration Guide documents specific STIG-aligned values for the Security.PasswordQualityControlPwquality setting on ESX hosts, including parameters such as minlen=15, maxrepeat=3, maxclassrepeat=4, difok=4, and enforce_for_root. The NSX Security Configuration Guide provides recommendations for securing NSX components, including NSX nodes, NSX Controllers, and NSX Edge nodes, by configuring strong authentication, implementing role-based access control, and securing administrative access.
-VCF Operations also provides a Configure Host Security Config Data workflow that allows selective enforcement of host security hardening rules. Beyond security settings, vSphere Lifecycle Manager maintains a desired-state cluster image that defines the ESX base build, vendor add-ons, and firmware for every host in a cluster, so the software baseline stays consistent across hosts, and VCF Operations runs scheduled drift detection that flags configuration deviations from the desired state for remediation. Administrators can configure individual configuration elements under Enforce Options, enabling granular control over which baseline settings are applied and enforced across the environment. This supports reducing organizational and business risk by maintaining configuration consistency. vSphere Host Profiles provide an additional mechanism for automated and centrally managed host configuration baseline enforcement, capturing a reference host's configuration and applying it consistently across ESX hosts, covering memory, storage, networking, and other configuration aspects.
-For containerized workloads, VMware Kubernetes Service (VKS) includes preconfigured security policy templates. The Baseline security template provides a set of constraints that restrict known privilege escalations while maintaining compatibility with common containerized workloads.
-DISA STIGs for Supervisor and VKrs are available to guide hardening of the Supervisor control plane and individual VKS cluster releases, providing baseline security guidance at the same standard as the DISA STIGs applied to VCF infrastructure components. The VKS cluster management interface provides out-of-the-box security policy templates that mirror industry-standard Pod Security Standards profiles, including both Baseline and Restricted configurations. Custom VKS Cluster Management Security Policy templates are also available to fine-tune individual security context parameters and support governance controls tailored to specific organizational requirements.
-Pod Security Admission (PSA), enabled in VKr 1.25 and later, enforces pod security standards at the namespace level. Three policy profiles are defined: Privileged (unrestricted, for system-level workloads), Baseline (helps prevent known privilege escalations while allowing the default minimally specified pod configuration), and Restricted (heavily restricted, following pod hardening best practices). Three enforcement modes are available: enforce, warn, and audit. The podSecurityStandard field in the ClusterClass API encodes the intended security posture in cluster definitions, accepting these modes with specific policy versions and namespace exemptions so that baseline security configurations are applied consistently across VKS deployments. System namespaces including kube-system, tkg-system, and vmware-system-cloudprovider are excluded from pod security enforcement. The PSA admission controller can also be statically configured with default enforce, audit, and warn levels for unlabeled namespaces, so namespaces created without explicit labels still receive a defined security baseline. To support gradual policy adoption, audit and warn modes can be set to a stricter level such as restricted while enforce remains at baseline, giving administrators visibility into policy violations before full enforcement is applied. VCF Automation IaaS Resource Policies provide an additional enforcement point at the management layer, supporting requirements that Kubernetes clusters operate at a minimum baseline pod security level.
-Kubernetes-native kernel security mechanisms provide workload-level baseline hardening options. seccomp restricts the Linux kernel system call surface available inside containers using BPF-based profiles, and the RuntimeDefault seccomp profile provides a strong set of security defaults while preserving workload functionality. AppArmor and SELinux provide further kernel-level restrictions through default configurations that offer foundational protections. Kubernetes default RBAC role bindings should be reviewed as part of establishing a security baseline, as defaults may grant broader access than a hardened configuration requires. Isolating each workload in its own Kubernetes namespace allows tailored security policies to be applied per workload and restricts access to namespace-scoped resources such as ConfigMaps and Secrets.
-Harbor Registry, available as a standard package for VKS clusters, supports a controlled baseline for container artifacts entering the environment. Harbor provides vulnerability scanning, content trust, and policy-based replication, along with role-based access control and artifact security policies, supporting controlled management of the container image supply chain. For stand-alone virtual machines deployed in vSphere Supervisor environments, Content Libraries can distribute VM images created with current patches and required security settings that follow corporate security policies.
-VMware Private AI Services (PAIS) provides PAIS-specific declarative configuration mechanisms that organizations can use to define and apply baseline settings across the AI infrastructure stack on VCF.
-The primary mechanism is the PAISConfiguration custom resource. Private AI Services settings are declared in a YAML file compliant with the PAISConfiguration schema and applied with kubectl, giving administrators a single resource that captures observability, identity, and trust configuration for an organization namespace. Observability includes the spec.observability.prometheusRuntime section for Prometheus metrics collection with a configurable storage class and metrics retention period, and an llmTraces section for routing large language model traces to an OpenTelemetry Collector. The PAISConfiguration custom resource can be patched with kubectl patch and verified with kubectl get paisconfiguration, supporting baseline change control and drift detection at the AI service layer.
-Certificate trust is handled through the spec.clientTls.caBundleRefs section, which references ConfigMaps containing CA trust bundles. Private AI Services requires HTTPS trust bundles for the OIDC provider, the Harbor registry, content management systems hosting knowledge database data, and MCP servers that provide tools to models. Trust bundles can be organized per application, with periodic updates required before certificate expiration. Access scope is restricted through the authorizedGroups setting, which limits Private AI Services access to specified OIDC groups.
-Harbor registry distribution carries baseline controls for model and image artifacts. Replication rules support configurable filters, target namespace, and trigger mode, including a manual trigger mode, so administrators can align artifact replication with organizational policy for connected and disconnected sites. The Model Gallery uses Harbor project access capabilities to restrict access to sensitive training and tuning data. Air-gapped deployments capture the self-hosted registry URL and registry login credentials as part of the activation flow.
-Workload resource baselines are defined through SupervisorNamespaceClassConfig, which specifies per-zone CPU limits, CPU reservations, memory limits, and memory reservations for resource allocation across zones. GPU-capable VM classes can carry GPU reservations and be confined to a single zone or supervisor namespace, supporting isolation of GPU consumption to a specific tenant. A default storage policy selection in the Private AI Services quickstart defines storage placement and resources for the service database.
-Deep Learning VM (DL VM) baselines are captured through VCF Automation self-service catalog items that parameterize VM class, data disk size, user password, and optional SSH public key authentication for remote access. The DL VM OVF property config-json accepts a base64-encoded configuration file that controls DCGM Exporter metrics visibility through export_dcgm_to_public and JupyterLab authentication through enable_jupyter_auth, giving operators a consistent surface to define DL VM hardening parameters.
-Credentials supplied during Private AI Services activation, including the private container registry password and proxy password, are stored as secrets in VCF Automation rather than as plaintext configuration values, supporting credential hygiene as part of the deployment baseline.</t>
+          <t>VCF enforces password complexity, length, and lifespan requirements across its component stack, with each component providing configurable password policies.
+At the platform level, VCF uses the Linux PAM (Pluggable Authentication Module) framework to enforce default password complexity rules. The default policy requires passwords of at least 12 characters containing at least one lowercase letter, one uppercase letter, one digit, one special character, and at least five different characters. The PAM module limits password entry attempts to a maximum of three retries before returning an error. On VMware ESX hosts, the password complexity policy is enforced for the root user, helping maintain strong credentials on the hypervisor layer.
+VMware vCenter's built-in authentication service, VCF SSO, enforces a password policy for local domain accounts with a default password lifetime of 90 days, configurable through the VCF SSO password policy settings in vCenter. For users authenticated through external identity sources such as Active Directory, password restrictions, expiration, and account lockout are governed by the identity source domain rather than VCF SSO policies.
+NSX Manager and NSX Edge enforce password complexity through Linux PAM modules. Default requirements include a minimum of 12 characters (maximum 128), at least one lowercase letter, one uppercase letter, one numeric character, one special character, and at least five different characters. NSX Edge adds restrictions against dictionary words, palindromes, and monotonic character sequences of more than four. All of these parameters are configurable through the NSX Authentication Policy Settings or the NSX Manager API, including minimum and maximum password length, required count of uppercase, lowercase, special, and numeric characters, password uniqueness, and hashing algorithm. NSX Manager enforces a retry limit of three attempts when setting a new password. For password lifespan, NSX Manager supports configuring password expiration with a range from 1 to 9,999 days.
+VCF Operations applies password complexity requirements at multiple levels. The admin user account requires a minimum of 15 characters with at least one uppercase letter, one lowercase letter, one digit, and one special character. The default password strength policy allows configuration of the minimum password length starting at eight characters. The password policy settings are managed through Administration &gt; Global Settings &gt; User Access &gt; Password Policy, which provides controls for password strength, password change policy, and account lockout. VCF Operations locks user accounts based on the password lockout policy, with a default threshold of seven failed login attempts, or if a user enters an incorrect password three times within five minutes. VCF Operations for Networks locks a user account after five consecutive failed login attempts for 15 minutes.
+VCF Automation supports its own password policy system settings, including account lockout after a configurable number of invalid login attempts. The lockout interval specifying the duration before automatic unlock is also configurable. Provider administrators can unlock a user account manually without waiting for the lockout interval to expire. VCF Automation passwords require a minimum of 15 characters.
+VCF Operations provides centralized password lifecycle management for all VCF components. Administrators can rotate passwords on demand or schedule automatic rotation on a recurring basis. During rotation, VCF Operations generates a randomized password that conforms to the component's password policy and re-establishes the relevant component integrations automatically. The VCF Operations UI offers preset rotation intervals, and the API supports custom scheduling. VCF Operations also provides a password remediation capability through the Security &gt; Password management interface, allowing administrators to update service account credentials and synchronize passwords when they have drifted out of sync between components.
+The VCF API supports managing the local accounts global password policy in vCenter. The Invoke-GetLocalAccountsGlobalPolicy and Invoke-SetLocalAccountsGlobalPolicy operations allow administrators to retrieve and update the vCenter password policy programmatically through the vSphere Automation SDK for PowerShell.
+VCF documentation recommends setting passwords following a common set of requirements across all accounts. While individual components support different password parameters and defaults, administrators can align password policies across the environment to establish a consistent security posture. The combination of enforced defaults, per-component customization options, password expiration controls, and centralized rotation provides the mechanisms needed to enforce complexity, length, and lifespan requirements for password-based authentication throughout the VCF stack.</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -2494,13 +2374,11 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to secure baseline configurations within its network security domain by providing structured configuration management capabilities, predefined security profiles and strategies, and configuration integrity controls that align with industry-accepted hardening practices.
-vDefend supports draft configuration management with configuration locking to prevent multiple users from simultaneously opening and editing a manual draft, helping maintain configuration integrity and reducing the risk of conflicting changes to firewall policy. Role-Based Access Control (RBAC) in vDefend governs who can create or modify firewall policies, providing control over which administrators can alter the security baseline.
-In vDefend, five system-defined VPC Security Strategies are available for establishing security baselines across Virtual Private Clouds (VPCs): VPC Isolation, VPC Isolation with Essential Services, VPC External Connectivity, VPC Secure Connection, and NONE. These strategies are consumed through Security Profiles in VCF Automation, which are predefined configuration templates that define the default security posture for VPCs. VPC Security Strategies provide a declarative, consistent way to apply DFW security baselines across multiple VPCs within a project, and Project Admins are guided to select a pre-defined high-level security posture that enforces Secure by Default principles rather than manually configuring individual firewall rules. Security profiles can be applied to one or more VPCs simultaneously and updated as requirements evolve.
-vDefend provides predefined TLS Decryption Action Profiles with four settings: Balanced (default), High Fidelity, High Security, and Custom. These profiles are vendor-defined baseline configurations for TLS inspection behavior, giving organizations a documented starting point aligned with different security postures. TLS Inspection policies also support an Advanced Configuration option to lock policies, preventing multiple users from making concurrent changes to TLS inspection policy baseline settings.
-Security Services Platform validates configuration changes before implementation through a deployment wizard that conducts thorough validations to confirm configurations are correct and compatible. The platform enforces initial security policies that cannot be modified through the user interface after they have been published, providing an immutability mechanism for foundational policy baseline elements. Security Services Platform supports backup and restore of configuration data, and certificate consistency between backup and restored environments should be verified to maintain NDR sensor integrity.
-Security Services Platform's Bare Metal Security feature extends vDefend policy enforcement to physical servers, applying L3/4 security policies to bare metal infrastructure using the same policy model and management plane as virtualized workloads. Two default DFW rules are created when Bare Metal servers are onboarded to Security Services Platform, providing an immediate baseline posture for physical infrastructure. Security policies are defined, propagated, and enforced across Bare Metal servers with consistent application and monitoring.
-vDefend's configuration management capabilities operate within the network security layer. The broader secure baseline configuration program for VCF, including the VCF Security Baseline document, component hardening guides, DISA STIGs, and compliance scanning through VCF Operations, is managed at the platform level. vDefend contributes by maintaining its own secure defaults and configuration controls within the network security domain.</t>
+          <t>VMware vDefend (vDefend) enforces password complexity, length, and lifespan requirements for its management interface accounts, contributing to the organization's password-based authentication posture.
+Security Services Platform (SSP) is the centralized management console for vDefend. SSP enforces password policies for local user accounts: admin and audit user passwords require a minimum of 12 characters and a maximum of 128 characters, and must contain at least one uppercase letter, one lowercase letter, one numeric character, and one special character. The same complexity criteria apply during password changes and resets. Local user passwords are valid for 180 days; a notification banner appears in the SSP UI 30 days before expiration to prompt users to update their password. Installer user passwords are valid for 60 days. The License Hub component of SSP also enforces password complexity requirements during local password change operations.
+SSP supports integration with directory services, including Active Directory over LDAP and OpenLDAP. When remote users or remote user groups are configured through LDAP, SSP applies the password expiration settings configured in the directory service; password expiry for these accounts cannot be modified from the SSP UI. SSP uses Authelia, an open-source authentication and authorization server, to handle authentication requests, including two-factor authentication and single sign-on.
+For Identity Firewall, vDefend uses an LDAP password to authenticate connections to the directory service used for identity-based policy enforcement.
+vDefend is a network security product and not a general-purpose identity management system. Its management interfaces enforce password complexity, length, and lifespan policies for vDefend administrative access. Satisfying this control fully requires applying equivalent password policies across all systems within the organization's environment, which is an organizational responsibility beyond vDefend's scope.</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
@@ -2524,13 +2402,11 @@
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) contributes to secure baseline configuration management through its infrastructure policy framework, data service policy enforcement, and built-in secure defaults for authentication and certificate management.
-Infrastructure policies in DSM define the compute, storage, and networking resources for each database deployment, including the list of allowed VM classes and compatible storage policies. These policies are configured by DSM administrators and act as standardized, repeatable deployment baselines that database users must follow. When administrators configure infrastructure policies, they constrain the quality and quantity of resources that users can consume from vSphere clusters, establishing guardrails that support consistent deployments across the environment. Database cluster creation applies both infrastructure policies and storage policies that enforce isolation and resource constraints, reducing the risk of misconfiguration by individual users.
-Data service policies extend this baseline enforcement across multi-tenant deployments. DSM administrators can define and configure data service policies for various database services and enforce them across different tenants to maintain a consistent security and compliance posture. Data service policies constrain which infrastructure options can be applied to database instances. When DSM is integrated with VCF Automation, data service policies can be applied consistently across organizational units.
-DSM also ships with predefined secure defaults for database authentication. PostgreSQL databases on DSM use scram-sha-256 as the default password-based authentication method, as configured in the default pg_hba.conf entries stored at /pgsql/data/pg_hba.conf. Custom pg_hba.conf entries support scram-sha-256, reject, and cert authentication methods. TLS is enforced by default for database client connections, with an administrator-controlled option to relax enforcement via the postgrescluster-allow-non-ssl-system-users setting in the advanced-system-config ConfigMap within the dsm-system namespace.
-Certificate management is integrated into the database creation workflow and validates certificate chains for connections to external systems, including VMware vCenter. DSM introduces a stricter default certificate validation mode, the "latest" mode, that enforces cryptographic and KeyUsage validations for all DSM endpoints, including the Provider VM and data service clusters. Certificates uploaded to DSM are validated against FIPS 140-3 cryptographic standards, and uploads containing unsupported algorithms or parameters are rejected. Custom trusted root certificates must comply with FIPS requirements. DSM also verifies the SHA256 thumbprint of vCenter during initial configuration to confirm the management connection targets the expected endpoint. Custom certificate support allows organizations to replace the default DSM certificate with organization-issued certificates for both the Provider VM and database clusters. For self-service deployments using the DSM Consumption Operator, signature verification confirms package integrity before installation.
-DSM validates certificate chains using configured root CA certificates stored in ConfigMaps and supports private container registry configuration with CA certificate validation for air-gapped environments.
-Addressing this control fully requires organizational processes beyond what DSM provides directly. DSM does not include tooling to document baseline configurations in a compliance-ready format, map configurations to specific industry hardening standards, or audit deviations from defined baselines over time. Organizations should supplement DSM's policy and defaults framework with configuration management documentation, change tracking processes, and integration with compliance scanning tools to satisfy the full requirements of this control.</t>
+          <t>VMware Data Services Manager (DSM) enforces password complexity and length requirements for all local user accounts. Local user passwords must contain a minimum of 8 and a maximum of 20 characters, including at least one uppercase letter, one lowercase letter, one number, and one special character from the set (?!@#$%^&amp;*). These requirements apply both at account creation and at every subsequent password reset; DSM rejects any new password that does not satisfy all criteria before accepting the change. Administrators can set the force_password_change flag on individual local user accounts to require a password reset at the next login, supporting periodic credential rotation and post-provisioning hygiene workflows.
+The root account for the DSM provider VM carries its own complexity requirements: a minimum of 15 and a maximum of 32 characters, requiring at least one uppercase letter, one lowercase letter, one number, and one special character. These constraints are enforced during OVA deployment, so the appliance cannot be instantiated with a weak root credential. The root password expiry date must be set to a valid future date and cannot be configured to never expire, making root credential rotation mandatory. DSM checks root password status at regular intervals and generates a ROOT_USER_PASSWORD_EXPIRE_SOON alert when the credential is approaching expiration, giving administrators advance notice before a reset is required.
+For PostgreSQL database instances managed by DSM, the default host-based authentication (HBA) configuration applies the scram-sha-256 algorithm, a salted challenge-response mechanism that avoids transmitting cleartext passwords during authentication. Custom pg_hba.conf entries also default to scram-sha-256 as the password-based authentication method. Local user management passwords within the DSM platform are encrypted using PGP symmetric encryption with dedicated keys (PGCRYPTO_PASSWORD and PGCRYPTO_ALGORITHM).
+DSM supports both local user authentication and LDAPS-based directory service authentication for platform access. Local users are authenticated by validating the email address and password against DSM's internal store. When LDAPS is configured, password lifecycle management, including organizational complexity and lifespan policies, is delegated to the directory service. PostgreSQL and MySQL database instances can independently be configured for LDAP or Active Directory authentication, allowing database-level credential management to align with enterprise directory policies. For PostgreSQL, the Enable Directory Service Authentication toggle on the database creation form activates this integration when a default directory service is configured. Administrators should configure LDAPS where enterprise password governance policies must extend to database-level credentials, or rely on DSM's built-in local user password policy where directory integration is not used.
+For SQL Server database instances, DSM supports SQL User authentication with standard SQL Server logins and passwords. The DSM privileged service account used for automated SQL Server tasks must be configured with its password policy set to Never Expire to prevent service interruptions; administrators should account for this service account exception when reviewing password lifespan policies across DSM-managed database instances.</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
@@ -2540,14 +2416,13 @@
       </c>
       <c r="N19" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides several built-in mechanisms that support the development and application of secure baseline configurations for the application delivery layer.
-The SSL/TLS Profile system gives administrators a documented starting point for cryptographic configuration. Profile Templates define accepted SSL and TLS versions and ciphers in prioritized order, and can be associated with virtual services or the Controller itself. The Standard SSL/TLS Profile is suitable for typical deployments, while the System-Standard profile provides modern cipher suites for backend server re-encryption in Kubernetes environments managed through the Avi Kubernetes Operator (AKO). Avi includes a curated list of cipher suites considered reasonably strong for SSL/TLS configuration, and the documentation notes the trade-offs between security, compatibility, and computational expense when selecting profiles. The Service Engine disables unsafe legacy renegotiation by default, providing a built-in protocol hardening baseline that reduces the risk of protocol downgrade attacks.
-The System-Secure-HTTP application profile is a pre-configured baseline for securing HTTP virtual services. It enforces HTTPS, protects cookies, manages client IP handling, and controls protocol behavior, giving administrators a hardened starting point for web application delivery. Administrators can supplement these defaults with more granular settings through policies or DataScripts.
-For deployments requiring validated cryptographic modules, Avi Load Balancer implements FIPS 140-3 compliance, providing a cryptographic baseline aligned with the U.S. and Canadian government standard for cryptographic modules.
-The Avi Web Application Firewall (WAF) Positive Security model supports application-layer baseline configuration through rules that define allowed application behavior. Each rule supports Enable/Disable control, mode selection between Detection and Enforcement, and configurable Paranoia levels, allowing organizations to tune an application security baseline to their risk posture. The Positive Security Rule Updates feature can be enabled to activate additional configuration options for application security policies. The Cloud Console Application Rules service extends this with rules specifically designed to address known application vulnerabilities, including those with CVEs, and updates them automatically.
-For Kubernetes deployments, AKO uses Custom Resource Definitions (CRDs) to enable syntactical validation of configuration objects at creation time, which helps prevent invalid configurations from being deployed. The AKO L4 CRD Rule supports SSL profiles and PKI profiles for securing pool connections, allowing Kubernetes-native expression of Avi's cryptographic baseline settings.
-Certificate lifecycle management supports maintaining cryptographic baselines over time. Certificate Management Profiles support automated certificate renewal workflows, and the Trust Protection Platform integration can automatically handle certificate and chain certificate renewals by learning the mapping of virtual service names to their certificates.
-The organizational process of developing, documenting, and maintaining baseline configurations across all in-scope technology assets, including selecting appropriate profile settings, applying them consistently, and updating them as software versions and security guidance evolve, remains outside what Avi performs on the organization's behalf.</t>
+          <t>VMware Avi Load Balancer (Avi) enforces password-based authentication controls through the Avi Controller's administrative identity plane, addressing complexity, length, and lifespan for locally authenticated accounts.
+The Controller's strong password enforcement feature requires each password to contain at least one uppercase character, at least one lowercase character, at least one numeric character, and at least one special character from the allowed set. The Controller rejects passwords consisting of sequences of adjacent keyboard keys. These requirements apply to both newly created accounts and to existing accounts when a user changes their password. Complexity enforcement is controlled through the password_strength_check setting, which the Controller applies at the portal level regardless of the administrative interface used.
+The minimum permissible password length is configurable through the minimum_password_length setting. The Controller enforces a minimum of 8 characters by default; administrators can raise this threshold via the REST API or CLI. The Avi License Hub enforces stricter length requirements for its admin and audit accounts: a minimum of 12 characters and a maximum of 128 characters.
+Password expiration is enforced through user account profiles using the password_expiration_days setting. The Default-User-Account-Profile sets password expiration at 365 days. The Controller displays a notification banner in the UI 30 days before a password expires to prompt renewal. The expiration period is configurable per profile.
+Password history enforcement restricts users from reusing recent passwords by comparing proposed updates against a configurable list of previous password hashes. The history count is configurable from 1 to 10 previous passwords, with a default of 5.
+Locally authenticated users change their own password through the My Account menu, which requires entry of the current password before accepting a new one. Administrators can generate a random password for a local user account or input a new password manually during a password reset. User-initiated password recovery through the GUI is supported when SMTP email is configured.
+These controls apply to locally authenticated Avi Controller accounts. For administrators who authenticate against external directories such as LDAP, password complexity and lifespan are managed by those external directories.</t>
         </is>
       </c>
     </row>
@@ -2651,24 +2526,23 @@
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>VCF enforces logical access control permissions through role-based access control (RBAC) mechanisms across its component products, supporting the principle of least privilege at each layer of the platform.
-VMware vCenter implements a granular privilege model where privileges are fine-grained access controls that can be grouped into roles and then mapped to users or groups. The privileges themselves are defined by VMware on the objects and properties contained in the system and are fixed, meaning client applications cannot alter the underlying privilege definitions. The AuthorizationManager service controls access to specific server objects based on the permissions associated with each object, and the authorization model provides consistent security control regardless of operational context.
-vCenter ships with several predefined roles that embody different levels of access. The Read Only role grants only three system-defined privileges: System.Anonymous, System.View, and System.Read. vCenter also includes a No Access role, where users or groups assigned that role cannot view or modify the objects to which it applies. New users and groups receive the No Access role by default, so access must be explicitly granted rather than revoked. The operator role is the most restricted authorization level, allowing users to view information about vCenter but not alter its configuration. When a predefined role does not meet operational needs, administrators can define custom roles containing only the minimum set of required privileges. This custom role capability, combined with permission propagation to vSphere objects, enables organizations to tailor access to the exact scope needed for each user or group.
-Cryptographic operations privileges provide an additional layer of fine-grained access control. The default Administrator system role includes all Cryptographic Operations privileges, while a separate No Cryptography Administrator role supports all Administrator privileges except for cryptographic operations. Administrators can clone the No Cryptography Administrator role and create custom roles with only specific Cryptographic Operations privileges, limiting what users can do with virtual machine encryption and decryption. Only users who are assigned the Cryptographic Operations privileges can perform those operations.
-VCF Operations implements its own RBAC model where users can only perform the actions that their permissions allow. Each user must have a unique account with one or more roles assigned, and administrators can assign roles to user groups and restrict object access based on role permissions. Access rights are fine-grained, covering actions such as adding, editing, or deleting dashboards, and viewing, configuring, or managing objects. Privilege-based access control restricts users without appropriate privileges from viewing collected data for specific objects. The Access Control interface provides granular permission management through expandable category trees where administrators can apply or modify permissions for selected roles. A ReadOnly role is available that provides read-only access, restricting write actions such as create, update, or delete. The platform documentation recommends configuring both local VCF Operations users and vCenter users with only the privileges they need in the environment, rather than assigning overly permissive roles. vCenter roles and privileges cannot be viewed or edited from within VCF Operations, maintaining separation of privilege management between the two components.
-NSX implements role-based access control to restrict system access to authorized users by assigning users roles with specific permissions. NSX defines scoped roles including Network Admin, Network Operator, Security Admin, and Security Operator, where permissions within a project apply only within the scope of that project and not for the entire NSX system. When these roles are assigned in NSX, the scope can be set to all projects and VPCs, or to selected projects and VPCs, enabling fine-grained access boundaries across the networking layer.
-VCF Automation governs project access through predefined roles and supports role-based access control through group membership and role assignment management. System administrators with the Manage General ACL right can create, modify, and remove specific access control lists using the accessControls API, providing programmatic control over access permissions. The cloud_admin service role satisfies the minimum service role requirement for VCF Automation API access, while the Cloud Administrator group has host switch-level permissions, so administrative actions are scoped to defined capabilities.
-For Kubernetes workloads running on VMware Kubernetes Service (VKS) within VCF, access control operates at two layers: the vSphere Namespace layer and the Kubernetes cluster layer. At the namespace layer, vSphere Namespaces support three permission roles assigned to VCF SSO users and groups: Owner (full control including namespace deletion), Can Edit (provisioning and operating workloads), and Can View (read-only access to VKS cluster objects with no permissions mapped to Kubernetes roles inside the cluster). The VCF Consumption CLI enforces these role assignments: users without sufficient permissions on the vSphere Namespace cannot connect to Supervisor or VKS clusters as VCF SSO users, and the system returns an explicit "Error from server (Forbidden)" response that makes enforcement directly observable. Supervisor applies a role separation pattern where DevOps and Platform Operators receive non-admin or custom roles, while Developers receive read-only or no roles. Specific operations require explicit privilege grants beyond general administrative roles: adding Supervisor Services to VMware vCenter requires the Manage Supervisor Services privilege on the vCenter system, and administering content libraries for VKS clusters requires specific vSphere role permissions that must be individually assigned when using a custom role rather than the vSphere Administrator role. The Namespace Owner, Edit, and View roles do not have access to vSphere Cluster, vSphere Namespace Inventory, or vSphere Namespace resources, while vSphere Administrator and Supervisor Administrator roles have varying levels of access to these resources, maintaining separation of duties between platform and workload operations.
-Within VKS clusters, access control is defined through Kubernetes Role-Based Access Control (RBAC) using Roles, ClusterRoles, RoleBindings, and ClusterRoleBindings. These objects specify which API groups, resources, and verbs a subject (user, group, or service account) may act on, scoped either to a specific namespace or across the entire cluster. VKS RoleBinding subjects must contain either a VCF SSO user name or a VCF SSO group name in the name parameter to grant access, tying Kubernetes RBAC directly to the platform identity provider. For VKS clusters deployed on a custom ClusterClass with VKS 3.2.0 and later, RBAC permissions can additionally be granted to users authenticated through an external OIDC provider using ClusterRoleBinding objects that bind ClusterRoles to individual users identified by their OIDC identity or to groups from the OIDC provider. Built-in ClusterRoles support tiered access: the view ClusterRole grants read-only access to most namespace objects without permitting visibility into roles or role bindings, and the edit ClusterRole adds read/write access to most objects but does not permit modification of roles or role bindings, containing the reach of any single identity. Kubernetes RBAC includes a privilege escalation prevention mechanism at the API level: a user can create or update a RoleBinding only if they already hold all the permissions contained in the referenced role, and this restriction applies even when the RBAC authorizer is not otherwise active so that the check remains in force regardless of authorizer configuration. Where explicit delegation is required, administrators can grant the `bind` verb on a specific Role or ClusterRole to authorize a user to create bindings for that named role without requiring the user to hold all of its permissions; the `escalate` verb on roles and clusterroles in the rbac.authorization.k8s.io API group provides a parallel mechanism to authorize controlled role escalation when that operation is intentionally permitted. The Kubernetes documentation included in VCF recommends using specific resources and verbs rather than wildcard entries, enforcing least-privilege access to Secret objects through RBAC, and applying strict RBAC policies that limit access to system namespaces. Service accounts are governed by the same RBAC mechanism, allowing workloads to receive only the minimum permissions required to function correctly, and fine-grained role bindings to particular service accounts are preferred over broader grants. Administrators can scope IAM role trust policies to specific service accounts and namespaces to further constrain workload permissions.
-Pod Security Admission (PSA) provides workload-level enforcement within VKS clusters through three profiles: Privileged (unrestricted, allows privilege escalation), Baseline, and Restricted. The Restricted profile targets least-privilege pod execution by requiring non-root execution, limiting Linux capabilities, and blocking privilege escalation at the pod level. Pods can be further constrained through security contexts, where settings such as runAsUser, capabilities, seccomp, AppArmor, and readOnlyRootFilesystem restrict what container processes may do at runtime. Namespaces that permit privileged workloads should establish access controls that reflect the principle of least privilege. ValidatingAdmissionPolicy resources allow administrators to define fine-grained policy rules specifying which API groups, operations, and resources fall within the scope of enforcement, providing a declarative mechanism to express access control requirements across the cluster.
-The Secret Store service, available as a Supervisor Service, enforces its own RBAC layer with distinct roles for administrators, DevOps engineers, and application tenants, scoping sensitive data distribution to specific roles rather than making it broadly accessible to all cluster users. Harbor, available as a standard package on VKS clusters through VCF Services consumption, enforces role-based access control to manage access to container images and other artifacts stored in the registry. Argo CD, also available as a standard package, supports local account authentication with global RBAC policies that define role-based access control through policy rules and group mappings that control account permissions and resource access.
-VCF SSO supports multiple authentication methods including username token (signed and plaintext), X.509 certificate, and holder-of-key token authentication. Certificate-based authentication enables secure service-to-service communications within the platform.
-VCF provides the platform-level identity and role-based access control infrastructure on which VMware Private AI Services (PAIS) relies. Within that foundation, PAIS adds AI-specific service, data, and catalog access controls that restrict access to authorized users and groups across the AI workload layer.
-PAIS enforces access to model inference endpoints through OIDC group-based authorization configured in the PAISConfiguration custom resource. The authorizedGroups field specifies which identity provider groups are permitted to call PAIS; accounts outside the named groups are denied access. The OIDC integration is configured with issuer URL, client ID, and scopes that include openid, groups, and offline_access, so group membership is evaluated at the identity provider and carried into the service through standard OIDC group claims. The groups claim name itself is configurable, and PAIS supports Extra Audiences for additional OAuth 2.0 clients that PAIS will accept when validating the access token. Activating PAIS requires coordination with an OIDC provider administrator, making access configuration an explicit administrative act rather than a default-open posture.
-The Grafana observability interface for PAIS applies the same OIDC group model for role-based access. A role-mapping expression assigns the Admin role to users whose OIDC group claims match the configured pais-access-group attribute path, and the Viewer role to all other authenticated users. This two-tier assignment scopes administrative control of the observability platform to a designated group while keeping monitoring data accessible to authenticated PAIS users.
-PAIS model endpoints support authentication through a harbor-pull-secret-readonly credential that restricts access to container images stored in private registries, and PAIS integrates with Harbor registries as the model storage backend with authentication and certificate-based trust required for model retrieval. Harbor project-based permissions restrict access to ML model artifacts and training data stored in the Model Gallery; read-write access to a Harbor project is required to upload or modify models, and project membership is scoped to explicitly authorized users.
-PAIS catalog items in VCF Automation are shared with selected project members through project-based permissions. Users requesting AI catalog items must have permissions granted by organization administrators, and the organization administrator must assign the required user role before users can deploy deep learning VMs. VI administrators must have appropriate permissions on the vSphere cluster to deploy deep learning VM templates. This administrator-mediated model scopes AI infrastructure access to explicitly authorized principals. When running VMware vCenter 8.x, VCF SSO must be configured to access PAIS namespaces from VCF Automation; on vCenter 9.x the SSO configuration step can be skipped because the integration is already present.
-Knowledge Bases and linked data sources in PAIS use personal access tokens generated from user account settings for programmatic access, scoping API-driven retrieval to the issuing user. VCF Automation separates provider-level and tenant-level administrative operations through distinct credential scopes: a PROVIDER_ADMIN_ACCESS_TOKEN is required for provider-level operations such as registering vCenter instances, while a TENANT_ADMIN_ACCESS_TOKEN is scoped to organization administrator operations. This separation limits what any single credential can affect across the PAIS deployment.</t>
+          <t>VCF enforces role-based access control across all major platform components, restricting access to technology assets, applications, services, and data based on assigned roles with defined permissions. RBAC is applied consistently throughout the stack, covering compute management, networking, storage, operations management, automation services, and Kubernetes workloads.
+VMware vCenter provides fine-grained authorization through a permissions model that associates roles with users or groups on objects in the vCenter inventory hierarchy. Roles are sets of privileges, and vCenter defines three authorization levels: operator (read-only access to configuration, the most restricted level), administrator (read and write access to configuration but cannot manage user accounts, intended for users who alter vCenter configuration or exercise control functions), and super administrator (full control). When a predefined role is modified, the updated privilege set applies immediately to all users assigned that role. New roles are created with three default system-defined privileges (System.Anonymous, System.Read, System.View), and administrators add specific privileges to match the intended access level. vCenter also supports creation of custom roles with granular privilege assignment and permission propagation to vSphere objects in the inventory hierarchy.
+NSX implements RBAC by assigning users predefined roles with specific permissions. The platform includes 15 built-in roles: Enterprise Admin, Admin, Network Admin, Network Operator, Security Admin, Security Operator, Cloud Admin, Cloud Operator, Cloud Project Admin, Load Balancer Admin, Load Balancer Operator, VPN Admin, GI Platform Admin, NSX Platform Admin, and Support Bundle Collector. These roles follow the principle of least privilege, with each role carrying only the permissions needed for its functional area. NSX RBAC applies across multiple operational domains including inventory, plan and troubleshoot, and system management functions. NSX also supports project-scoped RBAC, where Network Admin, Network Operator, Security Admin, and Security Operator roles assigned within a project have permissions limited to that project's scope rather than the entire NSX system. This project-scoped model extends to VPCs and subnets within the NSX networking hierarchy. For organizations that need role definitions beyond the built-in set, NSX allows creation of custom roles tailored to specific operational requirements. Only an Enterprise Administrator can assign the role management permission to a custom role. NSX Federation extends RBAC to multi-site deployments, applying the same access control model across federated NSX instances. Principal identities, which are used for service-to-service authentication local to NSX, also support RBAC role assignment, so automated integrations operate under the same access control model as human users.
+VCF Operations enforces RBAC through the assignment of service roles to users and groups. Administrators configure role-based permissions through the Roles tab under Infrastructure Operations, where individual permissions can be selected or deselected to define what each role is authorized to do. The System Administrator role includes rights covering approvals, audits, certificates, datastores, edge clusters, integrations, LDAP settings, namespaces, proxy rules, system settings, tokens, and truststore operations. Administrative operations such as password management require authentication with a user assigned the ADMIN role. VCF Operations also defines its own roles within vCenter, with privileges named using a convention that appends the role to the product name (such as VCF Operations ContentAdmin Role and VCF Operations PowerUser Role). The PowerUser role has privileges to perform the actions of the Administrator role except for user management and cluster management. A further restricted PowerUserMinusRemediation role excludes remediation actions in addition to those limitations. A vCenter administrator assigns these roles to users, and VCF Operations maps vCenter users to the appropriate role.
+vSAN supports RBAC and permissions management for authentication and authorization of storage operations. The vSAN Security Configuration Guide provides guidance on configuring these role-based controls for storage infrastructure.
+VCF Automation governs access through multiple RBAC mechanisms at different scopes. At the organization level, rights bundles assign specific API permissions to roles including Organization Administrator, Organization Auditor, and Organization User. Group membership and role assignment are managed through the Access Control interface, and organization administrators can edit role assignments for groups at any time. At the project level, VCF Automation defines three distinct roles: administrators, members, and viewers, providing tiered access to project resources and operations. VCF Automation also governs blueprints, catalogs, content libraries, and custom entities through its role model. The Assembler Administrator role has read and write access to the entire user interface and API resources, while other roles have progressively narrower permissions.
+For Kubernetes workloads running on VMware Kubernetes Service (VKS), VCF enforces RBAC through two complementary control layers. At the vSphere layer, vSphere Namespaces assign three permission roles: Owner (full control including namespace deletion), Can Edit (provisioning and operating workloads), and Can View (read-only access). At the Kubernetes layer, the Kubernetes RBAC authorization framework governs access to all API server requests through four core objects: Roles define permissions scoped to a single namespace, ClusterRoles define permissions applying cluster-wide, and RoleBindings and ClusterRoleBindings associate those roles with authenticated subjects such as users, groups, or ServiceAccounts. Permissions are purely additive with no deny rules, and administrators can restrict access to individual resource instances by name using the resourceNames list in role rules.
+VKS clusters integrate with VCF SSO so that Kubernetes RoleBinding objects grant RBAC permissions directly to VCF SSO users and groups. This means the same identity provider that governs VMware vCenter access also governs Kubernetes cluster access, providing a consistent identity model across both the platform and workload layers. Cluster operators use kubectl or the Kubernetes API to assign role permissions to developers and other personas with defined responsibilities.
+Kubernetes RBAC also governs ServiceAccounts, which provide discrete identities for pods and automation processes. This separation allows human access and workload access to be governed independently, with each scoped to the minimum permissions required for its function. ServiceAccounts follow the principle of least privilege by receiving only the minimum set of permissions required to function correctly, and RBAC should be applied to Secret objects to enforce least-privilege access to sensitive data stored within namespaces.
+The Kubernetes RBAC API includes built-in controls against privilege escalation: the API prevents users from editing roles or role bindings to gain permissions beyond those they already hold, and this enforcement applies at the API level regardless of the authorization mode in use. Role-binding authority can be explicitly delegated by granting a user permission to perform the bind verb on a specific Role or ClusterRole, limiting the roles that identity can delegate to others.
+In multi-tenant VKS deployments, RBAC is the primary mechanism for isolating tenants within a shared cluster. Administrators use Role and RoleBinding objects at the namespace level to restrict each tenant's access to its assigned namespaces, and ClusterRole and ClusterRoleBinding objects to control access to cluster-level resources, blocking unprivileged users from crossing tenant boundaries.
+Supervisor services deployed on VKS clusters extend RBAC to their own access models. The Secret Store Supervisor Service enforces role-based access control across administrator, DevOps engineer, and application tenant roles, controlling who can manage and retrieve sensitive data. The Argo CD Supervisor Service implements RBAC through a configurable policy field using Casbin syntax, with the spec.rbac.policy setting defining role assignments and permission rules; policy rules (p rules) control account permissions including the ability to grant admin roles to specific local accounts, and group mappings (g rules) assign accounts to role groups.
+VMware Private AI Services (PAIS) provides role-based access control scoped to its AI services and AI workload delivery components. The central mechanism is OIDC group-based authorization for PAIS. When activating PAIS in an organization namespace, administrators populate the authorizedGroups setting with one or more OIDC group identifiers so that only users who belong to those groups can access the service. The OIDC configuration supports a configurable groups claim name through the oidc-groups-claim setting, with the groups claim carried in the Access Token and evaluated at access time. PAIS requires an OIDC provider configured as a public client application with Authorization Code and Refresh Token grant types, and it can be configured with one OIDC provider. Additional OAuth 2.0 client identifiers can be accepted by configuring Extra Audiences through the oidc-extra-audiences setting when the OIDC provider issues tokens for multiple audiences.
+PAIS extends the same identity model to the Grafana observability platform used for PAIS metrics. Grafana role assignment is configured through the grafana-oidc-role-mapping property using an expression such as contains(groups[*], 'pais-access-group') &amp;&amp; 'Admin' || 'Viewer', so OIDC group membership maps automatically to Grafana Admin or Viewer roles. PAIS uses the same OIDC provider for Grafana authentication that it uses for service access.
+For machine learning model storage, the Model Gallery uses Harbor project access capabilities to restrict access to the sensitive data used to train and tune models. PAIS integrates with Harbor registries as the model storage backend and requires authentication and certificate-based trust for model retrieval. PAIS is compatible with OCI-compliant registries from other vendors when deployed in a disconnected or air-gapped environment, and the project-scoped access controls apply to the chosen registry.
+Access to PAIS catalog items for GPU-accelerated VKS clusters and other AI workloads is governed through project-based permissions in VCF Automation. PAIS custom forms in blueprints can be modified to control user inputs at request time, scoping which configuration choices a requester can make when provisioning AI workloads. Knowledge Base data sources used by PAIS retrieval augmented generation require authenticated access to external repositories, including user name and password authentication for SharePoint On-Premises data sources and access keys with list and read permissions on the target bucket for Amazon S3 compatible stores. PAIS uses a CA trust bundle for secure communication with external services and databases.
+These PAIS-specific controls operate at the AI services and workload layer. Access to the underlying compute, storage, and networking infrastructure is governed by platform-level RBAC in VCF, including VCF SSO and VMware vCenter role assignments, and database-level access for vector and operational data is governed by Data Services Manager. PAIS adds service-level and workload-level RBAC for AI-specific assets on top of the VCF platform foundation rather than replacing those platform controls.</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -2678,14 +2552,12 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend enforces least-privilege access at the network layer through microsegmentation and granular firewall policy, and within its own management plane through role-based access control.
-At the network enforcement layer, vDefend (DFW) operates at the vNIC level, allowing administrators to define security policies that restrict workload-to-workload communication to only the specific traffic required. This microsegmentation model implements least-privilege networking by default-denying traffic between segments and requiring explicit allow rules for each permitted communication path. vDefend documentation recommends governance practices to avoid overly permissive rules such as "ANY/ANY/ANY ALLOW" to maintain a least-privilege security model.
-vDefend supports Identity Firewall, which enforces access controls based on user identity by creating rules that permit traffic from Active Directory (AD) groups to specific destinations while blocking other users from reaching those same destinations. Identity Firewall rules can match AD group membership to network traffic to enforce context-aware access control, including blocking SSH access for specific user groups. This capability supports user-identity-based least-privilege enforcement for Windows desktop environments.
-In 9.1, vDefend introduces Privileged Labels, a tamper-proof mechanism that anchors firewall rules to immutable labels. Workloads assigned a privileged label remain within their designated security groups, limiting the ability of unauthorized users to move workloads out of those groups to circumvent the intended firewall rules.
-Security Intelligence, integrated into the Security Services Platform (SSP), generates granular application-level rules that allow only authorized traffic between environments. Initial policy recommendations can be deployed while traffic is allowed but monitored, enabling administrators to verify that recommended rules do not disrupt legitimate operations before full enforcement. When a security policy is published, a rule is automatically generated to permit intra-application traffic, simplifying least-privilege policy deployment.
-VCF Automation includes a dedicated Firewall category under its role-based access control rights. Configuring security postures in VCF Automation requires the Organization Administrator role or a custom role granting VPC Security Profile Manage and View rights, limiting who can define or modify firewall security postures across VPC environments.
-Within the vDefend management plane, the Security Services Platform enforces role-based access control with five defined roles: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. Each role carries differentiated permissions across three levels: Full Access (which includes Create, Read, Update, and Delete permissions), Read (view only), and None. Role assignments support both individual directory-managed user accounts and remote user groups via LDAP. The Security Operator role, for example, has Full Access to view and download Rule Analysis results but no access to other Rule Analysis operations, restricting what each role can perform. Security Intelligence within the SSP implements its own role-based access control with five distinct roles using the same differentiated permission model, governing who can view, configure, or modify detection and policy functions.
-vDefend uses its own role-based access control to determine who can create or modify firewall rules, restricting unauthorized or unintended changes to security policy. The vDefend gateway firewall adds north-south traffic enforcement, applying least-privilege principles to traffic entering and leaving the virtualized environment.</t>
+          <t>VMware vDefend (vDefend) enforces role-based access control across its security management interfaces to restrict access to firewall policy administration, threat analysis functions, and monitoring capabilities based on assigned user roles.
+The vDefend distributed firewall (DFW) implements RBAC to control who can create or modify firewall rules, limiting policy changes to authorized personnel. Access to DFW monitoring features, including Firewall Insights, requires one of three designated roles: Enterprise Admin, Security Admin, or Security Operator. Rule Analysis operations within the platform are also role-gated across the five defined role types.
+Security Services Platform (SSP) implements RBAC with five defined roles governing access to platform operations: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. Each role carries differentiated permissions; Full Access grants create, read, update, and delete capabilities, while Read-only access is available for monitoring-oriented roles such as Auditor and Support Bundle Collector. Role assignments can be applied to individual remote users or to remote user groups managed through a directory service, allowing administrators to align vDefend access with existing organizational structures. Multiple roles can be assigned to a single user or group to meet varying operational requirements. SSP's RBAC model also applies to License Hub operations, restricting licensing management actions to authorized roles.
+Security Intelligence RBAC in 9.1 uses the same five-role model as SSP (Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector), aligning Security Intelligence access governance with SSP's permission model and providing consistent role boundaries across both the detection and platform layers.
+For organizations using VCF Automation for vDefend firewall management, VCF Automation provides a dedicated Firewall category under RBAC rights, controlling access to the management and viewing of DFW rules, Tenant Gateway Firewall policy, VPC Gateway Firewall policy, and VPC Security Profiles. This allows organizations to scope firewall administration rights independently of other VCF Automation capabilities, supporting separation of duties between network automation and security policy management.
+vDefend's RBAC controls complement the broader VCF RBAC model by restricting access to network security policy management independently of compute, storage, or platform configuration access. An administrator with VMware vCenter privileges does not automatically gain the ability to modify firewall rules or security analytics configurations unless explicitly granted the appropriate vDefend roles. This separation of duties between infrastructure administration and security policy management supports distinct team structures for network security management.</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
@@ -2723,15 +2595,14 @@
       </c>
       <c r="N21" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides a native role-based access control (RBAC) system on the Avi Controller that supports least-privilege access enforcement for all administrative operations on the application delivery plane.
-The Avi Controller RBAC model assigns each user a role that determines their level of access: write, read, or no access to individual resource types. Roles operate at the object level, with write access grantable to specific objects including Virtual Services, Application Profiles, SSL/TLS Certificates, and Certificate Management Profiles. This granular object-level permission model allows administrators to scope each user's access to only the resources required for their function.
-For more precise scoping, the Avi Controller supports Extended Granular RBAC using markers. Labels attached to Avi resources allow roles to restrict user permissions to a specific subset of objects within a resource type, rather than granting blanket access across all objects of that type. The allow_unlabelled_access parameter in the role object controls whether a role can access resources that do not carry a matching label, and the restrict_cloud_read_access field in controller properties further enforces label-based access on cloud objects. The Avi Controller also supports granular RBAC per field, which allows update permissions to be scoped to specific fields within an object while restricting changes to other fields.
-Auth Mapping Profiles enable integration with external identity directories such as LDAP, SAML, TACACS+, and OAuth/OIDC. Each profile maps external identity groups to specific Avi roles and tenants. The "Any Group or Any Attribute" fallback rule in an Auth Mapping Profile should be configured to the least-privileged role so that users not matched by a more specific mapping receive minimal access by default.
-The Avi Controller's service account for VMware vCenter integration follows a least-privilege model. The vCenter Cloud Connector requires a minimal set of permissions assigned to the vCenter user account. Integration between the Avi vCenter Cloud Connector and vCenter requires two roles: Avi-Global-Role with global privileges (assigned with the "Propagate to children" option to propagate permissions to all child objects) and Avi-Folder-Role assigned to the specific folder or folders containing Service Engine VMs in the vCenter inventory. The vCenter permissions required cover Change Configuration, Edit Inventory, Interaction, and Provisioning capabilities scoped to Service Engine management needs.
-The Avi Cloud Console enforces access control through two tiers: Full Access (User Administrator or Product Administrator role) and Read-Only (Site Access role), with differentiated permissions for license visibility, management, and administration operations.
-For Kubernetes environments, the Avi Kubernetes Operator (AKO) custom resource definitions (CRDs) can be governed by Kubernetes RBAC policies to restrict access to a defined group of users, supporting least-privilege enforcement on the Kubernetes control plane.
-The Avi Web Application Firewall (WAF) supports authorization rules that enforce path-based access control by evaluating client domain and request path conditions. When authorization rule conditions are met, access is allowed; otherwise, a 403 response is returned, restricting access to application paths based on defined policies.
-Organizations must define role structures and Auth Mapping Profile rules that reflect the least-privilege assignments appropriate to each administrative function. The RBAC mechanisms described here apply to the Avi application delivery plane; least-privilege enforcement across the broader VCF environment is handled by VCF's own access control systems.</t>
+          <t>VMware Avi Load Balancer provides a native, multi-tiered Role-Based Access Control (RBAC) framework that governs all administrative access to the Avi Controller. At the base level, Avi roles assign one of four privilege types to each resource category: Write (full create, read, modify, and delete access), Read (view-only access to configuration, health, and analytics data without modification capability), Assorted (a mixed access level combining permissions across specific operations), and No Access (no access to the resource at all, including the inability to read or list it). Roles are combined with tenants to define the complete authorization settings for each user, scoping what resources a user can interact with and what actions they may take.
+Beyond base privilege levels, the Extended Granular RBAC feature refines access using markers, which are key-value label pairs assigned to Avi objects. A role definition specifies that a user may access only objects bearing labels that match the role's marker set. The allow_unlabelled_access parameter controls whether a user can view objects that lack matching labels, allowing administrators to restrict visibility to labeled objects only. Label groups can be associated with tenants to enforce label-based access policies across the tenant boundary. Multiple label values can be mapped to a single key, enabling flexible classification schemes. This mechanism enables resource-level scoping across tenants and teams: for example, restricting a group of operators to only the virtual services labeled with their team's identifier, without granting visibility into other teams' objects.
+At the finest granularity, Avi implements sub-resource (field-level) RBAC, which scopes which specific fields within a configuration object a given user is authorized to modify. Sub-resource definitions can be combined so that a user can configure multiple fields or features within a single object while remaining restricted from updating others. Label-based permissions for cloud objects extend this field-level control to infrastructure resources managed by the Avi Controller. Virtual service configuration exposes RBAC directly: the RBAC tab in the Virtual Service advanced setup provides label-based access control for health monitors and associated objects, extending role enforcement down to individual service configuration items.
+For GSLB deployments, the Avi Controller enforces RBAC through role references such as Gslb_Group_Enabled and Gslb_Health_Monitor that can be assigned to user accounts with tenant-level scope. These role references apply to follower sites configured with federated JWT profiles, scoping which accounts can modify GSLB configuration.
+The Avi Controller applies RBAC within the License Hub, limiting which users can perform specific actions based on their assigned role.
+For deployments using the Avi Kubernetes Operator (AKO), the Avi Controller implements RBAC by assigning tenants and roles to user accounts at the Kubernetes or OpenShift cluster level. AKO Custom Resource Definitions (CRDs) can leverage Kubernetes RBAC policies to restrict which user groups can configure routing rules, extending the Controller's authorization model into the Kubernetes control plane.
+For deployments on Microsoft Azure, Avi integrates with Azure IAM to control which Azure identities have access to Avi Load Balancer resources hosted in Azure. Administrators can use built-in Azure roles such as Reader (read-only access) or Owner (full access), or define custom roles for finer control over specific resources.
+RBAC configuration is managed through the Users section of the Avi Controller UI. Roles are defined per resource type and then assigned to users within a tenant. Extended Granular RBAC markers are attached to individual Avi objects (virtual services, pools, health monitors, and others) and referenced in the role definition. Sub-resource RBAC is configured as part of the Extended Granular RBAC object, combining field-level restrictions as needed.</t>
         </is>
       </c>
     </row>
@@ -2753,95 +2624,57 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>VCF provides secure baseline configurations for all major platform components, consistent with industry-accepted hardening standards. The VCF Security Baseline is a purpose-built document that builds on VCF security fundamentals to address frequently requested compliance standards, regulations, and frameworks. It is designed and validated to tailor security configurations without affecting VCF's ability to meet its design objectives. Organizations can use the VCF Security Baseline to evaluate both default and non-default configurations and to secure their environments in a compliance context.
-VCF Operations includes a consolidated out-of-the-box benchmark called the VCF 9 Security Baseline, which provides a ready-to-use compliance profile for evaluating the security posture of a VCF environment. This benchmark enables automated assessment of configurations against the documented baseline, helping maintain a consistent configuration across VCF components. ISO Security Standards compliance benchmarks are also available from the VCF Operations repository as a native pack, giving organizations the ability to measure their environment against internationally recognized hardening standards. Broadcom also provides DISA Security Technical Implementation Guides (STIGs) for VCF components, including vSphere 7.0 and vSphere 8.0 STIGs, which provide detailed instructions for securing and configuring systems to meet specific security requirements.
-Individual VCF components have their own security configuration guides that document hardening recommendations. The vSphere Security Configuration Guide provides best practices for securing VMware vCenter, including securing the installation, configuring access and authentication, defining roles and permissions, and enabling auditing and logging. VMware ESX host hardening covers authentication and authorization settings, disabling unnecessary services, enabling security features such as Secure Boot and Trusted Platform Module (TPM), and implementing network security measures. The vSphere Security Configuration Guide documents specific STIG-aligned values for the Security.PasswordQualityControlPwquality setting on ESX hosts, including parameters such as minlen=15, maxrepeat=3, maxclassrepeat=4, difok=4, and enforce_for_root. The NSX Security Configuration Guide provides recommendations for securing NSX components, including NSX nodes, NSX Controllers, and NSX Edge nodes, by configuring strong authentication, implementing role-based access control, and securing administrative access.
-VCF Operations also provides a Configure Host Security Config Data workflow that allows selective enforcement of host security hardening rules. Beyond security settings, vSphere Lifecycle Manager maintains a desired-state cluster image that defines the ESX base build, vendor add-ons, and firmware for every host in a cluster, so the software baseline stays consistent across hosts, and VCF Operations runs scheduled drift detection that flags configuration deviations from the desired state for remediation. Administrators can configure individual configuration elements under Enforce Options, enabling granular control over which baseline settings are applied and enforced across the environment. This supports reducing organizational and business risk by maintaining configuration consistency. vSphere Host Profiles provide an additional mechanism for automated and centrally managed host configuration baseline enforcement, capturing a reference host's configuration and applying it consistently across ESX hosts, covering memory, storage, networking, and other configuration aspects.
-For containerized workloads, VMware Kubernetes Service (VKS) includes preconfigured security policy templates. The Baseline security template provides a set of constraints that restrict known privilege escalations while maintaining compatibility with common containerized workloads.
-DISA STIGs for Supervisor and VKrs are available to guide hardening of the Supervisor control plane and individual VKS cluster releases, providing baseline security guidance at the same standard as the DISA STIGs applied to VCF infrastructure components. The VKS cluster management interface provides out-of-the-box security policy templates that mirror industry-standard Pod Security Standards profiles, including both Baseline and Restricted configurations. Custom VKS Cluster Management Security Policy templates are also available to fine-tune individual security context parameters and support governance controls tailored to specific organizational requirements.
-Pod Security Admission (PSA), enabled in VKr 1.25 and later, enforces pod security standards at the namespace level. Three policy profiles are defined: Privileged (unrestricted, for system-level workloads), Baseline (helps prevent known privilege escalations while allowing the default minimally specified pod configuration), and Restricted (heavily restricted, following pod hardening best practices). Three enforcement modes are available: enforce, warn, and audit. The podSecurityStandard field in the ClusterClass API encodes the intended security posture in cluster definitions, accepting these modes with specific policy versions and namespace exemptions so that baseline security configurations are applied consistently across VKS deployments. System namespaces including kube-system, tkg-system, and vmware-system-cloudprovider are excluded from pod security enforcement. The PSA admission controller can also be statically configured with default enforce, audit, and warn levels for unlabeled namespaces, so namespaces created without explicit labels still receive a defined security baseline. To support gradual policy adoption, audit and warn modes can be set to a stricter level such as restricted while enforce remains at baseline, giving administrators visibility into policy violations before full enforcement is applied. VCF Automation IaaS Resource Policies provide an additional enforcement point at the management layer, supporting requirements that Kubernetes clusters operate at a minimum baseline pod security level.
-Kubernetes-native kernel security mechanisms provide workload-level baseline hardening options. seccomp restricts the Linux kernel system call surface available inside containers using BPF-based profiles, and the RuntimeDefault seccomp profile provides a strong set of security defaults while preserving workload functionality. AppArmor and SELinux provide further kernel-level restrictions through default configurations that offer foundational protections. Kubernetes default RBAC role bindings should be reviewed as part of establishing a security baseline, as defaults may grant broader access than a hardened configuration requires. Isolating each workload in its own Kubernetes namespace allows tailored security policies to be applied per workload and restricts access to namespace-scoped resources such as ConfigMaps and Secrets.
-Harbor Registry, available as a standard package for VKS clusters, supports a controlled baseline for container artifacts entering the environment. Harbor provides vulnerability scanning, content trust, and policy-based replication, along with role-based access control and artifact security policies, supporting controlled management of the container image supply chain. For stand-alone virtual machines deployed in vSphere Supervisor environments, Content Libraries can distribute VM images created with current patches and required security settings that follow corporate security policies.
-VMware Private AI Services (PAIS) provides PAIS-specific declarative configuration mechanisms that organizations can use to define and apply baseline settings across the AI infrastructure stack on VCF.
-The primary mechanism is the PAISConfiguration custom resource. Private AI Services settings are declared in a YAML file compliant with the PAISConfiguration schema and applied with kubectl, giving administrators a single resource that captures observability, identity, and trust configuration for an organization namespace. Observability includes the spec.observability.prometheusRuntime section for Prometheus metrics collection with a configurable storage class and metrics retention period, and an llmTraces section for routing large language model traces to an OpenTelemetry Collector. The PAISConfiguration custom resource can be patched with kubectl patch and verified with kubectl get paisconfiguration, supporting baseline change control and drift detection at the AI service layer.
-Certificate trust is handled through the spec.clientTls.caBundleRefs section, which references ConfigMaps containing CA trust bundles. Private AI Services requires HTTPS trust bundles for the OIDC provider, the Harbor registry, content management systems hosting knowledge database data, and MCP servers that provide tools to models. Trust bundles can be organized per application, with periodic updates required before certificate expiration. Access scope is restricted through the authorizedGroups setting, which limits Private AI Services access to specified OIDC groups.
-Harbor registry distribution carries baseline controls for model and image artifacts. Replication rules support configurable filters, target namespace, and trigger mode, including a manual trigger mode, so administrators can align artifact replication with organizational policy for connected and disconnected sites. The Model Gallery uses Harbor project access capabilities to restrict access to sensitive training and tuning data. Air-gapped deployments capture the self-hosted registry URL and registry login credentials as part of the activation flow.
-Workload resource baselines are defined through SupervisorNamespaceClassConfig, which specifies per-zone CPU limits, CPU reservations, memory limits, and memory reservations for resource allocation across zones. GPU-capable VM classes can carry GPU reservations and be confined to a single zone or supervisor namespace, supporting isolation of GPU consumption to a specific tenant. A default storage policy selection in the Private AI Services quickstart defines storage placement and resources for the service database.
-Deep Learning VM (DL VM) baselines are captured through VCF Automation self-service catalog items that parameterize VM class, data disk size, user password, and optional SSH public key authentication for remote access. The DL VM OVF property config-json accepts a base64-encoded configuration file that controls DCGM Exporter metrics visibility through export_dcgm_to_public and JupyterLab authentication through enable_jupyter_auth, giving operators a consistent surface to define DL VM hardening parameters.
-Credentials supplied during Private AI Services activation, including the private container registry password and proxy password, are stored as secrets in VCF Automation rather than as plaintext configuration values, supporting credential hygiene as part of the deployment baseline.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to secure baseline configurations within its network security domain by providing structured configuration management capabilities, predefined security profiles and strategies, and configuration integrity controls that align with industry-accepted hardening practices.
-vDefend supports draft configuration management with configuration locking to prevent multiple users from simultaneously opening and editing a manual draft, helping maintain configuration integrity and reducing the risk of conflicting changes to firewall policy. Role-Based Access Control (RBAC) in vDefend governs who can create or modify firewall policies, providing control over which administrators can alter the security baseline.
-In vDefend, five system-defined VPC Security Strategies are available for establishing security baselines across Virtual Private Clouds (VPCs): VPC Isolation, VPC Isolation with Essential Services, VPC External Connectivity, VPC Secure Connection, and NONE. These strategies are consumed through Security Profiles in VCF Automation, which are predefined configuration templates that define the default security posture for VPCs. VPC Security Strategies provide a declarative, consistent way to apply DFW security baselines across multiple VPCs within a project, and Project Admins are guided to select a pre-defined high-level security posture that enforces Secure by Default principles rather than manually configuring individual firewall rules. Security profiles can be applied to one or more VPCs simultaneously and updated as requirements evolve.
-vDefend provides predefined TLS Decryption Action Profiles with four settings: Balanced (default), High Fidelity, High Security, and Custom. These profiles are vendor-defined baseline configurations for TLS inspection behavior, giving organizations a documented starting point aligned with different security postures. TLS Inspection policies also support an Advanced Configuration option to lock policies, preventing multiple users from making concurrent changes to TLS inspection policy baseline settings.
-Security Services Platform validates configuration changes before implementation through a deployment wizard that conducts thorough validations to confirm configurations are correct and compatible. The platform enforces initial security policies that cannot be modified through the user interface after they have been published, providing an immutability mechanism for foundational policy baseline elements. Security Services Platform supports backup and restore of configuration data, and certificate consistency between backup and restored environments should be verified to maintain NDR sensor integrity.
-Security Services Platform's Bare Metal Security feature extends vDefend policy enforcement to physical servers, applying L3/4 security policies to bare metal infrastructure using the same policy model and management plane as virtualized workloads. Two default DFW rules are created when Bare Metal servers are onboarded to Security Services Platform, providing an immediate baseline posture for physical infrastructure. Security policies are defined, propagated, and enforced across Bare Metal servers with consistent application and monitoring.
-vDefend's configuration management capabilities operate within the network security layer. The broader secure baseline configuration program for VCF, including the VCF Security Baseline document, component hardening guides, DISA STIGs, and compliance scanning through VCF Operations, is managed at the platform level. vDefend contributes by maintaining its own secure defaults and configuration controls within the network security domain.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides configurable security baseline mechanisms for its replication and recovery infrastructure. The PNR appliance includes a security reference section that identifies configuration files containing settings that affect environment security, and PNR documentation establishes that secure operation depends on proper configuration and maintenance of the PNR server. The security reference also documents network port requirements, providing the technical specifications needed to develop and maintain secure baseline configurations for disaster recovery infrastructure.
-PNR includes a Configuration Import/Export Tool that captures the complete set of protection and recovery configuration settings, including server version, build number, local and remote site names, inventory mappings, placeholder datastores, advanced settings, and array managers. The tool supports both UI-based and scripted exports and can transfer configuration data without requiring credential entry when using the bundled generated script. This gives organizations a mechanism to document, back up, and restore known-good baseline configurations for their disaster recovery infrastructure. The underlying system configuration is stored in the va-configurator.xml file and is accessible through Advanced Settings on the Site Pair tab in the management interface, providing a defined location for baseline review and modification.
-The PNR appliance management interface allows administrators to configure appliance security settings after deployment. The Advanced Settings system provides privileged users with the ability to adjust default values governing protection and recovery features. When modifying the minimum protocol version for TLS, PNR requires that the change be applied consistently across all configuration occurrences in the system, supporting systematic baseline management for transport security settings.
-For cyber recovery deployments, PNR documentation recommends using standard VCF topology with separate workload and management domains to achieve better isolation and align with security best practices at the recovery site.
-Full compliance with this control requires an organizational baseline configuration management program, documentation practices, version control, and hardening tooling extending beyond what PNR provides directly.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) contributes to secure baseline configuration management through its infrastructure policy framework, data service policy enforcement, and built-in secure defaults for authentication and certificate management.
-Infrastructure policies in DSM define the compute, storage, and networking resources for each database deployment, including the list of allowed VM classes and compatible storage policies. These policies are configured by DSM administrators and act as standardized, repeatable deployment baselines that database users must follow. When administrators configure infrastructure policies, they constrain the quality and quantity of resources that users can consume from vSphere clusters, establishing guardrails that support consistent deployments across the environment. Database cluster creation applies both infrastructure policies and storage policies that enforce isolation and resource constraints, reducing the risk of misconfiguration by individual users.
-Data service policies extend this baseline enforcement across multi-tenant deployments. DSM administrators can define and configure data service policies for various database services and enforce them across different tenants to maintain a consistent security and compliance posture. Data service policies constrain which infrastructure options can be applied to database instances. When DSM is integrated with VCF Automation, data service policies can be applied consistently across organizational units.
-DSM also ships with predefined secure defaults for database authentication. PostgreSQL databases on DSM use scram-sha-256 as the default password-based authentication method, as configured in the default pg_hba.conf entries stored at /pgsql/data/pg_hba.conf. Custom pg_hba.conf entries support scram-sha-256, reject, and cert authentication methods. TLS is enforced by default for database client connections, with an administrator-controlled option to relax enforcement via the postgrescluster-allow-non-ssl-system-users setting in the advanced-system-config ConfigMap within the dsm-system namespace.
-Certificate management is integrated into the database creation workflow and validates certificate chains for connections to external systems, including VMware vCenter. DSM introduces a stricter default certificate validation mode, the "latest" mode, that enforces cryptographic and KeyUsage validations for all DSM endpoints, including the Provider VM and data service clusters. Certificates uploaded to DSM are validated against FIPS 140-3 cryptographic standards, and uploads containing unsupported algorithms or parameters are rejected. Custom trusted root certificates must comply with FIPS requirements. DSM also verifies the SHA256 thumbprint of vCenter during initial configuration to confirm the management connection targets the expected endpoint. Custom certificate support allows organizations to replace the default DSM certificate with organization-issued certificates for both the Provider VM and database clusters. For self-service deployments using the DSM Consumption Operator, signature verification confirms package integrity before installation.
-DSM validates certificate chains using configured root CA certificates stored in ConfigMaps and supports private container registry configuration with CA certificate validation for air-gapped environments.
-Addressing this control fully requires organizational processes beyond what DSM provides directly. DSM does not include tooling to document baseline configurations in a compliance-ready format, map configurations to specific industry hardening standards, or audit deviations from defined baselines over time. Organizations should supplement DSM's policy and defaults framework with configuration management documentation, change tracking processes, and integration with compliance scanning tools to satisfy the full requirements of this control.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N22" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides several built-in mechanisms that support the development and application of secure baseline configurations for the application delivery layer.
-The SSL/TLS Profile system gives administrators a documented starting point for cryptographic configuration. Profile Templates define accepted SSL and TLS versions and ciphers in prioritized order, and can be associated with virtual services or the Controller itself. The Standard SSL/TLS Profile is suitable for typical deployments, while the System-Standard profile provides modern cipher suites for backend server re-encryption in Kubernetes environments managed through the Avi Kubernetes Operator (AKO). Avi includes a curated list of cipher suites considered reasonably strong for SSL/TLS configuration, and the documentation notes the trade-offs between security, compatibility, and computational expense when selecting profiles. The Service Engine disables unsafe legacy renegotiation by default, providing a built-in protocol hardening baseline that reduces the risk of protocol downgrade attacks.
-The System-Secure-HTTP application profile is a pre-configured baseline for securing HTTP virtual services. It enforces HTTPS, protects cookies, manages client IP handling, and controls protocol behavior, giving administrators a hardened starting point for web application delivery. Administrators can supplement these defaults with more granular settings through policies or DataScripts.
-For deployments requiring validated cryptographic modules, Avi Load Balancer implements FIPS 140-3 compliance, providing a cryptographic baseline aligned with the U.S. and Canadian government standard for cryptographic modules.
-The Avi Web Application Firewall (WAF) Positive Security model supports application-layer baseline configuration through rules that define allowed application behavior. Each rule supports Enable/Disable control, mode selection between Detection and Enforcement, and configurable Paranoia levels, allowing organizations to tune an application security baseline to their risk posture. The Positive Security Rule Updates feature can be enabled to activate additional configuration options for application security policies. The Cloud Console Application Rules service extends this with rules specifically designed to address known application vulnerabilities, including those with CVEs, and updates them automatically.
-For Kubernetes deployments, AKO uses Custom Resource Definitions (CRDs) to enable syntactical validation of configuration objects at creation time, which helps prevent invalid configurations from being deployed. The AKO L4 CRD Rule supports SSL profiles and PKI profiles for securing pool connections, allowing Kubernetes-native expression of Avi's cryptographic baseline settings.
-Certificate lifecycle management supports maintaining cryptographic baselines over time. Certificate Management Profiles support automated certificate renewal workflows, and the Trust Protection Platform integration can automatically handle certificate and chain certificate renewals by learning the mapping of virtual service names to their certificates.
-The organizational process of developing, documenting, and maintaining baseline configurations across all in-scope technology assets, including selecting appropriate profile settings, applying them consistently, and updating them as software versions and security guidance evolve, remains outside what Avi performs on the organization's behalf.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -2945,25 +2778,12 @@
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>VCF provides a layered authentication infrastructure that supports secure management of authenticators across the platform's components and the Kubernetes workload consumption layer, though the broader organizational policies governing authenticator lifecycle management require processes and governance beyond what VCF itself provides.
-VCF Identity Broker integrates with a selected identity provider for user authentication, establishing trust through metadata exchange between the service provider and the identity provider. This centralized approach allows organizations to manage authenticators through their existing identity management systems rather than maintaining separate credential stores for each VCF component. VCF SSO provides a single sign-on environment where a user provides credentials once, and components in the environment perform operations based on the original authentication. Administrators can federate VMware vCenter with an enterprise identity provider, which enables multifactor authentication (MFA), automatic user provisioning and deprovisioning, and token-based authentication that reduces the risk of credential exposure. VCF SSO supports SCIM (System for Cross-domain Identity Management) for automating user identity exchange across identity domains, and named providers including Okta are supported through the identity provider federation mechanism. When configured for identity provider federation, the external provider handles all authentication mechanisms, including passwords, MFA, and biometrics, delegating full authenticator management to the organization's existing identity infrastructure. The Authorization Code grant type in VMware Identity Broker supports MFA workflows, while the Password OAuth 2.0 grant type is incompatible with MFA requirements, so organizations should use the Authorization Code flow when MFA is needed.
-VMware Kubernetes Service (VKS) extends this identity architecture to the workload consumption layer. VKS clusters support two authentication methods: VCF SSO and any OIDC-compliant external identity provider, including Okta, so identity lifecycle management, including onboarding, offboarding, and group membership changes, can remain in the organization's central identity system. Users authenticated through an external identity provider are granted Kubernetes RBAC permissions using the sso:&lt;username&gt;@&lt;domain&gt; naming convention in ClusterRoleBindings. Custom ClusterClass configurations allow organizations to authenticate developers against existing corporate identity systems. When provisioning clusters based on a custom ClusterClass, the authentication Secret can be configured with multiple JWT issuers to support distinct identity providers simultaneously, such as Keycloak for contractors and Microsoft Entra ID for employees. At the kube-apiserver level, VKS supports multiple authenticator types: client certificates, bearer tokens, an authenticating proxy, and HTTP basic auth. The --authentication-config file provides structured control, allowing multiple JWT authenticators each with a unique issuer URL and discovery URL, and CEL expressions to map claims to user attributes and validate claims. When multiple authenticator modules are active, the first to successfully authenticate a request short-circuits further evaluation, making authenticator order significant; Kubernetes hardening guidance recommends enabling as few authentication mechanisms as possible to simplify user management and reduce the risk of users retaining access after it is no longer needed. The kube-apiserver can also leverage existing authentication methods such as LDAP or Kerberos through plugins, and kubectl integrates with credential plugins for centralized operator credential management. The system:auth-delegator ClusterRole provides unified authentication and authorization flows for add-on API servers deployed into VKS clusters. Production VKS clusters should enable Kubelet authentication and authorization to restrict direct access to the kubelet API. For Windows node pools, VKS clusters support Group Managed Service Accounts (gMSA) for authenticating Windows nodes to Active Directory; gMSAs are managed by security groups that control password retrieval and delegation permissions, allowing Windows workloads to use Active Directory-managed identities.
-Standard packages deployable on VKS clusters extend authenticator management to workload-level services. Argo CD, available as a standard package, supports local account authentication with global RBAC policies and OIDC authentication for federated identity, allowing GitOps workflow access to be governed through the same identity infrastructure used for cluster access. The Harbor container registry package provides authentication and token management for artifact access, with role-based access control restricting image push and pull operations.
-VCF Operations integrates with VCF SSO for centralized authentication through an identity provider. NSX Manager can be configured to authenticate users from identity management providers or through a directory service such as Active Directory over LDAP or OpenLDAP. NSX authentication best practices include integrating with identity providers, enabling multi-factor authentication, and defining access controls based on user roles and permissions. NSX Manager requires authentication prior to establishing a management connection for administrative access. The VCF Automation Provider Management Portal supports authentication via local users and SAML users, and Organization Administrators use credentials configured during organization creation to access their respective organizations.
-For local accounts, each VCF component enforces password complexity and lifecycle policies. NSX Manager requires passwords of at least 12 characters with uppercase, lowercase, numeric, and special character requirements, enforced through Linux PAM modules. Each NSX user password has an expiration date tracked by NSX, with a default expiration period of 90 days. Password expiration is configurable between 1 and 9,999 days. VCF Operations enforces a minimum of 15 characters with similar complexity rules. VCF Automation passwords must also be at least 15 characters in length.
-VCF provides configurable account lockout policies across its components. VCF Operations locks accounts after five consecutive failed login attempts for 15 minutes. A separate policy locks VCF Operations accounts if a user enters an incorrect password three times within five minutes. VCF Automation supports account lockout in password policy system settings, which locks user accounts after a configurable number of invalid login attempts. VCF Automation also provides a configurable account lockout interval that specifies the duration before an account is automatically unlocked, and provider administrators can unlock a user account manually without waiting for that interval to expire.
-For service-to-service authentication, VCF uses certificate-based credentials. VCF SSO supports X.509 certificate authentication, and vCenter extensions can authenticate using loginExtensionByCertificate() with an extension key certificate. Provider management accounts authenticate using API access tokens that rotate after each use. VCF Automation provides service accounts with the same access restrictions as user API tokens, so service accounts cannot perform user management or create refresh tokens. NSX supports Principal Identity certificates for cloud management platform integration, requiring SHA256-based certificates with RSA/DSA message algorithm and 2048-bit or larger key sizes. At the Kubernetes layer, service account authentication uses bearer token secrets generated automatically for service accounts. Kubernetes hardening guidance recommends setting short lifetimes on certificates and automating their rotation, and recommends using an authentication provider that controls how long issued tokens remain valid; using short-lived Secrets helps detect or limit the impact of credential exposure. The system:masters group functions as a break-glass super-user group that bypasses the RBAC authorization layer and should be reserved for emergency access scenarios only.
-VCF Operations provides API endpoints for trusted certificate management and displays certificate expiration status for each workload domain through its Certificates tab. NSX supports non-disruptive certificate rotation in VCF and later, allowing certificate replacement without service interruption.
-VCF also provides visibility into authenticator usage through audit logging. User authentication details are viewable in VCF Operations, including user name, successful or failed authentications, and events such as user login and guest operation authentication. This logging supports detection of compromised or misused authenticators.
-While VCF provides the technical controls for authenticator strength, complexity, expiration, lockout, and rotation within its own components, as well as identity provider integration for MFA enforcement and centralized authentication, and the VKS consumption layer provides configurable multi-method kube-apiserver authentication, external identity provider integration, short-lived credential support, and gMSA for Windows workloads, the broader organizational policies for initial authenticator issuance, periodic credential rotation schedules, revocation upon personnel changes, and mapping authentication strength requirements to data classification levels require processes and governance outside VCF's scope.
-VMware Private AI Services (PAIS) provides authentication mechanisms specific to its AI infrastructure components, integrating with externally managed identity systems to control access to AI services, model endpoints, and training data.
-PAIS uses OIDC-based authentication as its primary access control mechanism. The PAISConfiguration custom resource configures the OIDC provider with issuerUrl, clientId, and scopes including openid, groups, and offline_access. Access is restricted to user accounts whose membership matches OIDC groups listed in the authorizedGroups field, and the Access Token carries a groups claim that PAIS validates against the authorized group list. The OIDC configuration also supports configurable group claim names and Extra Audiences for additional OAuth2.0 clients that PAIS will accept when validating the Access Token.
-The PAISConfiguration custom resource supports client TLS for outbound authentication to the OIDC provider and Harbor registry, configured through the worker.clientTls.caBundleRefs field. This binds certificate-based trust to identity provider and registry connections so that authentication exchanges are integrity-checked against approved CAs.
-Authenticator management for the Harbor registry that stores AI models and artifacts follows a credential-based pattern. The oras login command authenticates to a private Harbor registry using username and password credentials for artifact push operations, and docker login is used for pushing models to Harbor projects through the Model Gallery. Harbor project access capabilities restrict access to the sensitive data that is used to train and tune models. Model endpoints support authentication through harbor-pull-secret-readonly to control access to container images stored in private registries, and Harbor model retrieval requires certificate-based trust in addition to credential authentication.
-Internal service-to-service authentication is addressed at the component level. PAIS authenticates to the OpenTelemetry Collector using a Kubernetes Secret containing Authorization Bearer tokens and custom headers, and the LLM Traces flow uses the same pattern with semi-colon separated headers. The PAIS MCP server supports custom HTTP headers including User-Agent and Authorization headers for API authentication, and remote MCP servers can optionally use static authentication tokens. PAIS integrates with Grafana for metrics visualization using OIDC provider authentication.
-For Knowledge Base data sources, PAIS supports authentication to Confluence using either a username and password or a personal access token, configured according to the Confluence administrator's settings. Personal access tokens are generated from user account settings and used for programmatic access to Knowledge Bases and data sources. Microsoft SharePoint data sources require username and password authentication, with support limited to SharePoint On-Premises deployments.
-Deep Learning VMs deployed through self-service catalog items in VCF Automation, when configured with the PyTorch NGC software bundle, support optional JupyterLab authentication activation for interactive notebook access.
-The underlying user accounts, credential storage, password policies, and OIDC provider administration are owned by VCF SSO or an external identity provider. PAIS configures and enforces authentication using those systems but does not manage authenticator lifecycle itself.</t>
+          <t>VCF includes built-in password management capabilities that address the storage, protection, and lifecycle management of credentials for the components and service accounts within the platform. These capabilities function as an integrated credential manager for the VCF stack, though they do not replace a general-purpose enterprise password manager tool.
+VCF Operations provides a centralized password management interface accessible through the Security menu. This interface gives administrators a consolidated view of all managed accounts, their current statuses, and any remediation needs across the VCF fleet. Platform Operators can manage passwords for integrated components, including VMware ESX hosts, VMware vCenter, NSX, and other VCF components, from this single pane. A password management dashboard provides visibility into password status across the environment. Passwords for managed components can be rotated on demand or scheduled for automatic rotation on a recurring basis. The UI offers preset intervals for scheduled rotation, and the API supports custom intervals for more granular scheduling. During rotation, VCF Operations generates a randomized password based on the component's password policy and reestablishes the respective component integrations automatically. Passwords can also be retrieved programmatically through the VCF Operations API.
+NSX Manager provides its own password management capabilities for local user accounts through the user interface, CLI, and API. Administrators can reset user passwords through a Local Users interface, and the system supports auto-generated passwords for both Administrator and Auditor accounts. An API endpoint at System Administration &gt; Configuration &gt; Fabric &gt; Nodes &gt; User Management is available for programmatic password management operations. Additional VCF components such as HCX Manager support password updates for administrative accounts via CLI. VMware vCenter provides the `dir-cli password create` CLI command, which generates a random password that meets the platform's complexity requirements and can be used for service accounts or third-party solution users managed through VCF SSO.
+Password protection within the platform uses multiple mechanisms. NSX Manager local user passwords are secured using Linux/PAM libraries, which store hashed and salted representations in /etc/shadow. Other passwords stored within NSX Manager are encrypted using a random key held in the local file system, and all passwords across NSX Manager databases, configuration files, and log files are encrypted using strong one-way hashing with a salt. The platform documentation recommends that any password output from manual update operations be saved to a secure location with encryption for later retrieval. ESX hosts include a `Security.PasswordHistory` advanced system setting that specifies the number of previous passwords retained per user account to prevent reuse; this history check is enforced when passwords are changed through the VIM LocalAccountManager.changePassword API.
+VCF's standard web interfaces and APIs are compatible with external privileged access management and credential vaulting solutions. Organizations that use enterprise-grade password management tools can integrate them with VCF through its well-documented REST APIs and web-based management consoles, extending their enterprise credential management strategy to cover VCF infrastructure credentials alongside other systems.
+VCF's password management is scoped to its own credential ecosystem. The platform provides the tooling to manage, rotate, generate, store, and protect the passwords for VCF component service accounts and local user accounts. An organization's broader password management needs, including end-user credentials, application passwords, and credentials for systems outside the VCF stack, require a dedicated enterprise password manager solution that is outside VCF's scope.</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -3054,7 +2874,7 @@
 NSX Guest Introspection provides an agent-based framework that supports endpoint security within virtual machines. The Guest Introspection Agent must be installed and running in each guest VM, and logged-in users should not have the privilege to remove or stop the agent. This architecture enables third-party security solutions to inspect guest operating system activity without requiring agents to be installed directly on the hypervisor. The security and integrity of the guest operating system must be maintained for these integrations to function correctly.
 For container workloads, the VCF CLI supports cosign signature verification for container images through the imgpkg tool, which enables finding and copying cosign signatures. Image pull authentication through imagePullSecrets restricts container image pulls to authenticated private registries. Plugin discovery image signature verification is supported, with configurable public key paths for the cosign verifier. These capabilities help restrict deployment of images that have been tampered with.
 VCF Operations supports the deployment and monitoring of agents on endpoint virtual machines, with guest operation privileges required to install agents. Automated software update capabilities in vCenter help keep systems current with security patches, reducing the window of exposure to known malware exploits.
-For organizations that deploy VMware vDefend as an add-on to VCF, distributed malware prevention capabilities become available. The NSX Application Platform hosts the Malware Prevention for vDefend feature, which can be deployed from the Local Manager UI in NSX Federation environments. When host clusters are activated for Distributed Malware Prevention, a service virtual machine (SVM) is deployed on each host to perform malware scanning. vDefend also supports IDS/IPS capabilities alongside distributed malware prevention. The DistributedMps runbook is available to verify the health of the Malware Prevention Service pipeline and diagnose issues such as protection not working on a particular VM or certain files not being scanned.
+For organizations that deploy VMware vDefend, a separately licensed advanced service, distributed malware prevention capabilities become available. The NSX Application Platform hosts the Malware Prevention for vDefend feature, which can be deployed from the Local Manager UI in NSX Federation environments. When host clusters are activated for Distributed Malware Prevention, a service virtual machine (SVM) is deployed on each host to perform malware scanning. vDefend also supports IDS/IPS capabilities alongside distributed malware prevention. The DistributedMps runbook is available to verify the health of the Malware Prevention Service pipeline and diagnose issues such as protection not working on a particular VM or certain files not being scanned.
 Malware prevention activities generate log data for audit and forensic purposes. The Malware Prevention for vDefend feature writes log files that can be used for troubleshooting and security monitoring, and remote logging can be configured on the malware prevention SVMs for centralized log collection.
 VMware Private AI Services (PAIS) includes model validation capabilities that scan machine learning model files for malicious content before they are accepted into a Model Gallery. The validation runs as a sandbox process on Deep Learning VMs and covers integrity verification through hash code checking, malware scanning, serialization attack scanning, and inference behavior testing with NVIDIA Triton Inference Server. Both the malware and serialization checks run as part of the validation workflow required before a model can be uploaded to a Model Gallery and made available to downstream model endpoints, knowledge bases, or AI agents.
 Machine learning model files are a category of artifact that traditional endpoint security tools may not inspect. Serialized models in formats such as Python pickle files can carry executable payloads that activate when an application or researcher loads the model. The PAIS Model Gallery intake workflow treats this upload boundary as a security checkpoint, requiring each artifact to pass hash, malware, serialization, and inference behavior tests before it is published for use. PAIS guidance also directs organizations to distribute only models that have been validated internally on a Deep Learning VM rather than pulling artifacts directly from the Internet, where models may contain malicious code or be tuned for malicious behavior. The validation is operated by MLOps engineers, who confirm that onboarded models meet the organization's security, privacy, and technical requirements.
@@ -3149,15 +2969,17 @@
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>VCF provides technical capabilities that support several phases of the incident handling lifecycle, though the organizational preparation, process governance, and manual intake elements require processes and structures outside the platform.
-For preparation, VCF Operations supports the configuration of notification rules with detailed incident field mappings, including incident state, resolution codes, impact, urgency, priority, severity levels, and assignment groups. The ServiceNow Management Pack can be configured with parameters such as callerId, propagateAlertUpdates, retrieveIncidentUpdates, and incidentReopenState, allowing organizations to establish incident handling workflows before events occur. These configuration options allow teams to define how incidents are categorized, prioritized, and routed in advance of any actual incident.
-For automated event detection, VCF Operations correlates events from monitored infrastructure components and delivers them as faults. Events are ranked by severity from Info through Warning, Critical, and Immediate, and notification rules trigger actions based on incident state changes. VCF Operations can automatically create incidents in ServiceNow through the Service-Now Notifications plug-in, with structured information including the caller, category, subcategory, and business service. This integration bridges the gap between infrastructure monitoring and organizational incident tracking systems. VCF Operations also combines Diagnostic Findings with VCF Health to detect and predict issues, which helps reduce mean time to resolution. VMware vCenter alarms provide additional automated detection, triggering script execution, SNMP traps, email notifications, or API calls when infrastructure conditions exceed defined thresholds.
-For analysis, the Troubleshooting Incident Page displays information related to the entity under investigation, including traffic and flows on the entity, past incidents created for that entity, status, root cause metrics, and closing remarks. Operators can flag metrics and mark specific metrics as root cause during investigation. The Notes section on each incident allows users to add observations that are visible to anyone who opens the session, which supports collaborative analysis across team members. vCenter Events record user and system actions on inventory objects and can be used for forensic analysis and auditing of activity in the virtual environment, providing an audit trail for incident investigation. Diagnostic Findings consolidates log-based and property-based findings with specific resolution recommendations and links to knowledge base articles, helping analysts identify known issues by matching log patterns and property-based signatures against a library of diagnostic rules. Log Assist can generate log bundles and automatically attach property-based diagnostic findings data to support cases. VCF Operations also integrates with ServiceNow, allowing incidents to flow into existing ITSM workflows for structured triage.
-For containment, vCenter supports isolating affected workloads through VM power state changes and network reconfiguration. VMware vDefend (a separate product that extends VCF's networking foundation) provides more targeted containment through quarantine policies that automatically isolate VMs based on security events while preserving forensic access for investigation. Physical containment, network isolation decisions, and cross-system coordination during active incidents depend on processes and authority structures that exist outside the platform.
-For eradication, VCF Operations maps out-of-the-box workflows to recommendations and associates them with specific alerts, enabling automated remediation of known conditions. Diagnostic Findings helps operators find and resolve known issues using diagnostic rules and signatures, with recommended fixes based on industry-standard best practices.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a host failure, with admission control policies that reserve capacity for failover. Proactive HA integrates with hardware vendor monitoring to detect degrading components and evacuate workloads before failure occurs. vSphere Fault Tolerance provides continuous availability for workloads that require zero-downtime protection during failover. VCF Operations maintains a summary view of all incidents with status tracking, entity counts for in-progress incidents, and counts of top root causes for visibility into the overall state of incident resolution.
-VCF Operations also provides a centralized incident list displaying all incidents with their status and key details, with edit, share, and delete actions for incident lifecycle management. Incident tracking captures state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation, which is a structured audit trail for each incident. The Guided Network Troubleshooting feature automatically maintains a list of the 20 most recently modified incidents within a selected scope for continuity across investigation sessions.
-While VCF Operations provides tooling for detection, analysis, and remediation of infrastructure incidents, several aspects of the six-phase incident handling lifecycle require organizational processes beyond what the platform provides. Preparation requires documented incident response plans, team roles, and communication procedures. Manual incident report intake requires organizational channels and triage processes. Containment decisions require human judgment and authority structures. A formal incident response program that incorporates VCF's technical capabilities into broader organizational processes is necessary to address all six phases.</t>
+          <t>VCF provides multiple layers of integrity checking for software, firmware, and configurations across the platform stack, from hardware boot validation through ongoing operational monitoring.
+At the hardware level, VCF supports Secure Boot, Trusted Platform Modules (TPM), and Intel Trusted Execution Technology (TXT) to validate system firmware and boot integrity. VMware vCenter can retrieve the TPM event log for configuring firmware trust with an attestation service or validating boot-time TPM measurements, and APIs are available to list configured TPM devices and endorsement keys on each host. The hypervisor enforces code signing to restrict execution to authorized code. Each vSphere Installation Bundle (VIB) has an associated acceptance level, controlled through the Host-Image-Profile-Acceptance-Level setting, and VIB signature validation uses a cryptographic checksum to confirm that each package was produced by its authorized author.
+vSphere Lifecycle Manager (vLCM) is the primary tool for software and firmware integrity validation. Administrators define a desired software specification for each cluster, and vLCM compares the committed specification against each host to identify drift from the expected software baseline. A compliance check can be performed against the committed draft to confirm host conformance. The Initialize-SettingsHostsSoftwareCheckSpec cmdlet in PowerCLI initializes a software check specification with a commit parameter to define the desired software version, and the Invoke-CheckHostSoftwareAsync cmdlet runs a remediation pre-check to confirm software and hardware compatibility before applying changes. When enabling a cluster to use a software specification, administrators can submit a Software.CheckSpec structure to define which preliminary checks to run. Draft specifications can be validated before committing to confirm they are complete and conflict-free, and remediation pre-checks include hardware compatibility validation to identify issues before applying updates. When vLCM downloads a software package for a host update, it verifies the SHA-256 checksum of each downloaded package to confirm integrity before applying it. The vSphere Image Library provides a complementary SHA-256 verification mechanism: administrators can compare the checksum of an imported image against the checksum generated when the image was created, supporting integrity validation when images are transferred between different vCenter instances.
+vSphere Configuration Profiles extend desired-state management by enabling drift detection for vSphere clusters. When Configuration Profiles are enabled, VCF Operations monitors drift status through a collection cycle that runs every 8 hours, providing a proactive method to detect when cluster configurations have changed from their expected state.
+vCenter includes File Integrity Monitoring, which maintains cryptographic checksums representing the current state of the vCenter file system and schedules periodic integrity scans. The File Integrity Monitoring Status API, accessible via standard HTTPS requests, returns a files_changed boolean field indicating whether monitored files have been altered and a check_time field containing the Unix timestamp of the last completed scan. Administrators can configure the scan frequency in seconds through the API, allowing the monitoring interval to be tuned for operational requirements.
+VCF Operations extends configuration validation to the broader VCF deployment. It exposes a POST /v1/vcf-management-components/validations API endpoint that validates JSON deployment configuration files before they are applied. The VCF Installer deployment wizard similarly validates install specifications before starting the setup process, allowing administrators to review failed validations and resolve issues using the remediation information provided in error messages. An optional API operation allows administrators to verify whether an install spec is valid before beginning deployment. The configuration validation process examines configuration files for errors and conflicts, returning output that helps avoid loading an incorrect configuration.
+For virtual machines, VCF supports UEFI Secure Boot to verify guest operating system integrity at boot time. VMware Tools packages are signed, with verification performed during installation and updates. VCF Operations management pack PAK files are also signed with digital signatures that indicate the original developer or publisher and provide authenticity verification; VCF Operations displays a warning if a PAK file lacks a valid signature.
+Certificate validation is built into the platform at multiple levels. VCF detects when certificates have expired or are nearing their expiration dates. The Certificates tab in VCF Operations displays certificate expiration status for each workload domain. VCF Operations provides a Certificates widget to view certificates that require attention based on their expiration dates. NSX Manager certificate expiry scanning identifies appliance certificates due to expire within 31 days, and critical severity alarms are generated after certificate expiration.
+At the storage layer, vSAN provides data integrity checking through end-to-end checksum verification, confirming that each copy of a file matches the source. When a checksum mismatch is detected, vSAN automatically repairs the data by overwriting the incorrect copy with the correct version. The system checks data validity during read and write operations and reports errors when repair is not possible. Object checksum can be configured through vSAN storage policies to control whether checksum calculations are performed. vSAN configuration validation checks are performed as part of the host synchronization process, confirming that vSAN settings remain consistent across cluster members. RAID-5 and RAID-6 erasure coding provide additional data protection as policy-driven attributes that can be applied to virtual machine components.
+The VMware Kubernetes Service (VKS) and vSphere Supervisor layer extends integrity checking to containerized workloads. At the Kubernetes API layer, administrators can deploy ValidatingAdmissionPolicy resources using Common Expression Language (CEL) expressions to enforce configurable validation checks on every object submitted to the API server. The validationActions field controls whether validation failures generate audit log entries, warnings, or hard rejections, and the failurePolicy field defines how policy evaluation errors are handled, including failures from CEL parse errors, type check errors, and runtime errors. ValidatingAdmissionWebhook resources provide an additional validation layer after all mutations are complete. For container image integrity, the kubelet image verification mode is configurable per VKS cluster with four settings: NeverVerify, NeverVerifyPreloadedImages (the default), NeverVerifyAllowlistedImages, and AlwaysVerify; the AlwaysVerify setting requires cryptographic signature verification for every image before it is permitted to run. Admission controllers can automatically verify image signatures at deploy time to validate their authenticity and integrity. Harbor, available as a Supervisor service and certified by Broadcom for compatibility with Supervisor networking, storage, and authentication, provides registry-layer integrity controls including vulnerability scanning, content trust, and policy-based replication; Harbor signs images as trusted before they are available for deployment. During VKS cluster lifecycle operations, pre-checks are enforced before cluster upgrades to validate system state and confirm compatibility. The VCF CLI binary, used for Consumption layer operations, can be verified using a sha256sum.txt checksum file available alongside the CLI download from the VCF Automation Tenant Portal.
+For ongoing configuration integrity monitoring, VCF Operations includes a Compliance Checks capability that supports compliance validation throughout workload transitions. Organizations can run compliance checks in parallel and review the results to identify where configurations have drifted from established security baselines. VCF supports checking system configurations against DISA STIG requirements using automated tools, providing a mechanism to validate that security configurations remain aligned with the established hardening standards. DISA STIGs are also available for Supervisor and VKS release (VKr) components, extending this hardening validation to the containerized workload layer.</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -3209,13 +3031,15 @@
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>Avi Load Balancer contributes to the incident handling lifecycle by providing application-layer detection, analysis, automated alerting, and recovery capabilities within its role as an application delivery controller.
-For preparation, the Controller's alert and event framework supports pre-configured response actions. ControlScripts, defined under Alert Actions in the Controller UI, allow administrators to specify automated responses that fire when defined alert conditions are met. The Alert feature processes system events and metrics against user-defined rules and generates notifications via email, syslog message, or SNMP trap. The Syslog-Audit-Persistence alert action streams audit compliance events to external syslog servers, enabling incident response tooling to receive Avi event data in real time.
-For automated event detection, the Controller's System Events Overlay records event codes that provide high-level definitions of system status, including SERVER_HEALTH_DEGRADED, POOL_HEALTH_DEGRADED, and VS_UP. The Avi Service Engine logs events when WAF matches a transaction, and logs audit record failures to Events, Syslog, and Splunk, covering initiation and termination of trusted channels, certificate validation failures, client authentication failures, and SSH session establishment failures. The Application Security Report provides an executive summary alongside WAF statistics, including ranked lists of top attack types such as SQL injection and cross-site scripting, lists of top attacking source IP addresses, and trend summaries of total and flagged request volumes.
-For analysis, Avi Service Engine health monitoring records failure details for each monitored server, including failure type, failure count, average response time, and minimum and maximum response times. The Service Engine analytics page displays the list of failed health monitors per server in a pool, enabling investigation of health patterns. WAF Log Analytics supports creation of exceptions at the group or rule level for false positive remediation, enabling more accurate signal analysis during an investigation. Support bundles collect diagnostic data, logs, and configuration information from the system to assist in troubleshooting and resolving issues.
-For containment, WAF policies block application-layer requests that match defined rules or anomaly score thresholds, and WAF Policies can attach a Positive Security group to apply learned data and define hit/miss actions for fine-grained control. ControlScripts can trigger automated containment actions in response to alert events.
-For recovery, the Avi for VCF rollback procedure supports validation of the operational status of all VIPs and pools, followed by end-to-end health checks on the VS-App environment. GSLB services with the priority algorithm support a manual resume option for controlled failover and recovery management.
-The full incident handling program, including organizational preparation procedures, eradication processes for removing attacker footholds across the broader environment, cross-team coordination, and end-to-end recovery governance, requires processes and tooling beyond what Avi provides within its application delivery scope.</t>
+          <t>VMware Avi Load Balancer provides configuration integrity validation through automated pre-operation checks, on-demand consistency verification, and image integrity verification at the application delivery layer.
+The Avi Controller CLI includes a `show config-consistency-check` command that reports the current consistency state of controller configuration. Operators can run this command at any time to verify that configuration state is consistent across cluster nodes and to surface any drift or discrepancies.
+Before upgrade operations, the Controller runs automated pre-upgrade verification that confirms Controller Cluster readiness, detects whether an upgrade is already in progress, validates active version compatibility across the cluster, and verifies Service Engine reachability. In the Avi for VCF deployment, the Controller requires verification of image checksums or digital signatures to confirm file integrity before upgrade proceeds. A system configuration check validates the overall system state before upgrade operations begin. The upgrade pre-check system produces mandatory error messages for requirement violations that cannot be overridden and warning messages for optional requirements that can be skipped. The Avi Controller system report for upgrade operations records each pre-check result, including check code, description, state, start time, end time, and duration, providing a full audit record of the validation sequence.
+The Dry Run feature performs configuration validation in an isolated container before an upgrade is committed, including partial Controller initialization, configuration migration, new schema item validation, and configuration testing. Operators can review progress using the VIEW PROGRESS option under Administration &gt; Update &gt; System and return to the pre-check screen to evaluate results before proceeding.
+Before applying patches, the Controller performs patch compatibility checks to verify that a patch is safe to apply and that system stability will be maintained. Before restore operations, the Controller executes a pre-restore validation sequence covering Controller Cluster readiness, active upgrade operation detection, ServiceEngineGroup upgrade status, backup configuration version compatibility, FIPS mode compatibility, image object presence, configuration validity, and FIPS mode alignment between the backup file and the target environment.
+The Avi Controller maintains checksums and creation timestamps for custom IPAM script files, providing integrity tracking and an audit trail for configuration scripts used in custom IPAM implementations.
+For FIPS 140-3 compliance, Avi Load Balancer applies enhanced controls over software and firmware module integrity and module updates, including tighter requirements on module update procedures.
+In Kubernetes deployments, the Avi Kubernetes Operator (AKO) performs syntactical validation of Custom Resource Definition (CRD) objects at creation time, verifying configuration correctness and surfacing errors through effective status messages. AKO also monitors certificate files and Kubernetes secrets, with certificate and secret update events visible via AKO logs.
+These mechanisms operate at the Avi application delivery layer. Software and firmware integrity for the underlying compute, storage, and networking infrastructure relies on VCF through Secure Boot, VIB acceptance levels, and TPM attestation, which are covered under VCF Coverage. Organizations should account for both layers when demonstrating full coverage of this control.</t>
         </is>
       </c>
     </row>
@@ -3237,83 +3061,57 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Meets</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Meets</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>VCF provides technical capabilities that support several phases of the incident handling lifecycle, though the organizational preparation, process governance, and manual intake elements require processes and structures outside the platform.
-For preparation, VCF Operations supports the configuration of notification rules with detailed incident field mappings, including incident state, resolution codes, impact, urgency, priority, severity levels, and assignment groups. The ServiceNow Management Pack can be configured with parameters such as callerId, propagateAlertUpdates, retrieveIncidentUpdates, and incidentReopenState, allowing organizations to establish incident handling workflows before events occur. These configuration options allow teams to define how incidents are categorized, prioritized, and routed in advance of any actual incident.
-For automated event detection, VCF Operations correlates events from monitored infrastructure components and delivers them as faults. Events are ranked by severity from Info through Warning, Critical, and Immediate, and notification rules trigger actions based on incident state changes. VCF Operations can automatically create incidents in ServiceNow through the Service-Now Notifications plug-in, with structured information including the caller, category, subcategory, and business service. This integration bridges the gap between infrastructure monitoring and organizational incident tracking systems. VCF Operations also combines Diagnostic Findings with VCF Health to detect and predict issues, which helps reduce mean time to resolution. VMware vCenter alarms provide additional automated detection, triggering script execution, SNMP traps, email notifications, or API calls when infrastructure conditions exceed defined thresholds.
-For analysis, the Troubleshooting Incident Page displays information related to the entity under investigation, including traffic and flows on the entity, past incidents created for that entity, status, root cause metrics, and closing remarks. Operators can flag metrics and mark specific metrics as root cause during investigation. The Notes section on each incident allows users to add observations that are visible to anyone who opens the session, which supports collaborative analysis across team members. vCenter Events record user and system actions on inventory objects and can be used for forensic analysis and auditing of activity in the virtual environment, providing an audit trail for incident investigation. Diagnostic Findings consolidates log-based and property-based findings with specific resolution recommendations and links to knowledge base articles, helping analysts identify known issues by matching log patterns and property-based signatures against a library of diagnostic rules. Log Assist can generate log bundles and automatically attach property-based diagnostic findings data to support cases. VCF Operations also integrates with ServiceNow, allowing incidents to flow into existing ITSM workflows for structured triage.
-For containment, vCenter supports isolating affected workloads through VM power state changes and network reconfiguration. VMware vDefend (a separate product that extends VCF's networking foundation) provides more targeted containment through quarantine policies that automatically isolate VMs based on security events while preserving forensic access for investigation. Physical containment, network isolation decisions, and cross-system coordination during active incidents depend on processes and authority structures that exist outside the platform.
-For eradication, VCF Operations maps out-of-the-box workflows to recommendations and associates them with specific alerts, enabling automated remediation of known conditions. Diagnostic Findings helps operators find and resolve known issues using diagnostic rules and signatures, with recommended fixes based on industry-standard best practices.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a host failure, with admission control policies that reserve capacity for failover. Proactive HA integrates with hardware vendor monitoring to detect degrading components and evacuate workloads before failure occurs. vSphere Fault Tolerance provides continuous availability for workloads that require zero-downtime protection during failover. VCF Operations maintains a summary view of all incidents with status tracking, entity counts for in-progress incidents, and counts of top root causes for visibility into the overall state of incident resolution.
-VCF Operations also provides a centralized incident list displaying all incidents with their status and key details, with edit, share, and delete actions for incident lifecycle management. Incident tracking captures state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation, which is a structured audit trail for each incident. The Guided Network Troubleshooting feature automatically maintains a list of the 20 most recently modified incidents within a selected scope for continuity across investigation sessions.
-While VCF Operations provides tooling for detection, analysis, and remediation of infrastructure incidents, several aspects of the six-phase incident handling lifecycle require organizational processes beyond what the platform provides. Preparation requires documented incident response plans, team roles, and communication procedures. Manual incident report intake requires organizational channels and triage processes. Containment decisions require human judgment and authority structures. A formal incident response program that incorporates VCF's technical capabilities into broader organizational processes is necessary to address all six phases.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (VMware vDefend and Advanced Threat Protection) contributes to multiple phases of the incident handling lifecycle through network-layer detection, multi-signal analysis, and automated containment capabilities.
-For detection and event intake, Security Intelligence categorizes detected suspicious traffic events by impact type, assigning Critical, High, Medium, or Low severity to help teams prioritize response. Security Intelligence also maps detections to MITRE ATT&amp;CK tactics and techniques and records occurrence counts over configurable time windows, providing the structured event context that analysis workflows require.
-For analysis, Malware Prevention generates File Analysis Reports and Process Analysis Reports that detail the types of activities detected during artifact inspection. File Analysis Reports classify detected behaviors across categories including Autostart, Disable, Evasion, File, Memory, Network, Reputation, Settings, Signature, Steal, Stealth, and Silenced, and include an ATT&amp;CK TECHNIQUES field that records observed malicious actions or tools. Process Analysis Reports document in-memory script buffer inspection results and carry an Analyst UUID to track individual inspection events. Malware Prevention Service event logs capture file type, file size, inspection timestamp, client VM ID, submission source, detection status, verdict, and analysis status for each inspected file. The Malware Prevention Dashboard aggregates file and process event details and inspection results for operator review. Network Detection and Response (NDR) Campaign Correlation Rules correlate labeled file and process detections, including AV labels and PCAP matches, with matching IDS events on the same compute, supporting multi-signal analysis during investigation. The Security Services Platform assigns a Security Operator role dedicated to monitoring security systems and responding to security incidents.
-For containment and eradication, Intelligent Assist supports remediation by allowing selection of a Targeted Strategy for surgical, focused containment or a Comprehensive Strategy for broader remediation across potentially affected workloads. The Security Segmentation Report's Overview section summarizes inter-environment policies and rules, providing traffic flow context that can inform containment scope. Security Explorer's ratio of detected versus prevented events helps operators assess how effectively controls are operating during active response.
-A limitation applies to automated remediation: objects generated during Intelligent Assist or NDR remediation that encounter errors require manual cleanup, so recovery activities may require human intervention beyond automated policy actions. vDefend IDS/IPS also applies a severity-based prioritization under memory pressure, dropping lower-severity events (Low and Informational) first before Medium, High, and Critical, which operators should account for when assessing detection completeness during an investigation.
-Preparation and full organizational recovery rely on processes and tooling outside vDefend's scope.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides technical mechanisms that support the recovery, containment, and detection phases of incident handling through recovery plans, isolated cyber-recovery workflows, structured event logging, and integration with security monitoring platforms.
-Recovery plans define ordered procedures for recovering protected workloads at a recovery site, including custom recovery steps. PNR handles custom command failures in recovery plans based on the type of command, allowing operators to control how the plan continues when steps fail. When a disaster event affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so that users can recover workloads. After execution, PNR provides the ability to view and export reports about each run of a recovery plan, test of a recovery plan, or test cleanup, producing documented evidence for after-action review.
-For containment and eradication, the Clean Room Orchestrator enables triage and analysis of recovered workloads in an isolated environment. PNR monitors a global collection of clean room events, tasks, and alarms for recovery operations, with Clean Room Orchestrator events classified at severity levels of Info, Warning, Error, and Emergency. This isolated environment supports analysis of suspect workloads in parallel to site-level recovery actions.
-For detection and analysis, PNR logs events and triggers corresponding alarms to track system health, with event records including timestamp, priority level, message content, component name, severity level, configuration ID, component ID, and event type. PNR tracks Site Status events that provide information about the status of protected and recovery sites and the connection between them. PNR can forward Clean Room Orchestrator events to VCF Log Management, Microsoft Sentinel, or Splunk Cloud, supporting integration with broader security monitoring and incident response platforms.
-PNR Health findings classify status into Error, Warning, and Info categories and are visible through Protection and Recovery dashboards in VCF Operations. Deployment topology with separate management domains for each region is designed to contain the impact of a disaster event to one particular region, supporting preparation by limiting blast radius.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) generates audit records from multiple internal sources and provides mechanisms to centrally view, access, and export those records for review and analysis. The platform captures audit events covering user actions performed through the DSM UI and API, as well as actions that DSM itself initiates. This includes administrative operations, database lifecycle events, and system-level activities. The System Audit Events view, accessible through the System Audit section of the Provider interface, is the central location for tracking non-database-related operations and tasks.
-The audit records generated by DSM contain structured fields that support systematic review. Each audit event includes a Component field identifying which DSM component performed the operation, an Event Type field identifying the category of the event, an Event Details field providing operation-specific context, Event Time in UTC, a Status field, and a Source field identifying either the user identifier (Email ID) that initiated the operation or "System" when DSM itself initiated it. Gateway audit log files are stored on the Provider VM at /var/log/tdm/provider/audit/ with filenames in the format gateway-audit-timestamp.log, and contain standard Kubernetes audit events. When a default S3 provider log repository is configured, DSM automatically archives gateway audit log files to that repository on a periodic basis to an S3 subpath named "gateway audit," providing an off-platform collection point.
-For database-level audit logging, PostgreSQL databases provisioned by DSM include the pgaudit extension, which provides audit logging capabilities across all supported PostgreSQL versions. The pgaudit extension captures database-level audit events separately from the gateway-level audit trail, giving administrators visibility into both infrastructure-level operations and database operations as distinct audit sources. SQL Server databases provisioned by DSM include configurable server auditing with preset audits for login tracking and log retention. The Login Auditing option automatically creates an audit for login events, and DSM supports the T-SQL CREATE AUDIT and CREATE AUDIT SPECIFICATION DDL for custom audit definitions. These SQL Server capabilities add a third distinct audit source alongside gateway and PostgreSQL audit streams.
-DSM supports audit record export in CSV and XLSX formats through the ACTIONS dropdown in the System Audit Events view. Exports include all audit events visible to the current user regardless of pagination limits. DSM also supports log forwarding via syslog, enabling organizations to route audit data to external log management and SIEM platforms for automated collection and analysis across multiple sources. VI administrators can monitor PostgreSQL and MySQL clusters deployed by DSM using VCF Operations, which automatically discovers clusters in the Ready state and displays performance data at the cluster, node, and database levels.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N27" s="10" t="inlineStr">
         <is>
-          <t>Avi Load Balancer contributes to the incident handling lifecycle by providing application-layer detection, analysis, automated alerting, and recovery capabilities within its role as an application delivery controller.
-For preparation, the Controller's alert and event framework supports pre-configured response actions. ControlScripts, defined under Alert Actions in the Controller UI, allow administrators to specify automated responses that fire when defined alert conditions are met. The Alert feature processes system events and metrics against user-defined rules and generates notifications via email, syslog message, or SNMP trap. The Syslog-Audit-Persistence alert action streams audit compliance events to external syslog servers, enabling incident response tooling to receive Avi event data in real time.
-For automated event detection, the Controller's System Events Overlay records event codes that provide high-level definitions of system status, including SERVER_HEALTH_DEGRADED, POOL_HEALTH_DEGRADED, and VS_UP. The Avi Service Engine logs events when WAF matches a transaction, and logs audit record failures to Events, Syslog, and Splunk, covering initiation and termination of trusted channels, certificate validation failures, client authentication failures, and SSH session establishment failures. The Application Security Report provides an executive summary alongside WAF statistics, including ranked lists of top attack types such as SQL injection and cross-site scripting, lists of top attacking source IP addresses, and trend summaries of total and flagged request volumes.
-For analysis, Avi Service Engine health monitoring records failure details for each monitored server, including failure type, failure count, average response time, and minimum and maximum response times. The Service Engine analytics page displays the list of failed health monitors per server in a pool, enabling investigation of health patterns. WAF Log Analytics supports creation of exceptions at the group or rule level for false positive remediation, enabling more accurate signal analysis during an investigation. Support bundles collect diagnostic data, logs, and configuration information from the system to assist in troubleshooting and resolving issues.
-For containment, WAF policies block application-layer requests that match defined rules or anomaly score thresholds, and WAF Policies can attach a Positive Security group to apply learned data and define hit/miss actions for fine-grained control. ControlScripts can trigger automated containment actions in response to alert events.
-For recovery, the Avi for VCF rollback procedure supports validation of the operational status of all VIPs and pools, followed by end-to-end health checks on the VS-App environment. GSLB services with the priority algorithm support a manual resume option for controlled failover and recovery management.
-The full incident handling program, including organizational preparation procedures, eradication processes for removing attacker footholds across the broader environment, cross-team coordination, and end-to-end recovery governance, requires processes and tooling beyond what Avi provides within its application delivery scope.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -3345,22 +3143,17 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>VCF provides enterprise-wide monitoring through integrated tools that span infrastructure health, performance metrics, compliance assessment, log analysis, and alerting.
-VCF Operations continuously monitors the operational state of all VCF components to detect conditions that may affect availability or compliance. It collects metrics across compute, storage, and networking resources, and correlates them over time to identify trends that may lead to potential failures. VCF Health, a component of VCF Operations, continuously monitors the operational state of VCF components to verify they are functioning as expected, giving platform operators a single view of operational status. Platform operators can configure alerts, perform log analysis, run infrastructure diagnostics, and review VCF health from a unified interface.
-VCF Operations provides continuous compliance management by monitoring infrastructure against industry-standard benchmarks and custom policies. Administrators can create custom compliance benchmarks that monitor selected alert definitions and policies, tailoring the monitoring posture to organizational requirements. The platform assesses objects based on selected compliance policies and activates alert definitions associated with the current scorecard, providing ongoing visibility into compliance status. Compliance-related alerts are triggered on objects and displayed through a dedicated compliance alert subtype.
-The alerting subsystem in VCF Operations supports the full lifecycle of alert management. Administrators can configure and manage alert definitions to monitor infrastructure events and conditions, including performance metrics, log events, and custom conditions configured through the Management Pack Builder. The Platform Health Alerts page provides a centralized view of all alerts related to overall system health, including alerts from data sources and infrastructure nodes. Health alerts are generated for conditions that affect the health of the environment and require immediate attention. Administrators can create policies to govern how alert definitions are evaluated, including which objects to monitor and what thresholds to apply, and can apply consistent practices to optimize alert behavior across monitored objects.
-VCF Operations supports flexible grouping and scheduling to align monitoring with operational realities. Custom groups can be configured with automatic membership criteria to support monitoring strategies and achieve a high level of automation. Maintenance schedules can be assigned to objects undergoing planned downtime to keep monitoring data accurate and avoid false alerts when an object is offline for scheduled maintenance.
-VCF Log Management provides centralized log collection and analysis. It ingests logs from VMware vCenter, VMware ESX hosts, NSX, vSAN, VCF Automation, VCF Operations, VCF Identity Broker, VCF Operations for Networks, and VCF Operations HCX. VCF Operations and VCF Log Management must be integrated to implement the centralized log collection architecture. The platform provides dashboards and analytics for troubleshooting and security investigation. Log-based alert definitions allow administrators to trigger notifications when specific log patterns appear across monitored systems. Log forwarding to external SIEM or syslog targets is configurable, with support for TLS encryption to protect log data in transit. The vCenter syslog forwarding API supports TCP, UDP, TLS, and RELP protocols. NSX Manager syslog supports TLS and requires port 6514 for encrypted log transmission.
-At the vSphere layer, the alarm infrastructure integrates with events and performance counters to provide real-time alerting. The MetricAlarmExpression data object allows administrators to set alarms on specific performance metrics with configurable monitoring intervals and aggregation functions for processing data points. The vSphere Client provides direct visibility into tasks and events for change tracking and troubleshooting. VCF ships with preconfigured vSphere alarms that are active by default and monitor specific components including the Identity Management Service, Message Bus Configuration Service, ESX Agent Manager, VMware Service Control Agent, vSphere HA host status, and host connection and power state. The vCenter Management Interface provides appliance-level health visibility through an Overall Health badge that reflects one of five states (Good, Warning, Alert, Critical, or Unknown) across all vCenter components, and notifies administrators of available security patches through Critical or Alert badge indicators when automatic patch checks are enabled.
-When VCF Automation is integrated with VCF Operations, the Insights dashboard and Alerts tab provide real-time capacity awareness and alert information for VCF Automation objects, giving IT teams visibility into resource usage across both provisioned workloads and the underlying infrastructure. The VCF Automation Monitor tab surfaces deployment health information sourced from VCF Operations, and deployment cards display Last Request Status information that tracks the most recent operation on each deployment (Create, Update, or Delete) and its outcome (Successful, In Progress, or Failed). The Management Pack Builder allows administrators to set up event definitions for integrated systems, monitoring specific conditions or thresholds and configuring alerts for proactive management. Management Packs extend monitoring to network devices, including sensor monitoring for devices such as switches and routers. Adapters can be installed on VCF Operations nodes to extend monitoring to additional systems and data sources beyond the core VCF components.
-The VMware Kubernetes Service (VKS) layer of VCF extends enterprise monitoring to container workloads and Kubernetes infrastructure. VKS clusters support MachineHealthCheck objects for both control plane nodes and worker node deployments; administrators manage these through the VCF CLI vcf cluster machinehealthcheck command, which supports configuration of unhealthy-condition definitions, maximum unhealthy thresholds (expressed as an absolute number or a percentage), and label selectors to target specific machines. The VCF CLI vcf cluster machinehealthcheck node get and vcf cluster machinehealthcheck control-plane get commands retrieve node and control plane health status on demand. VKS cluster health conditions, including the Ready and ControlPlaneReady status indicators, reflect the operational state of each cluster and are accessible via kubectl and the VCF CLI. The VCF Automation Provider Management UI includes a Services overview interface that exposes VKS cluster management functions and the health status of all cluster elements, giving platform operators a centralized view of the VKS tier. The Kubernetes API server within VKS clusters exposes diagnostic and health check endpoints (/healthz, /livez, /readyz, /statusz, and /metrics) that external monitoring systems can scrape to track API server availability and readiness; the kube-apiserver also emits the kubernetes_healthchecks_total counter and kubernetes_healthcheck gauge metric, which report structured health check status for components including etcd and autoregister-completion. Access to these monitoring endpoints is governed by the built-in Kubernetes system:monitoring RBAC group, which grants read access to liveness, readiness, and metrics endpoints while restricting broader cluster access. The Kubernetes Watch API allows monitoring tools to track changes to any API object as a live stream, supporting event-driven monitoring without continuous polling. The Node Problem Detector monitors node health and surfaces node-level problems as Kubernetes events and node conditions that external monitoring systems can consume via the event stream.
-For workload-level monitoring within VKS clusters, Prometheus Operator is available as a standard package and defines custom resource definitions to deploy and manage Prometheus and Alertmanager StatefulSets, enabling high-availability alerting configurations. The Prometheus Alertmanager custom resource definition configures alert grouping, inhibition, and routing to external notification systems. The Istio service mesh, also available as a standard package on VKS clusters, provides service-level monitoring alongside its traffic management capabilities. The Dynatrace Operator can be deployed on VKS clusters to automate the deployment, scaling, and maintenance of the Dynatrace monitoring stack. Historical analysis, dashboarding, and alerting on cluster-level metrics require a dedicated monitoring solution configured to scrape the VKS metrics endpoints and subscribe to the Kubernetes event stream. The vcf cluster support-bundler create command gathers diagnostic information from Supervisor and VKS clusters when troubleshooting is needed.
-At the network layer, NSX provides monitored indicators including node uptime status, deployment status, management and controller connections, tunnel status, PNIC status, and uptime duration. NSX time series APIs allow viewing data such as VPN statistics, including metadata about the number of tunnels configured and how many are up or down at a given time.
-VCF Operations also supports self-monitoring through the VCF Operations adapter, which collects internal metrics such as activity success counts. This allows administrators to verify that the monitoring platform itself is functioning correctly. The VCF Operations policy engine monitors conditions and generates events to react to changing states in the orchestrator server or connected technologies. The Adapter Instance monitoring interval is configurable, with intervals as granular as five minutes.
-VMware Private AI Services (PAIS) includes a built-in observability stack that supplies monitoring data for AI infrastructure and AI workloads. PAIS Controller metrics are exposed at a Prometheus metrics endpoint on the pais-controller-manager service, allowing collection by monitoring systems and visualization in observability platforms such as Grafana. Observability is activated by updating the PAISConfiguration custom resource with optional sections for Prometheus metrics collection and LLM trace forwarding. The Prometheus runtime can be configured with a specified storage class policy and a configurable metrics retention period, giving administrators control over how long monitoring data is stored. A Prometheus server pod must be in a ready and running state for observability to function.
-LLM trace data from PAIS can be forwarded to an OpenTelemetry Collector endpoint over http/protobuf or gRPC, providing distributed tracing for AI model inference activity. The observability.llmTraces configuration governs trace forwarding and works alongside the Prometheus metrics pipeline to produce two signals: metrics for health and performance, and traces for inference-level behavior. PAIS Controller metrics include the Model Endpoint Controller and PAIS Configuration Controller, giving monitoring platforms component-level visibility into PAIS operations.
-In 9.1, PAIS adds direct integration with VCF Operations. The controller-pod-metrics-streaming setting activates streaming of PAIS controller pod metrics from the Supervisor cluster to VCF Operations, allowing administrators to view PAIS metrics alongside other VCF infrastructure metrics. A Telegraf deployment in the vmware-system-monitoring namespace uses a telegraf-user-config ConfigMap to manage user-configured monitoring endpoints for PAIS. The VCF Consumption CLI connects to the Supervisor endpoint and enables VI administrators to stream metrics from the PAIS controller pod. DevOps engineers can visualize health and performance metrics for PAIS components running in a VCF Automation namespace using Grafana, and MLOps engineers and application developers can monitor the health, quality, and behavior of AI applications and the models used in agents through the same observability platforms.
-PAIS supplies the technical monitoring mechanisms this control requires. Enterprise-wide orchestration of monitoring controls, including alert threshold definition, escalation procedures, and integration with a centralized monitoring or log management platform, remain organizational responsibilities.</t>
+          <t>VCF provides centralized collection and management of security-related event logs across all platform components. Every major subsystem supports syslog forwarding to external log aggregation infrastructure, enabling integration with any SIEM or centralized logging platform that accepts standard syslog input. In addition, VCF Log Management provides a built-in log aggregation and analysis capability within the platform itself.
+VMware ESX hosts can be configured to send syslog messages to a remote log server using the esxcli system syslog config set command, specifying the target server IP address and port. ESX syslog messages conform to RFC 3164. Configurable syslog log levels allow administrators to tune the verbosity of forwarded events using esxcli system syslog commands. The syslog directory location on ESX hosts is controlled through the Syslog.global.logDir parameter. The Syslog.global.auditRecord.remote parameter separately controls whether security audit records are transmitted to the remote hosts configured in Syslog.global.logHost. ESX hosts maintain local logging with configurable retention and rotation policies, maintaining six log files that rotate at each power-cycle by default or at a configured file size. When the configured file limit is reached, the oldest file is deleted. The ESX Dump Collector and vSphere Syslog Collector can be configured to redirect ESX memory dumps and system logs to a network server for persistent log storage.
+VMware vCenter provides syslog forwarding through both its management API and direct configuration. The vCenter Management API exposes endpoints to set the syslog forwarding configuration (PUT), retrieve the current configuration (GET), and test the connection with remote syslog servers (POST). vCenter syslog forwarding supports TCP, UDP, TLS, and RELP protocols, giving administrators flexibility in how log data is transmitted to the collection infrastructure. The remote syslog target must be a server running rsyslog. vCenter event streaming to a remote syslog server is activated through the vpxd.event.syslog.enabled option in the vCenter Management Interface, and the Appliance Management Interface supports a maximum of three remote syslog destination hosts. vCenter retains performance data with configurable intervals and automatic purge policies.
+NSX Manager can export syslog to a remote server with configurable protocol, port, and log level. NSX audit logs, which record security-related events such as logon, logoff, and access to resources, are sent directly to the configured remote syslog server. NSX Manager audit logs also record failed login attempts with username and timestamp information, and log user account role changes for remote users authenticated through identity sources. Each audit log entry contains the timestamp, source, result, and a description of the event. API calls from all sources and users are audited, and each audit log associated with an API call includes a request ID parameter for traceability. This logging is always enabled and cannot be disabled. NSX also captures logical switch messages and other operational events in its audit log. On ESX hosts, NSX syslog data is stored in /var/log/nsx-syslog and can be forwarded alongside other host logs. NSX Manager syslog supports TLS protocol on port 6514 for encrypted log transmission.
+VCF Log Management is the centralized log collection platform within the VCF stack, gathering logs from vCenter, ESX hosts, NSX, VCF Operations, and VCF Operations for Networks. It can be configured to pull tasks, events, and alerts from vCenter instances and receive syslog feeds from ESX hosts through its Log Collections configuration. VCF Log Management provides an analysis interface where administrators can search and filter log events, create queries based on timestamp, text, source, and structured fields, and build dashboards for operational and security scenarios. Content packs for VCF components provide pre-built dashboards, alerts, and queries for common use cases, including a content pack for VCF Operations for Networks. Log-based alert definitions allow administrators to trigger notifications when specific log patterns are detected.
+VCF Operations supports centralized log collection and editing of log sources through Infrastructure Operations, under Configurations and Log Collection. VCF Operations Host System Properties allow configuration of a remote syslog host for centralized log collection. The audit log in VCF Operations is integrated with syslog, and the syslog collector can be configured to collect all audit logs. VCF Operations can also send user activity audit logs to an external syslog server. Audit logs capture administrative actions carried out through the API, the user interface, and the CLI, including regular CRUD operations and login/logout alerts. Note that SSH login logs are not captured in VCF Operations audit logs; SSH logs can be found in /var/log/auth.log. VCF Operations supports outbound integrations that distribute alerts and log data to external systems via email, SNMP traps, REST webhooks, log files, and Slack notification plugins.
+VCF Operations for Networks supports centralized log collection and editing of log sources through its own Infrastructure Operations configuration. Remote syslog servers must be configured to accept syslog traffic over UDP. All platform servers in a VCF Operations for Networks cluster use the same remote syslog server, though individual collectors can be pointed to different remote syslog servers. The audit log in VCF Operations for Networks is integrated with syslog.
+Additional VCF components also support centralized log forwarding. The Foundation Load Balancer supports forwarding logs to a syslog server via IP address configuration, with certificate-based secure communication for log forwarding. VCF Operations HCX supports configuring a remote syslog server that receives logs from both the HCX manager and appliance virtual machines, and appliances deployed after adding the external syslog server automatically forward log messages. VCF Identity Broker supports log collection as well.
+The Consumption layer of VCF, which encompasses VMware Kubernetes Service (VKS) clusters running on vSphere Supervisor, provides its own log collection and forwarding capabilities that integrate with the broader platform logging infrastructure. Kubernetes audit logging within VKS generates a security-relevant, chronological record of cluster activity, documenting the sequence of API calls made by users, applications, and the control plane. This includes authentication events, authorization decisions, resource creation and modification, and user impersonation requests, with each impersonation request recorded individually in the audit log. Audit verbosity is governed by a Kubernetes audit policy that specifies which events to capture and at what level of detail; available backends for writing audit records include log files at /var/log/kubernetes/audit/ and external webhook endpoints. Kubernetes system component logs are configurable for verbosity, ranging from coarse-grained error reporting to fine-grained trace output covering HTTP access logs, pod state changes, and other operational detail. Fluent Bit is available as a standard package for VKS clusters and serves as the log forwarding agent. Once deployed as a DaemonSet on every node, Fluent Bit collects Kubernetes container logs, API audit logs, Linux daemon logs, and Linux authentication logs, then forwards them to a configured destination. Supported forwarding destinations include Syslog (port 514 for UDP, port 6514 for TCP), HTTP endpoints, Elasticsearch, Kafka, and Splunk. When integrated with VCF Log Management, Fluent Bit forwards over the CFAPI protocol; VCF Log Management accepts log forwarding connections on HTTPS port 9543 or HTTP port 9000 at the /api/v2/events endpoint. A logging management server must be deployed and accessible from the VKS cluster to receive, store, and analyze forwarded logs; the Consumption layer provides the collection and forwarding mechanisms rather than the SIEM itself. The Supervisor control plane also forwards its VM system logs to external syslog servers in RFC 5424 format over TCP, managed by Fluent Bit pods in the vmware-system-logging namespace whose status can be queried using kubectl commands.
+For workloads running as vSphere Pods within vSphere Namespaces, administrators configure the LogAgentConfiguration custom resource to stream syslog messages directly to a remote syslog server. Log messages from vSphere Pods include structured metadata fields covering namespace name, pod UID, pod name, container name, and ESX host name, enabling precise attribution and filtering at the receiving SIEM or log aggregation platform.
+VCF also aligns with global compliance logging requirements: auditable events are logged across the platform. This baseline of audit event generation feeds into the centralized collection mechanisms described above.</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -3397,6 +3190,102 @@
         </is>
       </c>
       <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>VMware Data Services Manager (DSM) produces structured audit logs that record platform-level and gateway-level operations, and provides several mechanisms that contribute to protecting those logs from unauthorized access and loss.
+At the platform level, DSM maintains gateway audit log files on the Provider VM at /var/log/tdm/provider/audit/, with individual files named using a timestamp format (gateway-audit-timestamp.log). Local retention covers the last five days of log files; once files are successfully uploaded to a configured S3 repository, DSM removes them from the local filesystem after five days. Each log entry captures structured fields including Component, Event Type, Event Details, Event Time (UTC), Status, and Source. The Source field records the email identifier of the user who initiated the operation, or "System" for events initiated by DSM without user intervention. The System Audit Events view, accessible through the Provider interface, is the designated location for reviewing non-database-related platform operations. Access to the Provider interface is scoped to the administrative role, restricting which users can read or interact with the system-level audit record.
+DSM supports offloading audit logs to external storage as the primary mechanism for durable protection. When a default S3 provider log repository is configured, DSM periodically archives gateway audit log files to an S3 subpath named "gateway audit." DSM does not delete audit logs stored in the S3 repository, which means the archived log record persists beyond the five-day local retention window. Externalizing audit logs to S3 separates the log record from the Provider VM that generated it, reducing the risk that a compromise or failure of the Provider VM affects the integrity or availability of the audit trail. Organizations apply bucket-level access controls and retention policies on the S3 repository to restrict who can read, modify, or delete the archived logs.
+DSM supports log forwarding, allowing DSM logs to be sent to a centralized log management or security information and event management (SIEM) platform via the System Logs capability. Forwarding logs to an external system provides a second copy of the audit record under access controls and integrity protections that are independent of the DSM platform itself.
+For SQL Server databases provisioned through DSM, the SQL Server data service uses server-level DDL triggers to restrict the file paths available for audit logs, limiting where audit log files can be written. DSM supports enabling audit logging for SQL Server with configurable levels of auditing for system logins and a configurable log retention period. DSM can automatically create a simple audit for login events based on the Login Auditing option selected during cluster creation. For custom audit requirements, the standard T-SQL CREATE AUDIT and CREATE AUDIT SPECIFICATION DDL statements are available.
+DSM can generate and download log bundles that aggregate relevant logs from database VMs, supporting diagnosis and out-of-band preservation of the operational log record.
+Audit events can be exported from the System Audit Events view in CSV or XLSX format using the ACTIONS menu. Exports include all events visible to the authenticated user regardless of pagination, supporting external archival and out-of-band preservation of the audit record.</t>
+        </is>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>VMware Avi Load Balancer (Avi) contributes to enterprise-wide monitoring through application-delivery-layer mechanisms built into the Avi Controller and Service Engines.
+The Avi Controller monitors Service Engine metrics and sends alarms and notifications to administrators when resource utilization data exceeds defined thresholds. Administrators configure custom thresholds on Service Engine groups through the Resource Events tab in the Avi UI. The Alert feature processes system events and metrics against user-defined rules and generates alerts that trigger configured actions, including sending an email, a syslog message, or an SNMP trap. Alert notifications can be forwarded to remote syslog servers for integration with centralized log management and monitoring platforms.
+ControlScripts extend this event-response capability: a ControlScript can alter Avi configuration or communicate to external systems, including through webhook integrations with external monitoring tools, in response to defined system events. This supports dynamic responses including resource scaling or automated notifications based on health scores from monitoring data.
+The Avi Controller and Service Engines track health score changes and SSL certificate expiration events. Avi integrates with external monitoring tools such as Prometheus for metrics collection and analysis. User-Defined Metrics allow administrators to define and extract customized telemetry data for specific compliance or reporting needs through the API. Real-time metrics are available via API but deactivate by default after 30 minutes to conserve resources and must be reactivated when sustained real-time visibility is required.
+At the data plane, Avi health monitors track the status of backend servers and Service Engines continuously. Service Engine health monitoring records detailed server operational status, including health monitor name, type, last transition timestamps, rise count, fall count, total checks, and total failed checks. Each health monitor can be assigned its own threshold and timeout period for server health validation. Monitors support HTTP, HTTPS, TCP, and UDP health-check protocols with configurable success and failure thresholds, send intervals, and receive timeouts.
+In Kubernetes environments managed by the Avi Kubernetes Operator (AKO), the HealthMonitor custom resource definition (CRD) allows users to define custom health monitoring configurations for backend services with fine-grained control over health check parameters. The Avi Multi-Cluster Kubernetes Operator (AMKO) GlobalDeploymentPolicy supports health monitor references for consistent monitoring across multi-cluster deployments. Within VCF Automation, a HealthMonitor custom resource can create monitors for tracking backend pool member status using TCP, PING, and HTTP check types.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>6.5A</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>END-07, MON-01, MON-01.1, NET-08</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Intrusion Detection: Detect and contain anomalous network activity into the local or remote SWIFT environment.</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides networking infrastructure through NSX that supports the deployment of intrusion detection and prevention capabilities across virtualized environments. The VCF stack includes IDS/IPS and distributed malware prevention through vDefend, a separately licensed product that extends NSX with security functions, and these capabilities can be configured on discovered host clusters using the NSX UI or API. vDefend Distributed IDS/IPS is also available for consumption under NSX Projects, allowing IDS/IPS policies to be scoped to specific tenants or workload groups within the platform.
+The IDS/IPS functionality in the VCF stack is delivered through VMware vDefend with Advanced Threat Prevention (ATP). ATP combines multiple detection technologies, including an Intrusion Detection/Prevention System, network sandboxing, and Network Traffic Analysis (NTA), with aggregation, correlation, and context engines from Network Detection and Response (NDR). vDefend with ATP is a software-defined Layer 2-7 firewall purpose-built to secure virtualized workloads in a private cloud, providing stateful firewalling with threat prevention capabilities. The NSX Application Platform hosts the features that support these advanced capabilities, including Security Intelligence, vDefend Network Detection and Response, and Malware Prevention for vDefend.
+Administrators configure IDS/IPS rules through the Security &gt; IDS/IPS &amp; Anti-malware page in NSX Manager. vDefend distributed firewall rules can be created with an IDPS security profile applied in either Detect Only or Detect and Prevent mode, allowing organizations to start with visibility before moving to active blocking. vDefend signature-based identification and enforcement provides visibility into, or restriction of, protocols that have known vulnerabilities across all deployed applications and their east-west flows within the datacenter. The NSX Distributed Load Balancer can apply vDefend IDPS and Anti-malware Prevention features for traffic traversing load-balanced services.
+To supplement signature-based detection, vDefend supports a Malicious IP Feed that downloads a list of known malicious IP addresses from the NTICS cloud service. Administrators can create groups that include these downloaded IPs and configure vDefend firewall rules to block access to them, providing a threat-intelligence-driven layer of protection. NSX App IDs further support traffic inspection by enabling network traffic classification and control based on application identity rather than port or protocol alone, helping reduce both north-south and east-west attack vectors.
+The vDefend distributed firewall can be configured on vSphere Distributed Switches in data centers and workloads where segmentation, visibility, or advanced security capabilities are desired. This distributed architecture places IDS/IPS inspection at each host rather than relying solely on chokepoint-based appliances, providing coverage for east-west traffic that traditional perimeter IDS/IPS solutions do not inspect. The packet interception mechanism underlying this distributed inspection is DVFilters, which operate at the VMware ESX kernel level to intercept packets at each virtual machine's virtual NIC. When deploying IDS/IPS in environments where vSphere vMotion is in use, administrators should verify that IDS and firewall rules permit the ports used for vMotion on ESX hosts. VCF's networking layer, NSX, is the foundation on which vDefend positions its detection and prevention sensors across the environment, providing the traffic routing and distributed switch architecture that the vDefend sensors attach to.
+Organizations deploying VCF should note that while the platform provides the technical IDS/IPS capabilities described above, effective intrusion detection and prevention also requires ongoing operational processes: signature and feed updates, alert triage and tuning, incident escalation workflows, and integration with a security operations center or SIEM for centralized monitoring. The vDefend components that deliver IDS/IPS are licensed separately from the base VCF platform.</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend provides network intrusion detection and prevention capabilities that directly address this control. vDefend with Advanced Threat Prevention combines multiple detection technologies, including Intrusion Detection/Prevention System (IDS/IPS), Network Detection and Response (NDR), and Network Traffic Analysis (NTA), with aggregation, correlation, and context engines to detect and prevent network intrusions.
+vDefend Distributed IDS/IPS operates at the hypervisor level, inspecting both north-south and east-west traffic. Administrators configure and manage intrusion detection and prevention policies through the NSX Manager interface, where they create IDS/IPS profiles, organize signature-based detection policies, and apply them through distributed firewall rules. The distributed architecture places IDS/IPS inspection at the vNIC level on every protected workload, providing visibility into lateral traffic between VMs that traditional perimeter-based NIDS/NIPS cannot see. IDS/IPS can be deployed in Detect Only mode or in Detect and Prevent mode, giving administrators control over enforcement posture.
+Signature management is automated. vDefend IDS/IPS downloads the latest intrusion detection signatures automatically, either directly from the Internet or through a proxy server. Signatures are bundled with custom detection logic that can be updated without recompiling or modifying the IDS engine itself, allowing signature updates to take effect immediately. System Signatures are managed through the Local Manager interface under Security &gt; IDS/IPS &amp; Malware Prevention &gt; Signature Management &gt; System Signatures. When building IDS/IPS profiles, administrators filter included signatures by Intrusion Severities, Attack Types, CVSS scores, Attack Targets, and Products Affected, allowing precise tuning of the detection scope. Administrators can also configure thresholds for individual signatures to control how frequently a signature generates an IPS event, and rate filters that dynamically adjust a rule's action when specific traffic conditions are met. Profiles can also enable packet capture for later analysis of matched traffic.
+Beyond automatic signature bundles, administrators can create custom signatures to detect malicious traffic specific to custom applications or to address zero-day vulnerabilities. Custom signatures support specific alert conditions, content matching, thresholds, and metadata, and can be included in IDS/IPS profiles applied to both the Distributed Firewall and Gateway Firewall. In multi-site environments, custom signatures can be managed from Global Manager. Network Detection and Response also consumes IDPS detections generated from custom IDS signatures, surfacing them alongside other detection events within the NDR interface.
+NDR extends detection beyond signature matching. Network Detection and Response detects IDS events through signature matches against network traffic in the protected network and integrates with Distributed IDS/IPS to display IDS event details within the NDR interface. NDR Sensor IDS monitors network traffic for suspicious activities or known threat signatures, alerting on potential security breaches. NDR Sensor IDS Packet Capture records raw network packets associated with detected intrusion events, supporting forensic analysis and incident response.
+Security Intelligence provides operational visibility into intrusion activity. Intrusion history can be filtered by action, attacker IP, attacker port, PCAP UUID, profile, rule, target IP, target port, and detection location. The IDS/IPS monitoring dashboard allows filtering of intrusion events by multiple criteria to support security event triage and analysis. Per-workload visibility includes impact scoring, signature details, and detection status for each protected VM. Each intrusion event is tagged with a Signature ID and associated protocol information, supporting precise identification and correlation during incident analysis.</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) provides monitoring capabilities specific to the disaster recovery domain and integrates with the broader VCF monitoring ecosystem through dedicated Protection and Recovery dashboards in VCF Operations. VCF Operations collects configuration, component health, and usage information from protection and recovery servers and site pairs, presenting this through an overview dashboard that displays all site pairs, configurations, health scores, and protection and recoverability status for sites and virtual machines. PNR provides default health alerts for protection groups, recovery plans, cloud file systems, recovery SDDCs, and protected sites through VCF Operations, and the dashboards surface alerts informing administrators about configurations and deployments that require attention. Separate dashboard views cover vSAN Snapshots and Replication monitoring, and an Inventory view provides health status, metrics, alerts, and network topology for all monitored objects.
+Within its own domain, PNR provides event logging and configurable alarms for replication and recovery operations. Administrators can create alarms that trigger on specified event conditions, with support for email notifications, SNMP traps, or script execution in response. PNR monitors connections between sites by sending periodic ping requests, logs connection check events, and generates alarms when broken connections are detected. The alarm system generates warning-level alerts for expired snapshot schedules, replication errors such as missing VMs, and connectivity issues with protected and target sites. PNR also monitors resource consumption on the Protection and Recovery Server host and raises alarms when configurable resource thresholds are reached.
+PNR includes a health monitoring service that checks each health finding every five minutes and records a timestamp at each check. Health findings are tracked with status history that can be reviewed over configurable time periods, defaulting to a 24-hour window. The Protection and Recovery Appliance supports syslog forwarding to a remote syslog server for log analysis and centralized monitoring, allowing appliance-level events to flow into existing log management infrastructure.
+The Clean Room Orchestrator, part of PNR's Cyber Recovery capabilities, supports monitoring of clean room events, tasks, and alarms for recovery operations. Clean Room Orchestrator can forward events to VCF Operations, Microsoft Sentinel, or Splunk Cloud for centralized monitoring, supporting organizations that require DR event data to flow into enterprise SIEM and log management platforms as part of a broader monitoring strategy. The Clean Room Orchestrator integrates with endpoint detection and response tools, including CrowdStrike and Carbon Black sensor appliances, for threat detection within isolated recovery environments.</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="L29" s="10" t="inlineStr">
         <is>
           <t>VMware Data Services Manager (DSM) contributes to enterprise-wide monitoring controls through a layered set of observability capabilities covering database health, infrastructure compliance, and event-driven alerting.
 DSM provides a built-in monitoring framework that tracks database instance health across multiple dimensions. From the Monitoring tab in the DSM UI or the vSphere Client, administrators and authorized users can view real-time and historical metrics for database VMs, including CPU Health, Data Disk Health, System Disk Health, Max Connections, Active Connections, Write Throughput, Read Throughput, Thread Resource Utilization, Slow Queries per Second, InnoDB Buffer Usage, and InnoDB Reads and Writes. The Monitoring page defaults to the last three hours of aggregated metric data, with the time range adjustable through the Time Range Last dropdown. This visibility supports detection of resource contention, performance degradation, and connectivity anomalies at the database layer.
@@ -3408,113 +3297,6 @@
 Enterprise-wide monitoring requires organizational decisions about monitoring architecture, log aggregation platforms, alerting policies, and operational response procedures that lie outside DSM's scope. DSM provides the data and integration points; the organization must determine how those signals are collected, correlated, and acted upon across the broader environment.</t>
         </is>
       </c>
-      <c r="M28" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N28" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer (Avi) contributes to enterprise-wide monitoring through application-delivery-layer mechanisms built into the Avi Controller and Service Engines.
-The Avi Controller monitors Service Engine metrics and sends alarms and notifications to administrators when resource utilization data exceeds defined thresholds. Administrators configure custom thresholds on Service Engine groups through the Resource Events tab in the Avi UI. The Alert feature processes system events and metrics against user-defined rules and generates alerts that trigger configured actions, including sending an email, a syslog message, or an SNMP trap. Alert notifications can be forwarded to remote syslog servers for integration with centralized log management and monitoring platforms.
-ControlScripts extend this event-response capability: a ControlScript can alter Avi configuration or communicate to external systems, including through webhook integrations with external monitoring tools, in response to defined system events. This supports dynamic responses including resource scaling or automated notifications based on health scores from monitoring data.
-The Avi Controller and Service Engines track health score changes and SSL certificate expiration events. Avi integrates with external monitoring tools such as Prometheus for metrics collection and analysis. User-Defined Metrics allow administrators to define and extract customized telemetry data for specific compliance or reporting needs through the API. Real-time metrics are available via API but deactivate by default after 30 minutes to conserve resources and must be reactivated when sustained real-time visibility is required.
-At the data plane, Avi health monitors track the status of backend servers and Service Engines continuously. Service Engine health monitoring records detailed server operational status, including health monitor name, type, last transition timestamps, rise count, fall count, total checks, and total failed checks. Each health monitor can be assigned its own threshold and timeout period for server health validation. Monitors support HTTP, HTTPS, TCP, and UDP health-check protocols with configurable success and failure thresholds, send intervals, and receive timeouts.
-In Kubernetes environments managed by the Avi Kubernetes Operator (AKO), the HealthMonitor custom resource definition (CRD) allows users to define custom health monitoring configurations for backend services with fine-grained control over health check parameters. The Avi Multi-Cluster Kubernetes Operator (AMKO) GlobalDeploymentPolicy supports health monitor references for consistent monitoring across multi-cluster deployments. Within VCF Automation, a HealthMonitor custom resource can create monitors for tracking backend pool member status using TCP, PING, and HTTP check types.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>6.5A</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>END-07, MON-01, MON-01.1, NET-08</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Intrusion Detection: Detect and contain anomalous network activity into the local or remote SWIFT environment.</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides enterprise-wide monitoring through integrated tools that span infrastructure health, performance metrics, compliance assessment, log analysis, and alerting.
-VCF Operations continuously monitors the operational state of all VCF components to detect conditions that may affect availability or compliance. It collects metrics across compute, storage, and networking resources, and correlates them over time to identify trends that may lead to potential failures. VCF Health, a component of VCF Operations, continuously monitors the operational state of VCF components to verify they are functioning as expected, giving platform operators a single view of operational status. Platform operators can configure alerts, perform log analysis, run infrastructure diagnostics, and review VCF health from a unified interface.
-VCF Operations provides continuous compliance management by monitoring infrastructure against industry-standard benchmarks and custom policies. Administrators can create custom compliance benchmarks that monitor selected alert definitions and policies, tailoring the monitoring posture to organizational requirements. The platform assesses objects based on selected compliance policies and activates alert definitions associated with the current scorecard, providing ongoing visibility into compliance status. Compliance-related alerts are triggered on objects and displayed through a dedicated compliance alert subtype.
-The alerting subsystem in VCF Operations supports the full lifecycle of alert management. Administrators can configure and manage alert definitions to monitor infrastructure events and conditions, including performance metrics, log events, and custom conditions configured through the Management Pack Builder. The Platform Health Alerts page provides a centralized view of all alerts related to overall system health, including alerts from data sources and infrastructure nodes. Health alerts are generated for conditions that affect the health of the environment and require immediate attention. Administrators can create policies to govern how alert definitions are evaluated, including which objects to monitor and what thresholds to apply, and can apply consistent practices to optimize alert behavior across monitored objects.
-VCF Operations supports flexible grouping and scheduling to align monitoring with operational realities. Custom groups can be configured with automatic membership criteria to support monitoring strategies and achieve a high level of automation. Maintenance schedules can be assigned to objects undergoing planned downtime to keep monitoring data accurate and avoid false alerts when an object is offline for scheduled maintenance.
-VCF Log Management provides centralized log collection and analysis. It ingests logs from VMware vCenter, VMware ESX hosts, NSX, vSAN, VCF Automation, VCF Operations, VCF Identity Broker, VCF Operations for Networks, and VCF Operations HCX. VCF Operations and VCF Log Management must be integrated to implement the centralized log collection architecture. The platform provides dashboards and analytics for troubleshooting and security investigation. Log-based alert definitions allow administrators to trigger notifications when specific log patterns appear across monitored systems. Log forwarding to external SIEM or syslog targets is configurable, with support for TLS encryption to protect log data in transit. The vCenter syslog forwarding API supports TCP, UDP, TLS, and RELP protocols. NSX Manager syslog supports TLS and requires port 6514 for encrypted log transmission.
-At the vSphere layer, the alarm infrastructure integrates with events and performance counters to provide real-time alerting. The MetricAlarmExpression data object allows administrators to set alarms on specific performance metrics with configurable monitoring intervals and aggregation functions for processing data points. The vSphere Client provides direct visibility into tasks and events for change tracking and troubleshooting. VCF ships with preconfigured vSphere alarms that are active by default and monitor specific components including the Identity Management Service, Message Bus Configuration Service, ESX Agent Manager, VMware Service Control Agent, vSphere HA host status, and host connection and power state. The vCenter Management Interface provides appliance-level health visibility through an Overall Health badge that reflects one of five states (Good, Warning, Alert, Critical, or Unknown) across all vCenter components, and notifies administrators of available security patches through Critical or Alert badge indicators when automatic patch checks are enabled.
-When VCF Automation is integrated with VCF Operations, the Insights dashboard and Alerts tab provide real-time capacity awareness and alert information for VCF Automation objects, giving IT teams visibility into resource usage across both provisioned workloads and the underlying infrastructure. The VCF Automation Monitor tab surfaces deployment health information sourced from VCF Operations, and deployment cards display Last Request Status information that tracks the most recent operation on each deployment (Create, Update, or Delete) and its outcome (Successful, In Progress, or Failed). The Management Pack Builder allows administrators to set up event definitions for integrated systems, monitoring specific conditions or thresholds and configuring alerts for proactive management. Management Packs extend monitoring to network devices, including sensor monitoring for devices such as switches and routers. Adapters can be installed on VCF Operations nodes to extend monitoring to additional systems and data sources beyond the core VCF components.
-The VMware Kubernetes Service (VKS) layer of VCF extends enterprise monitoring to container workloads and Kubernetes infrastructure. VKS clusters support MachineHealthCheck objects for both control plane nodes and worker node deployments; administrators manage these through the VCF CLI vcf cluster machinehealthcheck command, which supports configuration of unhealthy-condition definitions, maximum unhealthy thresholds (expressed as an absolute number or a percentage), and label selectors to target specific machines. The VCF CLI vcf cluster machinehealthcheck node get and vcf cluster machinehealthcheck control-plane get commands retrieve node and control plane health status on demand. VKS cluster health conditions, including the Ready and ControlPlaneReady status indicators, reflect the operational state of each cluster and are accessible via kubectl and the VCF CLI. The VCF Automation Provider Management UI includes a Services overview interface that exposes VKS cluster management functions and the health status of all cluster elements, giving platform operators a centralized view of the VKS tier. The Kubernetes API server within VKS clusters exposes diagnostic and health check endpoints (/healthz, /livez, /readyz, /statusz, and /metrics) that external monitoring systems can scrape to track API server availability and readiness; the kube-apiserver also emits the kubernetes_healthchecks_total counter and kubernetes_healthcheck gauge metric, which report structured health check status for components including etcd and autoregister-completion. Access to these monitoring endpoints is governed by the built-in Kubernetes system:monitoring RBAC group, which grants read access to liveness, readiness, and metrics endpoints while restricting broader cluster access. The Kubernetes Watch API allows monitoring tools to track changes to any API object as a live stream, supporting event-driven monitoring without continuous polling. The Node Problem Detector monitors node health and surfaces node-level problems as Kubernetes events and node conditions that external monitoring systems can consume via the event stream.
-For workload-level monitoring within VKS clusters, Prometheus Operator is available as a standard package and defines custom resource definitions to deploy and manage Prometheus and Alertmanager StatefulSets, enabling high-availability alerting configurations. The Prometheus Alertmanager custom resource definition configures alert grouping, inhibition, and routing to external notification systems. The Istio service mesh, also available as a standard package on VKS clusters, provides service-level monitoring alongside its traffic management capabilities. The Dynatrace Operator can be deployed on VKS clusters to automate the deployment, scaling, and maintenance of the Dynatrace monitoring stack. Historical analysis, dashboarding, and alerting on cluster-level metrics require a dedicated monitoring solution configured to scrape the VKS metrics endpoints and subscribe to the Kubernetes event stream. The vcf cluster support-bundler create command gathers diagnostic information from Supervisor and VKS clusters when troubleshooting is needed.
-At the network layer, NSX provides monitored indicators including node uptime status, deployment status, management and controller connections, tunnel status, PNIC status, and uptime duration. NSX time series APIs allow viewing data such as VPN statistics, including metadata about the number of tunnels configured and how many are up or down at a given time.
-VCF Operations also supports self-monitoring through the VCF Operations adapter, which collects internal metrics such as activity success counts. This allows administrators to verify that the monitoring platform itself is functioning correctly. The VCF Operations policy engine monitors conditions and generates events to react to changing states in the orchestrator server or connected technologies. The Adapter Instance monitoring interval is configurable, with intervals as granular as five minutes.
-VMware Private AI Services (PAIS) includes a built-in observability stack that supplies monitoring data for AI infrastructure and AI workloads. PAIS Controller metrics are exposed at a Prometheus metrics endpoint on the pais-controller-manager service, allowing collection by monitoring systems and visualization in observability platforms such as Grafana. Observability is activated by updating the PAISConfiguration custom resource with optional sections for Prometheus metrics collection and LLM trace forwarding. The Prometheus runtime can be configured with a specified storage class policy and a configurable metrics retention period, giving administrators control over how long monitoring data is stored. A Prometheus server pod must be in a ready and running state for observability to function.
-LLM trace data from PAIS can be forwarded to an OpenTelemetry Collector endpoint over http/protobuf or gRPC, providing distributed tracing for AI model inference activity. The observability.llmTraces configuration governs trace forwarding and works alongside the Prometheus metrics pipeline to produce two signals: metrics for health and performance, and traces for inference-level behavior. PAIS Controller metrics include the Model Endpoint Controller and PAIS Configuration Controller, giving monitoring platforms component-level visibility into PAIS operations.
-In 9.1, PAIS adds direct integration with VCF Operations. The controller-pod-metrics-streaming setting activates streaming of PAIS controller pod metrics from the Supervisor cluster to VCF Operations, allowing administrators to view PAIS metrics alongside other VCF infrastructure metrics. A Telegraf deployment in the vmware-system-monitoring namespace uses a telegraf-user-config ConfigMap to manage user-configured monitoring endpoints for PAIS. The VCF Consumption CLI connects to the Supervisor endpoint and enables VI administrators to stream metrics from the PAIS controller pod. DevOps engineers can visualize health and performance metrics for PAIS components running in a VCF Automation namespace using Grafana, and MLOps engineers and application developers can monitor the health, quality, and behavior of AI applications and the models used in agents through the same observability platforms.
-PAIS supplies the technical monitoring mechanisms this control requires. Enterprise-wide orchestration of monitoring controls, including alert threshold definition, escalation procedures, and integration with a centralized monitoring or log management platform, remain organizational responsibilities.</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend (vDefend) supports network security monitoring through multiple integrated capabilities that contribute to enterprise-wide monitoring frameworks.
-Security Intelligence, hosted on the Security Services Platform (SSP), provides continuous visibility into network traffic flows across protected workloads. It monitors flows between application pairs, updates the Policy Protection Status for each application to indicate that flows are being monitored, and continuously detects new flows between environment pairs, alerting administrators to unauthorized or unexpected traffic. The Monitor &amp; Plan Overview page presents a consolidated view of pending actions, data collection activity status, network security posture, flow trends, and a summary of suspicious traffic. The Security Intelligence Recommendations monitoring capability checks for changes in the scope of monitored entities every hour when the Monitoring toggle is enabled, allowing administrators to keep policy recommendations current as environments evolve. Segmentation Monitoring provides dedicated views of application and infrastructure flows with configurable time ranges spanning from the last hour to the last month, and displays flows related to detected infrastructure servers in a specified time interval.
-The Network Detection and Response (NDR) Sensor checks the status of activated detection features every 15 minutes and updates its configuration accordingly, supporting sustained threat detection coverage. NDR Sensor health status monitoring tracks whether key components, including network traffic capture, file analysis, and data transmission, are operating properly. The NDR Sensor also sends alerts notifying administrators of conditions such as services being down, high CPU, memory, or disk usage, packet drops, or missed heartbeats. NDR provides role-based access control covering triage operations such as viewing detections and campaigns, as well as SIEM configuration management.
-The Security Services Platform monitors its own health, with Yellow or Red health status indicators displayed when issues occur in subcomponents. SSP monitoring tracks the status of the flow clustering job that runs every hour and reports suspicious traffic detector execution status after each run, with values such as SUCCESS, NOT_ENOUGH_BASELINE, and FAILURE.
-The Security dashboard provides a consolidated view for monitoring and configuring security features across network workloads. In federated deployments, the Global Manager provides centralized event management and monitoring for malicious IP blocking activity across all Local Managers.
-vDefend generates Unified Security Logs that VCF Log Management can collect and analyze. These logs cover Distributed Firewall, Gateway Firewall, Identity Firewall, FQDN Analysis, TLS Inspection, Intrusion Detection/Prevention System (IDPS), and URL Filtering activity. Broader log aggregation and SIEM correlation for enterprise-wide monitoring remain the responsibility of the SIEM and logging infrastructure deployed alongside vDefend.</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides monitoring capabilities specific to the disaster recovery domain and integrates with the broader VCF monitoring ecosystem through dedicated Protection and Recovery dashboards in VCF Operations. VCF Operations collects configuration, component health, and usage information from protection and recovery servers and site pairs, presenting this through an overview dashboard that displays all site pairs, configurations, health scores, and protection and recoverability status for sites and virtual machines. PNR provides default health alerts for protection groups, recovery plans, cloud file systems, recovery SDDCs, and protected sites through VCF Operations, and the dashboards surface alerts informing administrators about configurations and deployments that require attention. Separate dashboard views cover vSAN Snapshots and Replication monitoring, and an Inventory view provides health status, metrics, alerts, and network topology for all monitored objects.
-Within its own domain, PNR provides event logging and configurable alarms for replication and recovery operations. Administrators can create alarms that trigger on specified event conditions, with support for email notifications, SNMP traps, or script execution in response. PNR monitors connections between sites by sending periodic ping requests, logs connection check events, and generates alarms when broken connections are detected. The alarm system generates warning-level alerts for expired snapshot schedules, replication errors such as missing VMs, and connectivity issues with protected and target sites. PNR also monitors resource consumption on the Protection and Recovery Server host and raises alarms when configurable resource thresholds are reached.
-PNR includes a health monitoring service that checks each health finding every five minutes and records a timestamp at each check. Health findings are tracked with status history that can be reviewed over configurable time periods, defaulting to a 24-hour window. The Protection and Recovery Appliance supports syslog forwarding to a remote syslog server for log analysis and centralized monitoring, allowing appliance-level events to flow into existing log management infrastructure.
-The Clean Room Orchestrator, part of PNR's Cyber Recovery capabilities, supports monitoring of clean room events, tasks, and alarms for recovery operations. Clean Room Orchestrator can forward events to VCF Operations, Microsoft Sentinel, or Splunk Cloud for centralized monitoring, supporting organizations that require DR event data to flow into enterprise SIEM and log management platforms as part of a broader monitoring strategy. The Clean Room Orchestrator integrates with endpoint detection and response tools, including CrowdStrike and Carbon Black sensor appliances, for threat detection within isolated recovery environments.</t>
-        </is>
-      </c>
-      <c r="K29" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="L29" s="10" t="inlineStr">
-        <is>
-          <t>VMware Data Services Manager (DSM) contributes to enterprise-wide monitoring controls through a layered set of observability capabilities covering database health, infrastructure compliance, and event-driven alerting.
-DSM provides a built-in monitoring framework that tracks database instance health across multiple dimensions. From the Monitoring tab in the DSM UI or the vSphere Client, administrators and authorized users can view real-time and historical metrics for database VMs, including CPU Health, Data Disk Health, System Disk Health, Max Connections, Active Connections, Write Throughput, Read Throughput, Thread Resource Utilization, Slow Queries per Second, InnoDB Buffer Usage, and InnoDB Reads and Writes. The Monitoring page defaults to the last three hours of aggregated metric data, with the time range adjustable through the Time Range Last dropdown. This visibility supports detection of resource contention, performance degradation, and connectivity anomalies at the database layer.
-DSM's alert framework provides configurable thresholds for warning and critical conditions on key health indicators. Administrators and users can set separate warning and critical thresholds for CPU Health, Data Disk Health, System Disk Health, and Max Connections parameters. When thresholds are exceeded, DSM generates typed alerts such as Database Engine Health, Custom Config Health, and Backup Storage Health alerts. DSM monitors database replication status and raises an alert when a secondary database is not replicating data from the primary. DSM also raises an alert when metrics are no longer being received from a cluster, supporting detection of monitoring gaps. Alerts can be activated or deactivated per data service through the "Enable Alerts for DB Alert" setting, providing granular control over which databases are subject to active alerting. For each alert, DSM provides mitigation suggestions to help administrators resolve issues without disrupting database services.
-In addition to database-level alerts, DSM generates global infrastructure alerts that surface vCenter integration and infrastructure policy issues. These include INFRASTRUCTURE_POLICY_VC_ALARMS, raised when vCenter resource alarms are active; INFRASTRUCTURE_POLICY_CLUSTER_COMPLIANT and INVALID_SUPERVISOR_INFRASTRUCTURE_POLICY_STATUS, which reflect cluster compliance state; VCENTER_CONNECTIVITY, raised when vCenter connectivity fails and triggering troubleshooting steps that include verifying connectivity and checking authentication logs; and LicensingNotUpdated and vCenterBinding API status alerts that surface license and API integration conditions. A Global Alerts page in the DSM UI provides a centralized view of these alerts during and after installation and ongoing operation.
-In 9.1, DSM integrates with VCF Operations to extend observability beyond the DSM UI. When configured, VCF Operations automatically discovers and monitors PostgreSQL and MySQL clusters in the Ready state and displays a Data Services View dashboard showing active alerts and inventory items. VCF Operations presents performance data across three levels: cluster-level for overall health, node-level for infrastructure resource use, and database-level for KPIs including Active Connections, Commits, Rollbacks, and Deadlocks. This integration requires configuring the connection between DSM and VCF Operations before use.
-DSM also adds SQL Server as a supported database type, with dedicated monitoring through an integrated InfluxDB instance and Telegraf agents deployed across the provider appliance and SQL Server workload clusters. The monitoring framework supports metrics-based and status-condition-based alerts for SQL Server, covering database engine degradation, non-operational status, and automated or transaction log backup failure conditions.
-DSM supports event notification to external systems through a webhook integration. Webhooks transmit alert notifications containing the triggered date, triggered time, triggered user email, task status, previous status, and task type. This allows DSM alerts to feed into centralized monitoring or incident management platforms maintained by the organization. DSM generates plug-in registration logs that administrators can review for vCenter connectivity errors, and DSM's troubleshooting guidance directs administrators to review active vCenter infrastructure alarms and resolve underlying issues identified through the alert system.
-Enterprise-wide monitoring requires organizational decisions about monitoring architecture, log aggregation platforms, alerting policies, and operational response procedures that lie outside DSM's scope. DSM provides the data and integration points; the organization must determine how those signals are collected, correlated, and acted upon across the broader environment.</t>
-        </is>
-      </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
           <t>Contributes</t>
@@ -3522,12 +3304,13 @@
       </c>
       <c r="N29" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) contributes to enterprise-wide monitoring through application-delivery-layer mechanisms built into the Avi Controller and Service Engines.
-The Avi Controller monitors Service Engine metrics and sends alarms and notifications to administrators when resource utilization data exceeds defined thresholds. Administrators configure custom thresholds on Service Engine groups through the Resource Events tab in the Avi UI. The Alert feature processes system events and metrics against user-defined rules and generates alerts that trigger configured actions, including sending an email, a syslog message, or an SNMP trap. Alert notifications can be forwarded to remote syslog servers for integration with centralized log management and monitoring platforms.
-ControlScripts extend this event-response capability: a ControlScript can alter Avi configuration or communicate to external systems, including through webhook integrations with external monitoring tools, in response to defined system events. This supports dynamic responses including resource scaling or automated notifications based on health scores from monitoring data.
-The Avi Controller and Service Engines track health score changes and SSL certificate expiration events. Avi integrates with external monitoring tools such as Prometheus for metrics collection and analysis. User-Defined Metrics allow administrators to define and extract customized telemetry data for specific compliance or reporting needs through the API. Real-time metrics are available via API but deactivate by default after 30 minutes to conserve resources and must be reactivated when sustained real-time visibility is required.
-At the data plane, Avi health monitors track the status of backend servers and Service Engines continuously. Service Engine health monitoring records detailed server operational status, including health monitor name, type, last transition timestamps, rise count, fall count, total checks, and total failed checks. Each health monitor can be assigned its own threshold and timeout period for server health validation. Monitors support HTTP, HTTPS, TCP, and UDP health-check protocols with configurable success and failure thresholds, send intervals, and receive timeouts.
-In Kubernetes environments managed by the Avi Kubernetes Operator (AKO), the HealthMonitor custom resource definition (CRD) allows users to define custom health monitoring configurations for backend services with fine-grained control over health check parameters. The Avi Multi-Cluster Kubernetes Operator (AMKO) GlobalDeploymentPolicy supports health monitor references for consistent monitoring across multi-cluster deployments. Within VCF Automation, a HealthMonitor custom resource can create monitors for tracking backend pool member status using TCP, PING, and HTTP check types.</t>
+          <t>VMware Avi Load Balancer (Avi) contributes to network intrusion detection and prevention at the application delivery layer through IP Reputation-based threat classification, automated DDoS detection and response, bot management, and an Application Rules service.
+The IP Reputation service classifies source IP addresses across a wide range of threat categories, including DoS and DDoS attack sources, malware-infected hosts, phishing sites, proxy services, network scanners, and botnets. When an IP address falls into a relevant threat category, administrators configure Network Security Policies on virtual services to identify and block connections from those addresses. Network Security Policy evaluates incoming client traffic based on network-level parameters and determines whether a connection should be accepted, discarded, or rate-limited, including dropping TCP SYN packets from flagged addresses. Shared IP groups allow a single blocklist to be referenced across multiple virtual service policies, so a flagged address can be blocked consistently across the application delivery tier.
+For volumetric and protocol attacks, Avi Service Engines detect and mitigate DDoS attacks across Layer 4 through Layer 7, including DNS amplification attacks, DNS Reflection Ingress attacks, and NXDOMAIN attacks. Avi can also report or actively block attackers performing port scans as part of DDoS detection. DDoS attack mitigation mechanisms support IPv6 addresses, including mitigation for Neighbor Discovery Protocol (NDP) attacks. The Avi Controller monitors denial-of-service attack events with configurable alert levels and thresholds, tracking attack count metrics and generating alerts at configurable severity levels. When a SYN flood or other volumetric attack is detected, alert actions can automatically invoke ControlScripts that add the offending source IP address to a blocklist IP group attached to a network security policy, providing automated blocking in response to detected attack events. The Avi Security Manager creates network security rules and DNS rules for Service Engines to block the attacker's IP address, source port, and DNS record request types.
+The Application Rules service, available through Avi Cloud Console, provides automatically updated rules specifically designed to block attacks on known application vulnerabilities, including those with published CVE identifiers. These rules extend the detection and prevention surface to application-layer attack patterns beyond IP reputation filtering.
+The Bot Management capability identifies bot traffic intent, distinguishing benign bots from malicious actors such as scrapers, spam sources, click fraud engines, bot impersonators, and botnets. The IP Reputation service is also used as a source for bot detection and classification, combining IP-reputation detection, user-agent detection, and IP-location detection through the Bot Decision Component.
+For Kubernetes environments, the Avi Kubernetes Operator (AKO) supports L4 Rule CRDs that express custom security policies applied to virtual service traffic, specifying configuration for DDoS attack detection and mitigation. These CRDs can also allow, deny, or rate-limit connections from individual or grouped IP addresses. HostRule CRDs can reference network security policy objects for consistent policy application across ingress resources.
+These capabilities address intrusion detection and prevention at the application ingress path. Network-layer intrusion detection and prevention covering east-west and north-south traffic flows across the broader VCF environment is provided by VMware vDefend with IDS/IPS capabilities, which is a separate product and carries the Meets rating for this control. Full satisfaction of the control requires NIDS/NIPS deployment at multiple network layers.</t>
         </is>
       </c>
     </row>
@@ -3559,15 +3342,15 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>VCF provides technical capabilities that support several phases of the incident handling lifecycle, though the organizational preparation, process governance, and manual intake elements require processes and structures outside the platform.
-For preparation, VCF Operations supports the configuration of notification rules with detailed incident field mappings, including incident state, resolution codes, impact, urgency, priority, severity levels, and assignment groups. The ServiceNow Management Pack can be configured with parameters such as callerId, propagateAlertUpdates, retrieveIncidentUpdates, and incidentReopenState, allowing organizations to establish incident handling workflows before events occur. These configuration options allow teams to define how incidents are categorized, prioritized, and routed in advance of any actual incident.
-For automated event detection, VCF Operations correlates events from monitored infrastructure components and delivers them as faults. Events are ranked by severity from Info through Warning, Critical, and Immediate, and notification rules trigger actions based on incident state changes. VCF Operations can automatically create incidents in ServiceNow through the Service-Now Notifications plug-in, with structured information including the caller, category, subcategory, and business service. This integration bridges the gap between infrastructure monitoring and organizational incident tracking systems. VCF Operations also combines Diagnostic Findings with VCF Health to detect and predict issues, which helps reduce mean time to resolution. VMware vCenter alarms provide additional automated detection, triggering script execution, SNMP traps, email notifications, or API calls when infrastructure conditions exceed defined thresholds.
-For analysis, the Troubleshooting Incident Page displays information related to the entity under investigation, including traffic and flows on the entity, past incidents created for that entity, status, root cause metrics, and closing remarks. Operators can flag metrics and mark specific metrics as root cause during investigation. The Notes section on each incident allows users to add observations that are visible to anyone who opens the session, which supports collaborative analysis across team members. vCenter Events record user and system actions on inventory objects and can be used for forensic analysis and auditing of activity in the virtual environment, providing an audit trail for incident investigation. Diagnostic Findings consolidates log-based and property-based findings with specific resolution recommendations and links to knowledge base articles, helping analysts identify known issues by matching log patterns and property-based signatures against a library of diagnostic rules. Log Assist can generate log bundles and automatically attach property-based diagnostic findings data to support cases. VCF Operations also integrates with ServiceNow, allowing incidents to flow into existing ITSM workflows for structured triage.
-For containment, vCenter supports isolating affected workloads through VM power state changes and network reconfiguration. VMware vDefend (a separate product that extends VCF's networking foundation) provides more targeted containment through quarantine policies that automatically isolate VMs based on security events while preserving forensic access for investigation. Physical containment, network isolation decisions, and cross-system coordination during active incidents depend on processes and authority structures that exist outside the platform.
-For eradication, VCF Operations maps out-of-the-box workflows to recommendations and associates them with specific alerts, enabling automated remediation of known conditions. Diagnostic Findings helps operators find and resolve known issues using diagnostic rules and signatures, with recommended fixes based on industry-standard best practices.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a host failure, with admission control policies that reserve capacity for failover. Proactive HA integrates with hardware vendor monitoring to detect degrading components and evacuate workloads before failure occurs. vSphere Fault Tolerance provides continuous availability for workloads that require zero-downtime protection during failover. VCF Operations maintains a summary view of all incidents with status tracking, entity counts for in-progress incidents, and counts of top root causes for visibility into the overall state of incident resolution.
-VCF Operations also provides a centralized incident list displaying all incidents with their status and key details, with edit, share, and delete actions for incident lifecycle management. Incident tracking captures state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation, which is a structured audit trail for each incident. The Guided Network Troubleshooting feature automatically maintains a list of the 20 most recently modified incidents within a selected scope for continuity across investigation sessions.
-While VCF Operations provides tooling for detection, analysis, and remediation of infrastructure incidents, several aspects of the six-phase incident handling lifecycle require organizational processes beyond what the platform provides. Preparation requires documented incident response plans, team roles, and communication procedures. Manual incident report intake requires organizational channels and triage processes. Containment decisions require human judgment and authority structures. A formal incident response program that incorporates VCF's technical capabilities into broader organizational processes is necessary to address all six phases.</t>
+          <t>VCF provides technical capabilities that support an organization's incident response operations, though it does not govern organization-wide incident response processes or maintain incident response documentation. VCF Operations is the primary platform for detecting, tracking, and investigating infrastructure-level incidents across the VCF environment.
+VCF Operations includes a dedicated incident management system that displays all incidents with their current status and key metadata. Each incident record tracks state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation. Operators can edit, share, and delete incidents directly from the incident list interface, and the system maintains an audit trail of who created each incident and when. This structured tracking provides the documentation trail that incident response processes require.
+For incident investigation, VCF Operations provides root cause analysis tooling through its Troubleshooting Incident Page. This interface displays information about the affected entity, including traffic and flow data, any past incidents created for the same entity, and root cause metrics. Investigators can flag individual metrics and mark specific metrics as the root cause of an incident. The system also allows drill-down into related entities to view detailed metrics for problem investigation, supporting a methodical approach to identifying the source and scope of an issue. A summary view displays the count of in-progress incidents, entity counts, and top root causes, which supports situational awareness during active incident response and helps teams prioritize efforts across multiple concurrent issues.
+For detection, VCF Operations performs event correlation across monitored systems, correlating a subset of published events and delivering them as faults. The platform maps events from target systems into the VCF Operations severity model, with event severity ranked from Info to Immediate. This automated correlation and severity classification helps operations teams identify incidents that require immediate response. Notification rules can be configured to trigger actions based on incident state changes, with configurable fields including incident state, resolution code, on-hold reason, impact, urgency, priority, assignment group, assigned-to person, severity, approval actions, related problems, and change cause. VCF Operations also supports defining fault symptoms and metric event symptoms based on thresholds and conditions reported by monitored systems, which can be combined into alert definitions that surface conditions requiring operator attention.
+At the VMware vCenter level, alarms can execute scripts, send SNMP traps, or call APIs when infrastructure conditions match defined thresholds. The SNMP agent included with vCenter sends traps when alarms are triggered, and VCF PowerCLI provides programmatic access to alarm management through cmdlets that support creation of script-based and SNMP alarm actions. These capabilities provide automated event detection and alerting that feed into broader incident response processes.
+To integrate with broader organizational incident response workflows, VCF Operations supports a ServiceNow Notifications plug-in that creates incidents directly in a ServiceNow ticketing system. The integration is configurable with fields including caller ID, incident category, sub-category, business service, contact type, and propagation settings for alert updates. This integration enables VCF-detected incidents to flow into an organization's established incident response and ticketing processes.
+For recovery, vSphere HA automatically restarts VMs on healthy hosts after a physical machine failure. Proactive HA integrates with hardware vendor health monitoring to evacuate workloads before failures occur. vSphere cluster HA configuration supports multiple remediation modes, including quarantine mode, maintenance mode, and mixed mode. These recovery capabilities can be exercised ad hoc or incorporated into existing playbooks and runbooks.
+VMware vDefend (a separate product that extends VCF's networking foundation) adds automated threat detection and containment through IDS/IPS and network detection features, including quarantine policies that isolate affected VMs while preserving forensic access.
+This control requires organization-wide incident response governance, documented processes, and cross-functional coordination that go beyond what any infrastructure platform provides on its own. VCF delivers incident tracking, investigation tooling, event correlation, automated alerting, ITSM integration, and infrastructure recovery capabilities that form a technical foundation for incident response, but organizations must build their own incident response plans, escalation procedures, communication protocols, and training programs around these capabilities.</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -3577,12 +3360,12 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (VMware vDefend and Advanced Threat Protection) contributes to multiple phases of the incident handling lifecycle through network-layer detection, multi-signal analysis, and automated containment capabilities.
-For detection and event intake, Security Intelligence categorizes detected suspicious traffic events by impact type, assigning Critical, High, Medium, or Low severity to help teams prioritize response. Security Intelligence also maps detections to MITRE ATT&amp;CK tactics and techniques and records occurrence counts over configurable time windows, providing the structured event context that analysis workflows require.
-For analysis, Malware Prevention generates File Analysis Reports and Process Analysis Reports that detail the types of activities detected during artifact inspection. File Analysis Reports classify detected behaviors across categories including Autostart, Disable, Evasion, File, Memory, Network, Reputation, Settings, Signature, Steal, Stealth, and Silenced, and include an ATT&amp;CK TECHNIQUES field that records observed malicious actions or tools. Process Analysis Reports document in-memory script buffer inspection results and carry an Analyst UUID to track individual inspection events. Malware Prevention Service event logs capture file type, file size, inspection timestamp, client VM ID, submission source, detection status, verdict, and analysis status for each inspected file. The Malware Prevention Dashboard aggregates file and process event details and inspection results for operator review. Network Detection and Response (NDR) Campaign Correlation Rules correlate labeled file and process detections, including AV labels and PCAP matches, with matching IDS events on the same compute, supporting multi-signal analysis during investigation. The Security Services Platform assigns a Security Operator role dedicated to monitoring security systems and responding to security incidents.
-For containment and eradication, Intelligent Assist supports remediation by allowing selection of a Targeted Strategy for surgical, focused containment or a Comprehensive Strategy for broader remediation across potentially affected workloads. The Security Segmentation Report's Overview section summarizes inter-environment policies and rules, providing traffic flow context that can inform containment scope. Security Explorer's ratio of detected versus prevented events helps operators assess how effectively controls are operating during active response.
-A limitation applies to automated remediation: objects generated during Intelligent Assist or NDR remediation that encounter errors require manual cleanup, so recovery activities may require human intervention beyond automated policy actions. vDefend IDS/IPS also applies a severity-based prioritization under memory pressure, dropping lower-severity events (Low and Informational) first before Medium, High, and Critical, which operators should account for when assessing detection completeness during an investigation.
-Preparation and full organizational recovery rely on processes and tooling outside vDefend's scope.</t>
+          <t>VMware vDefend contributes to incident response operations by providing integrated threat detection, investigation, correlation, and remediation capabilities within the network security layer of VCF. Security Services Platform defines a Security Operator role specifically for monitoring security systems and responding to security incidents, providing a built-in responsibility model for incident response activities at the network security layer.
+Security teams can investigate individual threat events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take appropriate mitigation actions. The Campaign Blueprint feature visualizes correlated security events and key actors within a campaign, simplifying triage and investigation to reduce mean time to detection. Campaign correlation surfaces multi-stage attack patterns: a drive-by infection event followed by a command-and-control event on the same workload is linked into a single campaign view. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions.
+Network Detection and Response (NDR) provides security analysts with capabilities to understand security events, triage them, and remediate by creating policies. NDR includes Suspicious Traffic detectors that collect and display suspicious traffic detections as events. Each detection event receives an impact score calculated from Confidence and Severity; informational events with scores from 1 to 24 indicate activity that is not essentially malicious and help teams focus attention on higher-priority events.
+Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows, helping teams assess the potential scope and lateral spread of an incident. The Rule Analysis feature generates downloadable CSV reports of anomaly analysis results, with separate files for each detected anomaly type. Security Services Platform provides metrics for Malware Prevention Service events, including malware family, non-benign indicators, process inspection events, and process state data, accessible through the API.
+For remediation, the Response and Remediation feature in Security Services Platform performs automated policy creation based on user role and permissions. Intelligent Assist supports two remediation strategies, Targeted (surgical, with potentially lower breadth) and Comprehensive (broader scope), allowing teams to select the appropriate approach for each incident. Security Services Platform collects IDS policies, rules, and security profiles created by Intelligent Assist as part of remediation operations. Objects generated during NDR remediation that encounter errors require manual cleanup in Intelligent Assist.
+These capabilities support detection, investigation, and remediation phases of an incident response lifecycle at the network security layer. vDefend does not govern organization-wide incident response processes, maintain incident response documentation, or manage incident tracking and status coordination functions. Those organizational and process governance functions fall outside the scope of a network security product.</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
